--- a/Data/FlightPlan/FPL_07OCT26.xlsx
+++ b/Data/FlightPlan/FPL_07OCT26.xlsx
@@ -431,525 +431,525 @@
     <t>VN-A544</t>
   </si>
   <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>23:50</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>CXR</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>BAX</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>DPS</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>HGH</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
     <t>06:05</t>
   </si>
   <si>
     <t>08:15</t>
   </si>
   <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>23:50</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>CXR</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>BAX</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>DPS</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>HGH</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
     <t>VN-A658</t>
   </si>
   <si>
@@ -1172,7 +1172,7 @@
     <t>Total Record(s): 337</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 06, 2026 20:12</t>
+    <t xml:space="preserve">Generated on  Oct 07, 2026 00:01</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3883,7 +3883,7 @@
         <v>13</v>
       </c>
       <c r="B80" s="7">
-        <v>124</v>
+        <v>382</v>
       </c>
       <c t="s" r="C80" s="7">
         <v>14</v>
@@ -3899,13 +3899,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -3916,7 +3916,7 @@
         <v>13</v>
       </c>
       <c r="B81" s="7">
-        <v>129</v>
+        <v>383</v>
       </c>
       <c t="s" r="C81" s="7">
         <v>14</v>
@@ -3929,16 +3929,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4052,7 +4052,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4115,10 +4115,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4132,11 +4132,11 @@
         <v>3523</v>
       </c>
       <c t="s" r="C88" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4148,10 +4148,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4165,11 +4165,11 @@
         <v>3523</v>
       </c>
       <c t="s" r="C89" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4178,10 +4178,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H89" s="8">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J89" s="7">
         <v>118</v>
@@ -4217,22 +4217,22 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="H91" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4262,10 +4262,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4292,13 +4292,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4316,22 +4316,22 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4373,10 +4373,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>23</v>
@@ -4397,13 +4397,13 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c t="s" r="H97" s="8">
         <v>17</v>
@@ -4412,7 +4412,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4445,7 +4445,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4475,7 +4475,7 @@
         <v>123</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>95</v>
@@ -4507,17 +4507,17 @@
         <v>7707</v>
       </c>
       <c t="s" r="C101" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="H101" s="8">
         <v>17</v>
@@ -4540,11 +4540,11 @@
         <v>7707</v>
       </c>
       <c t="s" r="C102" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4553,10 +4553,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>63</v>
@@ -4577,22 +4577,22 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4622,10 +4622,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4654,11 +4654,11 @@
         <v>5069</v>
       </c>
       <c t="s" r="C106" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4667,13 +4667,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H106" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4687,23 +4687,23 @@
         <v>7620</v>
       </c>
       <c t="s" r="C107" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="H107" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J107" s="7">
         <v>62</v>
@@ -4720,11 +4720,11 @@
         <v>7620</v>
       </c>
       <c t="s" r="C108" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4733,10 +4733,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>69</v>
@@ -4753,26 +4753,26 @@
         <v>7621</v>
       </c>
       <c t="s" r="C109" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4814,7 +4814,7 @@
         <v>49</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="I111" s="7">
         <v>112</v>
@@ -4838,19 +4838,19 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J112" s="7">
         <v>114</v>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -4883,10 +4883,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -4919,7 +4919,7 @@
         <v>130</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -4964,10 +4964,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -4994,7 +4994,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="I117" s="7">
         <v>111</v>
@@ -5018,22 +5018,22 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="H118" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5063,7 +5063,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J119" s="7">
         <v>96</v>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5111,10 +5111,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5144,7 +5144,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>36</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5180,7 +5180,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5207,13 +5207,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5231,22 +5231,22 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5273,13 +5273,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>204</v>
+        <v>141</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5327,7 +5327,7 @@
         <v>206</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5390,7 +5390,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>107</v>
@@ -5468,13 +5468,13 @@
         <v>123</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5498,16 +5498,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="I134" s="7">
         <v>43</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5531,16 +5531,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5564,16 +5564,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>123</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5654,7 +5654,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5684,7 +5684,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>220</v>
+        <v>144</v>
       </c>
       <c t="s" r="J140" s="7">
         <v>221</v>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5747,13 +5747,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H142" s="8">
+        <v>140</v>
+      </c>
+      <c t="s" r="I142" s="7">
+        <v>181</v>
+      </c>
+      <c t="s" r="J142" s="7">
         <v>222</v>
-      </c>
-      <c t="s" r="I142" s="7">
-        <v>180</v>
-      </c>
-      <c t="s" r="J142" s="7">
-        <v>223</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5771,13 +5771,13 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>222</v>
+        <v>140</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>17</v>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5813,7 +5813,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c t="s" r="I144" s="7">
         <v>108</v>
@@ -5837,22 +5837,22 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
+        <v>223</v>
+      </c>
+      <c t="s" r="H145" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I145" s="7">
         <v>224</v>
       </c>
-      <c t="s" r="H145" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I145" s="7">
+      <c t="s" r="J145" s="7">
         <v>225</v>
-      </c>
-      <c t="s" r="J145" s="7">
-        <v>226</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -5894,13 +5894,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="I147" s="7">
         <v>71</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -5918,13 +5918,13 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>16</v>
@@ -5933,7 +5933,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -5960,7 +5960,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c t="s" r="I149" s="7">
         <v>115</v>
@@ -5984,13 +5984,13 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>16</v>
@@ -5999,7 +5999,7 @@
         <v>66</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6017,7 +6017,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6062,10 +6062,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6098,22 +6098,22 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
+        <v>230</v>
+      </c>
+      <c r="F154" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G154" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H154" s="8">
         <v>231</v>
       </c>
-      <c r="F154" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G154" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H154" s="8">
+      <c t="s" r="I154" s="7">
+        <v>144</v>
+      </c>
+      <c t="s" r="J154" s="7">
         <v>232</v>
-      </c>
-      <c t="s" r="I154" s="7">
-        <v>220</v>
-      </c>
-      <c t="s" r="J154" s="7">
-        <v>233</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6131,19 +6131,19 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
+        <v>230</v>
+      </c>
+      <c r="F155" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G155" s="8">
         <v>231</v>
       </c>
-      <c r="F155" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G155" s="8">
-        <v>232</v>
-      </c>
       <c t="s" r="H155" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>73</v>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6176,10 +6176,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I156" s="7">
+        <v>233</v>
+      </c>
+      <c t="s" r="J156" s="7">
         <v>234</v>
-      </c>
-      <c t="s" r="J156" s="7">
-        <v>235</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6209,10 +6209,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6245,22 +6245,22 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
+        <v>236</v>
+      </c>
+      <c r="F159" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G159" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H159" s="8">
         <v>237</v>
       </c>
-      <c r="F159" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G159" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H159" s="8">
+      <c t="s" r="I159" s="7">
         <v>238</v>
       </c>
-      <c t="s" r="I159" s="7">
-        <v>239</v>
-      </c>
       <c t="s" r="J159" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6278,22 +6278,22 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
+        <v>236</v>
+      </c>
+      <c r="F160" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G160" s="8">
         <v>237</v>
       </c>
-      <c r="F160" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G160" s="8">
-        <v>238</v>
-      </c>
       <c t="s" r="H160" s="8">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c t="s" r="I160" s="7">
+        <v>239</v>
+      </c>
+      <c t="s" r="J160" s="7">
         <v>240</v>
-      </c>
-      <c t="s" r="J160" s="7">
-        <v>142</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6311,22 +6311,22 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
+        <v>236</v>
+      </c>
+      <c r="F161" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G161" s="8">
+        <v>228</v>
+      </c>
+      <c t="s" r="H161" s="8">
         <v>237</v>
-      </c>
-      <c r="F161" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G161" s="8">
-        <v>229</v>
-      </c>
-      <c t="s" r="H161" s="8">
-        <v>238</v>
       </c>
       <c t="s" r="I161" s="7">
         <v>241</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6344,19 +6344,19 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
+        <v>236</v>
+      </c>
+      <c r="F162" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G162" s="8">
         <v>237</v>
       </c>
-      <c r="F162" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G162" s="8">
-        <v>238</v>
-      </c>
       <c t="s" r="H162" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>220</v>
+        <v>144</v>
       </c>
       <c t="s" r="J162" s="7">
         <v>23</v>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6392,7 +6392,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6443,16 +6443,16 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
+        <v>236</v>
+      </c>
+      <c r="F165" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G165" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H165" s="8">
         <v>237</v>
-      </c>
-      <c r="F165" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G165" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H165" s="8">
-        <v>238</v>
       </c>
       <c t="s" r="I165" s="7">
         <v>243</v>
@@ -6476,13 +6476,13 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
+        <v>236</v>
+      </c>
+      <c r="F166" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G166" s="8">
         <v>237</v>
-      </c>
-      <c r="F166" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G166" s="8">
-        <v>238</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>16</v>
@@ -6491,7 +6491,7 @@
         <v>245</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6517,7 +6517,7 @@
         <v>13</v>
       </c>
       <c r="B168" s="7">
-        <v>771</v>
+        <v>138</v>
       </c>
       <c t="s" r="C168" s="7">
         <v>14</v>
@@ -6530,16 +6530,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>247</v>
+        <v>60</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6550,7 +6550,7 @@
         <v>13</v>
       </c>
       <c r="B169" s="7">
-        <v>770</v>
+        <v>147</v>
       </c>
       <c t="s" r="C169" s="7">
         <v>14</v>
@@ -6563,16 +6563,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6583,7 +6583,7 @@
         <v>13</v>
       </c>
       <c r="B170" s="7">
-        <v>787</v>
+        <v>154</v>
       </c>
       <c t="s" r="C170" s="7">
         <v>14</v>
@@ -6596,16 +6596,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>249</v>
+        <v>65</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>170</v>
+        <v>248</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6616,7 +6616,7 @@
         <v>13</v>
       </c>
       <c r="B171" s="7">
-        <v>774</v>
+        <v>163</v>
       </c>
       <c t="s" r="C171" s="7">
         <v>14</v>
@@ -6629,50 +6629,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>198</v>
+        <v>39</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c r="M171" s="7"/>
     </row>
     <row r="172" ht="14.25" customHeight="1">
-      <c t="s" r="A172" s="6">
-        <v>13</v>
-      </c>
-      <c r="B172" s="7">
-        <v>517</v>
-      </c>
-      <c t="s" r="C172" s="7">
-        <v>14</v>
-      </c>
+      <c r="A172" s="6"/>
+      <c r="B172" s="7"/>
+      <c r="C172" s="7"/>
       <c r="D172" s="7"/>
-      <c t="s" r="E172" s="7">
-        <v>246</v>
-      </c>
-      <c r="F172" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G172" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H172" s="8">
-        <v>49</v>
-      </c>
-      <c t="s" r="I172" s="7">
-        <v>28</v>
-      </c>
-      <c t="s" r="J172" s="7">
-        <v>250</v>
-      </c>
+      <c r="E172" s="7"/>
+      <c r="F172" s="7"/>
+      <c r="G172" s="8"/>
+      <c r="H172" s="8"/>
+      <c r="I172" s="7"/>
+      <c r="J172" s="7"/>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
       <c r="M172" s="7"/>
@@ -6682,45 +6664,63 @@
         <v>13</v>
       </c>
       <c r="B173" s="7">
-        <v>520</v>
+        <v>771</v>
       </c>
       <c t="s" r="C173" s="7">
         <v>14</v>
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>17</v>
+        <v>170</v>
       </c>
       <c t="s" r="I173" s="7">
         <v>251</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>252</v>
+        <v>76</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c r="M173" s="7"/>
     </row>
     <row r="174" ht="14.25" customHeight="1">
-      <c r="A174" s="6"/>
-      <c r="B174" s="7"/>
-      <c r="C174" s="7"/>
+      <c t="s" r="A174" s="6">
+        <v>13</v>
+      </c>
+      <c r="B174" s="7">
+        <v>770</v>
+      </c>
+      <c t="s" r="C174" s="7">
+        <v>14</v>
+      </c>
       <c r="D174" s="7"/>
-      <c r="E174" s="7"/>
-      <c r="F174" s="7"/>
-      <c r="G174" s="8"/>
-      <c r="H174" s="8"/>
-      <c r="I174" s="7"/>
-      <c r="J174" s="7"/>
+      <c t="s" r="E174" s="7">
+        <v>250</v>
+      </c>
+      <c r="F174" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G174" s="8">
+        <v>170</v>
+      </c>
+      <c t="s" r="H174" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I174" s="7">
+        <v>252</v>
+      </c>
+      <c t="s" r="J174" s="7">
+        <v>78</v>
+      </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c r="M174" s="7"/>
@@ -6730,29 +6730,29 @@
         <v>13</v>
       </c>
       <c r="B175" s="7">
-        <v>901</v>
+        <v>787</v>
       </c>
       <c t="s" r="C175" s="7">
         <v>14</v>
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
+        <v>250</v>
+      </c>
+      <c r="F175" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G175" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H175" s="8">
+        <v>170</v>
+      </c>
+      <c t="s" r="I175" s="7">
         <v>253</v>
       </c>
-      <c r="F175" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G175" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H175" s="8">
-        <v>254</v>
-      </c>
-      <c t="s" r="I175" s="7">
-        <v>220</v>
-      </c>
       <c t="s" r="J175" s="7">
-        <v>23</v>
+        <v>171</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6763,45 +6763,63 @@
         <v>13</v>
       </c>
       <c r="B176" s="7">
-        <v>902</v>
+        <v>774</v>
       </c>
       <c t="s" r="C176" s="7">
         <v>14</v>
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>254</v>
+        <v>170</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>126</v>
+        <v>199</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>184</v>
+        <v>222</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c r="M176" s="7"/>
     </row>
     <row r="177" ht="14.25" customHeight="1">
-      <c r="A177" s="6"/>
-      <c r="B177" s="7"/>
-      <c r="C177" s="7"/>
+      <c t="s" r="A177" s="6">
+        <v>13</v>
+      </c>
+      <c r="B177" s="7">
+        <v>517</v>
+      </c>
+      <c t="s" r="C177" s="7">
+        <v>14</v>
+      </c>
       <c r="D177" s="7"/>
-      <c r="E177" s="7"/>
-      <c r="F177" s="7"/>
-      <c r="G177" s="8"/>
-      <c r="H177" s="8"/>
-      <c r="I177" s="7"/>
-      <c r="J177" s="7"/>
+      <c t="s" r="E177" s="7">
+        <v>250</v>
+      </c>
+      <c r="F177" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G177" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H177" s="8">
+        <v>49</v>
+      </c>
+      <c t="s" r="I177" s="7">
+        <v>28</v>
+      </c>
+      <c t="s" r="J177" s="7">
+        <v>254</v>
+      </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c r="M177" s="7"/>
@@ -6811,63 +6829,45 @@
         <v>13</v>
       </c>
       <c r="B178" s="7">
-        <v>449</v>
+        <v>520</v>
       </c>
       <c t="s" r="C178" s="7">
         <v>14</v>
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
+        <v>250</v>
+      </c>
+      <c r="F178" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G178" s="8">
+        <v>49</v>
+      </c>
+      <c t="s" r="H178" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I178" s="7">
         <v>255</v>
       </c>
-      <c r="F178" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G178" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H178" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="I178" s="7">
-        <v>161</v>
-      </c>
       <c t="s" r="J178" s="7">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c r="M178" s="7"/>
     </row>
     <row r="179" ht="14.25" customHeight="1">
-      <c t="s" r="A179" s="6">
-        <v>13</v>
-      </c>
-      <c r="B179" s="7">
-        <v>450</v>
-      </c>
-      <c t="s" r="C179" s="7">
-        <v>14</v>
-      </c>
+      <c r="A179" s="6"/>
+      <c r="B179" s="7"/>
+      <c r="C179" s="7"/>
       <c r="D179" s="7"/>
-      <c t="s" r="E179" s="7">
-        <v>255</v>
-      </c>
-      <c r="F179" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G179" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="H179" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I179" s="7">
-        <v>118</v>
-      </c>
-      <c t="s" r="J179" s="7">
-        <v>257</v>
-      </c>
+      <c r="E179" s="7"/>
+      <c r="F179" s="7"/>
+      <c r="G179" s="8"/>
+      <c r="H179" s="8"/>
+      <c r="I179" s="7"/>
+      <c r="J179" s="7"/>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c r="M179" s="7"/>
@@ -6877,14 +6877,14 @@
         <v>13</v>
       </c>
       <c r="B180" s="7">
-        <v>775</v>
+        <v>449</v>
       </c>
       <c t="s" r="C180" s="7">
         <v>14</v>
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -6893,13 +6893,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>169</v>
+        <v>24</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>258</v>
+        <v>162</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>212</v>
+        <v>257</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -6910,29 +6910,29 @@
         <v>13</v>
       </c>
       <c r="B181" s="7">
-        <v>772</v>
+        <v>450</v>
       </c>
       <c t="s" r="C181" s="7">
         <v>14</v>
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>169</v>
+        <v>24</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>43</v>
+        <v>258</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -6943,14 +6943,14 @@
         <v>13</v>
       </c>
       <c r="B182" s="7">
-        <v>495</v>
+        <v>775</v>
       </c>
       <c t="s" r="C182" s="7">
         <v>14</v>
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -6959,13 +6959,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>229</v>
+        <v>170</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>192</v>
+        <v>259</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>259</v>
+        <v>213</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -6976,45 +6976,63 @@
         <v>13</v>
       </c>
       <c r="B183" s="7">
-        <v>496</v>
+        <v>772</v>
       </c>
       <c t="s" r="C183" s="7">
         <v>14</v>
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>229</v>
+        <v>170</v>
       </c>
       <c t="s" r="H183" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>260</v>
+        <v>43</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c r="M183" s="7"/>
     </row>
     <row r="184" ht="14.25" customHeight="1">
-      <c r="A184" s="6"/>
-      <c r="B184" s="7"/>
-      <c r="C184" s="7"/>
+      <c t="s" r="A184" s="6">
+        <v>13</v>
+      </c>
+      <c r="B184" s="7">
+        <v>495</v>
+      </c>
+      <c t="s" r="C184" s="7">
+        <v>14</v>
+      </c>
       <c r="D184" s="7"/>
-      <c r="E184" s="7"/>
-      <c r="F184" s="7"/>
-      <c r="G184" s="8"/>
-      <c r="H184" s="8"/>
-      <c r="I184" s="7"/>
-      <c r="J184" s="7"/>
+      <c t="s" r="E184" s="7">
+        <v>256</v>
+      </c>
+      <c r="F184" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G184" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H184" s="8">
+        <v>228</v>
+      </c>
+      <c t="s" r="I184" s="7">
+        <v>193</v>
+      </c>
+      <c t="s" r="J184" s="7">
+        <v>260</v>
+      </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c r="M184" s="7"/>
@@ -7024,63 +7042,45 @@
         <v>13</v>
       </c>
       <c r="B185" s="7">
-        <v>1491</v>
+        <v>496</v>
       </c>
       <c t="s" r="C185" s="7">
         <v>14</v>
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
+        <v>256</v>
+      </c>
+      <c r="F185" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G185" s="8">
+        <v>228</v>
+      </c>
+      <c t="s" r="H185" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I185" s="7">
+        <v>116</v>
+      </c>
+      <c t="s" r="J185" s="7">
         <v>261</v>
-      </c>
-      <c r="F185" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G185" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H185" s="8">
-        <v>229</v>
-      </c>
-      <c t="s" r="I185" s="7">
-        <v>99</v>
-      </c>
-      <c t="s" r="J185" s="7">
-        <v>112</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c r="M185" s="7"/>
     </row>
     <row r="186" ht="14.25" customHeight="1">
-      <c t="s" r="A186" s="6">
-        <v>13</v>
-      </c>
-      <c r="B186" s="7">
-        <v>1492</v>
-      </c>
-      <c t="s" r="C186" s="7">
-        <v>14</v>
-      </c>
+      <c r="A186" s="6"/>
+      <c r="B186" s="7"/>
+      <c r="C186" s="7"/>
       <c r="D186" s="7"/>
-      <c t="s" r="E186" s="7">
-        <v>261</v>
-      </c>
-      <c r="F186" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G186" s="8">
-        <v>229</v>
-      </c>
-      <c t="s" r="H186" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I186" s="7">
-        <v>87</v>
-      </c>
-      <c t="s" r="J186" s="7">
-        <v>145</v>
-      </c>
+      <c r="E186" s="7"/>
+      <c r="F186" s="7"/>
+      <c r="G186" s="8"/>
+      <c r="H186" s="8"/>
+      <c r="I186" s="7"/>
+      <c r="J186" s="7"/>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c r="M186" s="7"/>
@@ -7090,14 +7090,14 @@
         <v>13</v>
       </c>
       <c r="B187" s="7">
-        <v>405</v>
+        <v>1491</v>
       </c>
       <c t="s" r="C187" s="7">
         <v>14</v>
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7106,13 +7106,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>192</v>
+        <v>112</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7123,29 +7123,29 @@
         <v>13</v>
       </c>
       <c r="B188" s="7">
-        <v>406</v>
+        <v>1492</v>
       </c>
       <c t="s" r="C188" s="7">
         <v>14</v>
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c t="s" r="H188" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7153,17 +7153,17 @@
     </row>
     <row r="189" ht="14.25" customHeight="1">
       <c t="s" r="A189" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B189" s="7">
-        <v>958</v>
+        <v>405</v>
       </c>
       <c t="s" r="C189" s="7">
         <v>14</v>
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7172,95 +7172,95 @@
         <v>17</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>262</v>
+        <v>110</v>
       </c>
       <c t="s" r="I189" s="7">
         <v>181</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c r="M189" s="7"/>
     </row>
     <row r="190" ht="15" customHeight="1">
-      <c r="A190" s="6"/>
-      <c r="B190" s="7"/>
-      <c r="C190" s="7"/>
+      <c t="s" r="A190" s="6">
+        <v>13</v>
+      </c>
+      <c r="B190" s="7">
+        <v>406</v>
+      </c>
+      <c t="s" r="C190" s="7">
+        <v>14</v>
+      </c>
       <c r="D190" s="7"/>
-      <c r="E190" s="7"/>
-      <c r="F190" s="7"/>
-      <c r="G190" s="8"/>
-      <c r="H190" s="8"/>
-      <c r="I190" s="7"/>
-      <c r="J190" s="7"/>
+      <c t="s" r="E190" s="7">
+        <v>262</v>
+      </c>
+      <c r="F190" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G190" s="8">
+        <v>110</v>
+      </c>
+      <c t="s" r="H190" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I190" s="7">
+        <v>37</v>
+      </c>
+      <c t="s" r="J190" s="7">
+        <v>136</v>
+      </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c r="M190" s="7"/>
     </row>
     <row r="191" ht="14.25" customHeight="1">
       <c t="s" r="A191" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B191" s="7">
-        <v>120</v>
+        <v>958</v>
       </c>
       <c t="s" r="C191" s="7">
         <v>14</v>
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
+        <v>262</v>
+      </c>
+      <c r="F191" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G191" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H191" s="8">
         <v>263</v>
       </c>
-      <c r="F191" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G191" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H191" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I191" s="7">
-        <v>239</v>
+        <v>182</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c r="M191" s="7"/>
     </row>
     <row r="192" ht="14.25" customHeight="1">
-      <c t="s" r="A192" s="6">
-        <v>13</v>
-      </c>
-      <c r="B192" s="7">
-        <v>505</v>
-      </c>
-      <c t="s" r="C192" s="7">
-        <v>14</v>
-      </c>
+      <c r="A192" s="6"/>
+      <c r="B192" s="7"/>
+      <c r="C192" s="7"/>
       <c r="D192" s="7"/>
-      <c t="s" r="E192" s="7">
-        <v>263</v>
-      </c>
-      <c r="F192" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G192" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H192" s="8">
-        <v>49</v>
-      </c>
-      <c t="s" r="I192" s="7">
-        <v>196</v>
-      </c>
-      <c t="s" r="J192" s="7">
-        <v>111</v>
-      </c>
+      <c r="E192" s="7"/>
+      <c r="F192" s="7"/>
+      <c r="G192" s="8"/>
+      <c r="H192" s="8"/>
+      <c r="I192" s="7"/>
+      <c r="J192" s="7"/>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c r="M192" s="7"/>
@@ -7270,29 +7270,29 @@
         <v>13</v>
       </c>
       <c r="B193" s="7">
-        <v>506</v>
+        <v>120</v>
       </c>
       <c t="s" r="C193" s="7">
         <v>14</v>
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>143</v>
+        <v>238</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7303,14 +7303,14 @@
         <v>13</v>
       </c>
       <c r="B194" s="7">
-        <v>453</v>
+        <v>505</v>
       </c>
       <c t="s" r="C194" s="7">
         <v>14</v>
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7319,13 +7319,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7336,29 +7336,29 @@
         <v>13</v>
       </c>
       <c r="B195" s="7">
-        <v>456</v>
+        <v>506</v>
       </c>
       <c t="s" r="C195" s="7">
         <v>14</v>
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c t="s" r="H195" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7369,14 +7369,14 @@
         <v>13</v>
       </c>
       <c r="B196" s="7">
-        <v>521</v>
+        <v>453</v>
       </c>
       <c t="s" r="C196" s="7">
         <v>14</v>
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7385,13 +7385,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7402,45 +7402,63 @@
         <v>13</v>
       </c>
       <c r="B197" s="7">
-        <v>518</v>
+        <v>456</v>
       </c>
       <c t="s" r="C197" s="7">
         <v>14</v>
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>264</v>
+        <v>28</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c r="M197" s="7"/>
     </row>
     <row r="198" ht="14.25" customHeight="1">
-      <c r="A198" s="6"/>
-      <c r="B198" s="7"/>
-      <c r="C198" s="7"/>
+      <c t="s" r="A198" s="6">
+        <v>13</v>
+      </c>
+      <c r="B198" s="7">
+        <v>521</v>
+      </c>
+      <c t="s" r="C198" s="7">
+        <v>14</v>
+      </c>
       <c r="D198" s="7"/>
-      <c r="E198" s="7"/>
-      <c r="F198" s="7"/>
-      <c r="G198" s="8"/>
-      <c r="H198" s="8"/>
-      <c r="I198" s="7"/>
-      <c r="J198" s="7"/>
+      <c t="s" r="E198" s="7">
+        <v>264</v>
+      </c>
+      <c r="F198" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G198" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H198" s="8">
+        <v>49</v>
+      </c>
+      <c t="s" r="I198" s="7">
+        <v>65</v>
+      </c>
+      <c t="s" r="J198" s="7">
+        <v>54</v>
+      </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c r="M198" s="7"/>
@@ -7450,14 +7468,14 @@
         <v>13</v>
       </c>
       <c r="B199" s="7">
-        <v>621</v>
+        <v>518</v>
       </c>
       <c t="s" r="C199" s="7">
         <v>14</v>
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7466,47 +7484,29 @@
         <v>49</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>266</v>
+        <v>67</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c r="M199" s="7"/>
     </row>
     <row r="200" ht="15" customHeight="1">
-      <c t="s" r="A200" s="6">
-        <v>13</v>
-      </c>
-      <c r="B200" s="7">
-        <v>632</v>
-      </c>
-      <c t="s" r="C200" s="7">
-        <v>14</v>
-      </c>
+      <c r="A200" s="6"/>
+      <c r="B200" s="7"/>
+      <c r="C200" s="7"/>
       <c r="D200" s="7"/>
-      <c t="s" r="E200" s="7">
-        <v>265</v>
-      </c>
-      <c r="F200" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G200" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H200" s="8">
-        <v>49</v>
-      </c>
-      <c t="s" r="I200" s="7">
-        <v>31</v>
-      </c>
-      <c t="s" r="J200" s="7">
-        <v>77</v>
-      </c>
+      <c r="E200" s="7"/>
+      <c r="F200" s="7"/>
+      <c r="G200" s="8"/>
+      <c r="H200" s="8"/>
+      <c r="I200" s="7"/>
+      <c r="J200" s="7"/>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c r="M200" s="7"/>
@@ -7516,14 +7516,14 @@
         <v>13</v>
       </c>
       <c r="B201" s="7">
-        <v>703</v>
+        <v>621</v>
       </c>
       <c t="s" r="C201" s="7">
         <v>14</v>
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7532,13 +7532,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H201" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I201" s="7">
+        <v>267</v>
+      </c>
+      <c t="s" r="J201" s="7">
         <v>268</v>
-      </c>
-      <c t="s" r="I201" s="7">
-        <v>269</v>
-      </c>
-      <c t="s" r="J201" s="7">
-        <v>120</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7549,45 +7549,63 @@
         <v>13</v>
       </c>
       <c r="B202" s="7">
-        <v>704</v>
+        <v>632</v>
       </c>
       <c t="s" r="C202" s="7">
         <v>14</v>
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>268</v>
+        <v>16</v>
       </c>
       <c t="s" r="H202" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c r="M202" s="7"/>
     </row>
     <row r="203" ht="14.25" customHeight="1">
-      <c r="A203" s="6"/>
-      <c r="B203" s="7"/>
-      <c r="C203" s="7"/>
+      <c t="s" r="A203" s="6">
+        <v>13</v>
+      </c>
+      <c r="B203" s="7">
+        <v>703</v>
+      </c>
+      <c t="s" r="C203" s="7">
+        <v>14</v>
+      </c>
       <c r="D203" s="7"/>
-      <c r="E203" s="7"/>
-      <c r="F203" s="7"/>
-      <c r="G203" s="8"/>
-      <c r="H203" s="8"/>
-      <c r="I203" s="7"/>
-      <c r="J203" s="7"/>
+      <c t="s" r="E203" s="7">
+        <v>266</v>
+      </c>
+      <c r="F203" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G203" s="8">
+        <v>49</v>
+      </c>
+      <c t="s" r="H203" s="8">
+        <v>269</v>
+      </c>
+      <c t="s" r="I203" s="7">
+        <v>270</v>
+      </c>
+      <c t="s" r="J203" s="7">
+        <v>120</v>
+      </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c r="M203" s="7"/>
@@ -7597,63 +7615,45 @@
         <v>13</v>
       </c>
       <c r="B204" s="7">
-        <v>123</v>
+        <v>704</v>
       </c>
       <c t="s" r="C204" s="7">
         <v>14</v>
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>17</v>
+        <v>269</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>271</v>
+        <v>121</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>272</v>
+        <v>159</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c r="M204" s="7"/>
     </row>
     <row r="205" ht="15" customHeight="1">
-      <c t="s" r="A205" s="6">
-        <v>13</v>
-      </c>
-      <c r="B205" s="7">
-        <v>130</v>
-      </c>
-      <c t="s" r="C205" s="7">
-        <v>14</v>
-      </c>
+      <c r="A205" s="6"/>
+      <c r="B205" s="7"/>
+      <c r="C205" s="7"/>
       <c r="D205" s="7"/>
-      <c t="s" r="E205" s="7">
-        <v>270</v>
-      </c>
-      <c r="F205" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G205" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H205" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I205" s="7">
-        <v>164</v>
-      </c>
-      <c t="s" r="J205" s="7">
-        <v>119</v>
-      </c>
+      <c r="E205" s="7"/>
+      <c r="F205" s="7"/>
+      <c r="G205" s="8"/>
+      <c r="H205" s="8"/>
+      <c r="I205" s="7"/>
+      <c r="J205" s="7"/>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c r="M205" s="7"/>
@@ -7663,14 +7663,14 @@
         <v>13</v>
       </c>
       <c r="B206" s="7">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c t="s" r="C206" s="7">
         <v>14</v>
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7682,10 +7682,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>79</v>
+        <v>272</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>36</v>
+        <v>273</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7696,14 +7696,14 @@
         <v>13</v>
       </c>
       <c r="B207" s="7">
-        <v>327</v>
+        <v>130</v>
       </c>
       <c t="s" r="C207" s="7">
         <v>14</v>
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7712,13 +7712,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>184</v>
+        <v>119</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7729,29 +7729,29 @@
         <v>13</v>
       </c>
       <c r="B208" s="7">
-        <v>326</v>
+        <v>133</v>
       </c>
       <c t="s" r="C208" s="7">
         <v>14</v>
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7762,14 +7762,14 @@
         <v>13</v>
       </c>
       <c r="B209" s="7">
-        <v>642</v>
+        <v>327</v>
       </c>
       <c t="s" r="C209" s="7">
         <v>14</v>
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7778,29 +7778,47 @@
         <v>16</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c r="M209" s="7"/>
     </row>
     <row r="210" ht="15" customHeight="1">
-      <c r="A210" s="6"/>
-      <c r="B210" s="7"/>
-      <c r="C210" s="7"/>
+      <c t="s" r="A210" s="6">
+        <v>13</v>
+      </c>
+      <c r="B210" s="7">
+        <v>326</v>
+      </c>
+      <c t="s" r="C210" s="7">
+        <v>14</v>
+      </c>
       <c r="D210" s="7"/>
-      <c r="E210" s="7"/>
-      <c r="F210" s="7"/>
-      <c r="G210" s="8"/>
-      <c r="H210" s="8"/>
-      <c r="I210" s="7"/>
-      <c r="J210" s="7"/>
+      <c t="s" r="E210" s="7">
+        <v>271</v>
+      </c>
+      <c r="F210" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G210" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H210" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I210" s="7">
+        <v>44</v>
+      </c>
+      <c t="s" r="J210" s="7">
+        <v>193</v>
+      </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c r="M210" s="7"/>
@@ -7810,14 +7828,14 @@
         <v>13</v>
       </c>
       <c r="B211" s="7">
-        <v>270</v>
+        <v>642</v>
       </c>
       <c t="s" r="C211" s="7">
         <v>14</v>
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7826,47 +7844,29 @@
         <v>16</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>271</v>
+        <v>104</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>31</v>
+        <v>136</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c r="M211" s="7"/>
     </row>
     <row r="212" ht="14.25" customHeight="1">
-      <c t="s" r="A212" s="6">
-        <v>13</v>
-      </c>
-      <c r="B212" s="7">
-        <v>271</v>
-      </c>
-      <c t="s" r="C212" s="7">
-        <v>14</v>
-      </c>
+      <c r="A212" s="6"/>
+      <c r="B212" s="7"/>
+      <c r="C212" s="7"/>
       <c r="D212" s="7"/>
-      <c t="s" r="E212" s="7">
-        <v>273</v>
-      </c>
-      <c r="F212" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G212" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="H212" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I212" s="7">
-        <v>138</v>
-      </c>
-      <c t="s" r="J212" s="7">
-        <v>274</v>
-      </c>
+      <c r="E212" s="7"/>
+      <c r="F212" s="7"/>
+      <c r="G212" s="8"/>
+      <c r="H212" s="8"/>
+      <c r="I212" s="7"/>
+      <c r="J212" s="7"/>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c r="M212" s="7"/>
@@ -7876,14 +7876,14 @@
         <v>13</v>
       </c>
       <c r="B213" s="7">
-        <v>634</v>
+        <v>272</v>
       </c>
       <c t="s" r="C213" s="7">
         <v>14</v>
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -7892,10 +7892,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>86</v>
+        <v>191</v>
       </c>
       <c t="s" r="J213" s="7">
         <v>275</v>
@@ -7909,29 +7909,29 @@
         <v>13</v>
       </c>
       <c r="B214" s="7">
-        <v>973</v>
+        <v>693</v>
       </c>
       <c t="s" r="C214" s="7">
         <v>14</v>
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>232</v>
+        <v>110</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>249</v>
+        <v>52</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>276</v>
+        <v>115</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -7942,111 +7942,111 @@
         <v>13</v>
       </c>
       <c r="B215" s="7">
-        <v>814</v>
+        <v>692</v>
       </c>
       <c t="s" r="C215" s="7">
         <v>14</v>
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>232</v>
+        <v>110</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>115</v>
+        <v>45</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>38</v>
+        <v>235</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c r="M215" s="7"/>
     </row>
     <row r="216" ht="14.25" customHeight="1">
-      <c t="s" r="A216" s="6">
-        <v>13</v>
-      </c>
-      <c r="B216" s="7">
-        <v>3908</v>
-      </c>
-      <c t="s" r="C216" s="7">
-        <v>14</v>
-      </c>
+      <c r="A216" s="6"/>
+      <c r="B216" s="7"/>
+      <c r="C216" s="7"/>
       <c r="D216" s="7"/>
-      <c t="s" r="E216" s="7">
-        <v>273</v>
-      </c>
-      <c r="F216" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G216" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H216" s="8">
-        <v>224</v>
-      </c>
-      <c t="s" r="I216" s="7">
-        <v>149</v>
-      </c>
-      <c t="s" r="J216" s="7">
-        <v>277</v>
-      </c>
+      <c r="E216" s="7"/>
+      <c r="F216" s="7"/>
+      <c r="G216" s="8"/>
+      <c r="H216" s="8"/>
+      <c r="I216" s="7"/>
+      <c r="J216" s="7"/>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c r="M216" s="7"/>
     </row>
     <row r="217" ht="14.25" customHeight="1">
       <c t="s" r="A217" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B217" s="7">
-        <v>3909</v>
+        <v>961</v>
       </c>
       <c t="s" r="C217" s="7">
         <v>14</v>
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>224</v>
+        <v>27</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>279</v>
+        <v>213</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c r="M217" s="7"/>
     </row>
     <row r="218" ht="14.25" customHeight="1">
-      <c r="A218" s="6"/>
-      <c r="B218" s="7"/>
-      <c r="C218" s="7"/>
+      <c t="s" r="A218" s="6">
+        <v>13</v>
+      </c>
+      <c r="B218" s="7">
+        <v>946</v>
+      </c>
+      <c t="s" r="C218" s="7">
+        <v>14</v>
+      </c>
       <c r="D218" s="7"/>
-      <c r="E218" s="7"/>
-      <c r="F218" s="7"/>
-      <c r="G218" s="8"/>
-      <c r="H218" s="8"/>
-      <c r="I218" s="7"/>
-      <c r="J218" s="7"/>
+      <c t="s" r="E218" s="7">
+        <v>276</v>
+      </c>
+      <c r="F218" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G218" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H218" s="8">
+        <v>278</v>
+      </c>
+      <c t="s" r="I218" s="7">
+        <v>127</v>
+      </c>
+      <c t="s" r="J218" s="7">
+        <v>201</v>
+      </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c r="M218" s="7"/>
@@ -8056,29 +8056,29 @@
         <v>13</v>
       </c>
       <c r="B219" s="7">
-        <v>961</v>
+        <v>947</v>
       </c>
       <c t="s" r="C219" s="7">
         <v>14</v>
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>27</v>
+        <v>278</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>281</v>
+        <v>92</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8089,14 +8089,14 @@
         <v>13</v>
       </c>
       <c r="B220" s="7">
-        <v>946</v>
+        <v>962</v>
       </c>
       <c t="s" r="C220" s="7">
         <v>14</v>
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8105,47 +8105,29 @@
         <v>17</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>282</v>
+        <v>27</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>127</v>
+        <v>279</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>200</v>
+        <v>272</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c r="M220" s="7"/>
     </row>
     <row r="221" ht="14.25" customHeight="1">
-      <c t="s" r="A221" s="6">
-        <v>13</v>
-      </c>
-      <c r="B221" s="7">
-        <v>947</v>
-      </c>
-      <c t="s" r="C221" s="7">
-        <v>14</v>
-      </c>
+      <c r="A221" s="6"/>
+      <c r="B221" s="7"/>
+      <c r="C221" s="7"/>
       <c r="D221" s="7"/>
-      <c t="s" r="E221" s="7">
-        <v>280</v>
-      </c>
-      <c r="F221" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G221" s="8">
-        <v>282</v>
-      </c>
-      <c t="s" r="H221" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I221" s="7">
-        <v>92</v>
-      </c>
-      <c t="s" r="J221" s="7">
-        <v>185</v>
-      </c>
+      <c r="E221" s="7"/>
+      <c r="F221" s="7"/>
+      <c r="G221" s="8"/>
+      <c r="H221" s="8"/>
+      <c r="I221" s="7"/>
+      <c r="J221" s="7"/>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c r="M221" s="7"/>
@@ -8155,7 +8137,7 @@
         <v>13</v>
       </c>
       <c r="B222" s="7">
-        <v>962</v>
+        <v>823</v>
       </c>
       <c t="s" r="C222" s="7">
         <v>14</v>
@@ -8168,65 +8150,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>283</v>
+        <v>210</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c r="M222" s="7"/>
     </row>
     <row r="223" ht="14.25" customHeight="1">
-      <c r="A223" s="6"/>
-      <c r="B223" s="7"/>
-      <c r="C223" s="7"/>
+      <c t="s" r="A223" s="6">
+        <v>13</v>
+      </c>
+      <c r="B223" s="7">
+        <v>822</v>
+      </c>
+      <c t="s" r="C223" s="7">
+        <v>14</v>
+      </c>
       <c r="D223" s="7"/>
-      <c r="E223" s="7"/>
-      <c r="F223" s="7"/>
-      <c r="G223" s="8"/>
-      <c r="H223" s="8"/>
-      <c r="I223" s="7"/>
-      <c r="J223" s="7"/>
+      <c t="s" r="E223" s="7">
+        <v>280</v>
+      </c>
+      <c r="F223" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G223" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H223" s="8">
+        <v>59</v>
+      </c>
+      <c t="s" r="I223" s="7">
+        <v>249</v>
+      </c>
+      <c t="s" r="J223" s="7">
+        <v>71</v>
+      </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c r="M223" s="7"/>
     </row>
     <row r="224" ht="14.25" customHeight="1">
-      <c t="s" r="A224" s="6">
-        <v>13</v>
-      </c>
-      <c r="B224" s="7">
-        <v>823</v>
-      </c>
-      <c t="s" r="C224" s="7">
-        <v>14</v>
-      </c>
+      <c r="A224" s="6"/>
+      <c r="B224" s="7"/>
+      <c r="C224" s="7"/>
       <c r="D224" s="7"/>
-      <c t="s" r="E224" s="7">
-        <v>284</v>
-      </c>
-      <c r="F224" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G224" s="8">
-        <v>59</v>
-      </c>
-      <c t="s" r="H224" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I224" s="7">
-        <v>210</v>
-      </c>
-      <c t="s" r="J224" s="7">
-        <v>228</v>
-      </c>
+      <c r="E224" s="7"/>
+      <c r="F224" s="7"/>
+      <c r="G224" s="8"/>
+      <c r="H224" s="8"/>
+      <c r="I224" s="7"/>
+      <c r="J224" s="7"/>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c r="M224" s="7"/>
@@ -8236,14 +8218,14 @@
         <v>13</v>
       </c>
       <c r="B225" s="7">
-        <v>822</v>
+        <v>1242</v>
       </c>
       <c t="s" r="C225" s="7">
         <v>14</v>
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8252,29 +8234,47 @@
         <v>16</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>285</v>
+        <v>190</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c r="M225" s="7"/>
     </row>
     <row r="226" ht="14.25" customHeight="1">
-      <c r="A226" s="6"/>
-      <c r="B226" s="7"/>
-      <c r="C226" s="7"/>
+      <c t="s" r="A226" s="6">
+        <v>13</v>
+      </c>
+      <c r="B226" s="7">
+        <v>1241</v>
+      </c>
+      <c t="s" r="C226" s="7">
+        <v>14</v>
+      </c>
       <c r="D226" s="7"/>
-      <c r="E226" s="7"/>
-      <c r="F226" s="7"/>
-      <c r="G226" s="8"/>
-      <c r="H226" s="8"/>
-      <c r="I226" s="7"/>
-      <c r="J226" s="7"/>
+      <c t="s" r="E226" s="7">
+        <v>281</v>
+      </c>
+      <c r="F226" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G226" s="8">
+        <v>85</v>
+      </c>
+      <c t="s" r="H226" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I226" s="7">
+        <v>133</v>
+      </c>
+      <c t="s" r="J226" s="7">
+        <v>79</v>
+      </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c r="M226" s="7"/>
@@ -8284,14 +8284,14 @@
         <v>13</v>
       </c>
       <c r="B227" s="7">
-        <v>272</v>
+        <v>807</v>
       </c>
       <c t="s" r="C227" s="7">
         <v>14</v>
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8300,13 +8300,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>41</v>
+        <v>282</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>190</v>
+        <v>88</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8317,29 +8317,29 @@
         <v>13</v>
       </c>
       <c r="B228" s="7">
-        <v>693</v>
+        <v>800</v>
       </c>
       <c t="s" r="C228" s="7">
         <v>14</v>
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>41</v>
+        <v>282</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>52</v>
+        <v>247</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>115</v>
+        <v>222</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8350,78 +8350,78 @@
         <v>13</v>
       </c>
       <c r="B229" s="7">
-        <v>692</v>
+        <v>3900</v>
       </c>
       <c t="s" r="C229" s="7">
         <v>14</v>
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>41</v>
+        <v>284</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>45</v>
+        <v>285</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>236</v>
+        <v>209</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c r="M229" s="7"/>
     </row>
     <row r="230" ht="15" customHeight="1">
-      <c r="A230" s="6"/>
-      <c r="B230" s="7"/>
-      <c r="C230" s="7"/>
+      <c t="s" r="A230" s="6">
+        <v>46</v>
+      </c>
+      <c r="B230" s="7">
+        <v>3901</v>
+      </c>
+      <c t="s" r="C230" s="7">
+        <v>14</v>
+      </c>
       <c r="D230" s="7"/>
-      <c r="E230" s="7"/>
-      <c r="F230" s="7"/>
-      <c r="G230" s="8"/>
-      <c r="H230" s="8"/>
-      <c r="I230" s="7"/>
-      <c r="J230" s="7"/>
+      <c t="s" r="E230" s="7">
+        <v>281</v>
+      </c>
+      <c r="F230" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G230" s="8">
+        <v>284</v>
+      </c>
+      <c t="s" r="H230" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I230" s="7">
+        <v>286</v>
+      </c>
+      <c t="s" r="J230" s="7">
+        <v>287</v>
+      </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c r="M230" s="7"/>
     </row>
     <row r="231" ht="14.25" customHeight="1">
-      <c t="s" r="A231" s="6">
-        <v>13</v>
-      </c>
-      <c r="B231" s="7">
-        <v>925</v>
-      </c>
-      <c t="s" r="C231" s="7">
-        <v>14</v>
-      </c>
+      <c r="A231" s="6"/>
+      <c r="B231" s="7"/>
+      <c r="C231" s="7"/>
       <c r="D231" s="7"/>
-      <c t="s" r="E231" s="7">
-        <v>288</v>
-      </c>
-      <c r="F231" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G231" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H231" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I231" s="7">
-        <v>289</v>
-      </c>
-      <c t="s" r="J231" s="7">
-        <v>78</v>
-      </c>
+      <c r="E231" s="7"/>
+      <c r="F231" s="7"/>
+      <c r="G231" s="8"/>
+      <c r="H231" s="8"/>
+      <c r="I231" s="7"/>
+      <c r="J231" s="7"/>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c r="M231" s="7"/>
@@ -8431,7 +8431,7 @@
         <v>13</v>
       </c>
       <c r="B232" s="7">
-        <v>273</v>
+        <v>925</v>
       </c>
       <c t="s" r="C232" s="7">
         <v>14</v>
@@ -8444,16 +8444,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H232" s="8">
         <v>41</v>
       </c>
-      <c t="s" r="H232" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I232" s="7">
-        <v>258</v>
+        <v>289</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>290</v>
+        <v>78</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8464,7 +8464,7 @@
         <v>13</v>
       </c>
       <c r="B233" s="7">
-        <v>214</v>
+        <v>273</v>
       </c>
       <c t="s" r="C233" s="7">
         <v>14</v>
@@ -8477,16 +8477,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>238</v>
+        <v>16</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>199</v>
+        <v>290</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8497,7 +8497,7 @@
         <v>13</v>
       </c>
       <c r="B234" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="C234" s="7">
         <v>14</v>
@@ -8510,65 +8510,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>238</v>
+        <v>16</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>16</v>
+        <v>237</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>73</v>
+        <v>232</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c r="M234" s="7"/>
     </row>
     <row r="235" ht="15" customHeight="1">
-      <c r="A235" s="6"/>
-      <c r="B235" s="7"/>
-      <c r="C235" s="7"/>
+      <c t="s" r="A235" s="6">
+        <v>13</v>
+      </c>
+      <c r="B235" s="7">
+        <v>213</v>
+      </c>
+      <c t="s" r="C235" s="7">
+        <v>14</v>
+      </c>
       <c r="D235" s="7"/>
-      <c r="E235" s="7"/>
-      <c r="F235" s="7"/>
-      <c r="G235" s="8"/>
-      <c r="H235" s="8"/>
-      <c r="I235" s="7"/>
-      <c r="J235" s="7"/>
+      <c t="s" r="E235" s="7">
+        <v>288</v>
+      </c>
+      <c r="F235" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G235" s="8">
+        <v>237</v>
+      </c>
+      <c t="s" r="H235" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I235" s="7">
+        <v>73</v>
+      </c>
+      <c t="s" r="J235" s="7">
+        <v>166</v>
+      </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c r="M235" s="7"/>
     </row>
     <row r="236" ht="14.25" customHeight="1">
-      <c t="s" r="A236" s="6">
-        <v>13</v>
-      </c>
-      <c r="B236" s="7">
-        <v>1242</v>
-      </c>
-      <c t="s" r="C236" s="7">
-        <v>14</v>
-      </c>
+      <c r="A236" s="6"/>
+      <c r="B236" s="7"/>
+      <c r="C236" s="7"/>
       <c r="D236" s="7"/>
-      <c t="s" r="E236" s="7">
-        <v>291</v>
-      </c>
-      <c r="F236" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G236" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H236" s="8">
-        <v>85</v>
-      </c>
-      <c t="s" r="I236" s="7">
-        <v>189</v>
-      </c>
-      <c t="s" r="J236" s="7">
-        <v>77</v>
-      </c>
+      <c r="E236" s="7"/>
+      <c r="F236" s="7"/>
+      <c r="G236" s="8"/>
+      <c r="H236" s="8"/>
+      <c r="I236" s="7"/>
+      <c r="J236" s="7"/>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c r="M236" s="7"/>
@@ -8578,7 +8578,7 @@
         <v>13</v>
       </c>
       <c r="B237" s="7">
-        <v>1241</v>
+        <v>270</v>
       </c>
       <c t="s" r="C237" s="7">
         <v>14</v>
@@ -8591,16 +8591,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>133</v>
+        <v>272</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8611,7 +8611,7 @@
         <v>13</v>
       </c>
       <c r="B238" s="7">
-        <v>807</v>
+        <v>271</v>
       </c>
       <c t="s" r="C238" s="7">
         <v>14</v>
@@ -8624,13 +8624,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>292</v>
@@ -8644,7 +8644,7 @@
         <v>13</v>
       </c>
       <c r="B239" s="7">
-        <v>800</v>
+        <v>634</v>
       </c>
       <c t="s" r="C239" s="7">
         <v>14</v>
@@ -8657,16 +8657,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c t="s" r="I239" s="7">
+        <v>86</v>
+      </c>
+      <c t="s" r="J239" s="7">
         <v>293</v>
-      </c>
-      <c t="s" r="J239" s="7">
-        <v>223</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8677,7 +8677,7 @@
         <v>13</v>
       </c>
       <c r="B240" s="7">
-        <v>3900</v>
+        <v>973</v>
       </c>
       <c t="s" r="C240" s="7">
         <v>14</v>
@@ -8690,16 +8690,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c t="s" r="H240" s="8">
+        <v>231</v>
+      </c>
+      <c t="s" r="I240" s="7">
+        <v>253</v>
+      </c>
+      <c t="s" r="J240" s="7">
         <v>294</v>
-      </c>
-      <c t="s" r="I240" s="7">
-        <v>295</v>
-      </c>
-      <c t="s" r="J240" s="7">
-        <v>209</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8707,10 +8707,10 @@
     </row>
     <row r="241" ht="14.25" customHeight="1">
       <c t="s" r="A241" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B241" s="7">
-        <v>3901</v>
+        <v>814</v>
       </c>
       <c t="s" r="C241" s="7">
         <v>14</v>
@@ -8723,98 +8723,98 @@
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>294</v>
+        <v>231</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>296</v>
+        <v>115</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>297</v>
+        <v>38</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c r="M241" s="7"/>
     </row>
     <row r="242" ht="14.25" customHeight="1">
-      <c r="A242" s="6"/>
-      <c r="B242" s="7"/>
-      <c r="C242" s="7"/>
+      <c t="s" r="A242" s="6">
+        <v>13</v>
+      </c>
+      <c r="B242" s="7">
+        <v>3908</v>
+      </c>
+      <c t="s" r="C242" s="7">
+        <v>14</v>
+      </c>
       <c r="D242" s="7"/>
-      <c r="E242" s="7"/>
-      <c r="F242" s="7"/>
-      <c r="G242" s="8"/>
-      <c r="H242" s="8"/>
-      <c r="I242" s="7"/>
-      <c r="J242" s="7"/>
+      <c t="s" r="E242" s="7">
+        <v>291</v>
+      </c>
+      <c r="F242" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G242" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H242" s="8">
+        <v>223</v>
+      </c>
+      <c t="s" r="I242" s="7">
+        <v>150</v>
+      </c>
+      <c t="s" r="J242" s="7">
+        <v>295</v>
+      </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c r="M242" s="7"/>
     </row>
     <row r="243" ht="14.25" customHeight="1">
       <c t="s" r="A243" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B243" s="7">
-        <v>382</v>
+        <v>3909</v>
       </c>
       <c t="s" r="C243" s="7">
         <v>14</v>
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>16</v>
+        <v>223</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>222</v>
+        <v>16</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>204</v>
+        <v>296</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c r="M243" s="7"/>
     </row>
     <row r="244" ht="14.25" customHeight="1">
-      <c t="s" r="A244" s="6">
-        <v>13</v>
-      </c>
-      <c r="B244" s="7">
-        <v>383</v>
-      </c>
-      <c t="s" r="C244" s="7">
-        <v>14</v>
-      </c>
+      <c r="A244" s="6"/>
+      <c r="B244" s="7"/>
+      <c r="C244" s="7"/>
       <c r="D244" s="7"/>
-      <c t="s" r="E244" s="7">
-        <v>298</v>
-      </c>
-      <c r="F244" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G244" s="8">
-        <v>222</v>
-      </c>
-      <c t="s" r="H244" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I244" s="7">
-        <v>300</v>
-      </c>
-      <c t="s" r="J244" s="7">
-        <v>220</v>
-      </c>
+      <c r="E244" s="7"/>
+      <c r="F244" s="7"/>
+      <c r="G244" s="8"/>
+      <c r="H244" s="8"/>
+      <c r="I244" s="7"/>
+      <c r="J244" s="7"/>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c r="M244" s="7"/>
@@ -8824,7 +8824,7 @@
         <v>13</v>
       </c>
       <c r="B245" s="7">
-        <v>138</v>
+        <v>901</v>
       </c>
       <c t="s" r="C245" s="7">
         <v>14</v>
@@ -8837,16 +8837,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>17</v>
+        <v>282</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -8857,7 +8857,7 @@
         <v>13</v>
       </c>
       <c r="B246" s="7">
-        <v>147</v>
+        <v>902</v>
       </c>
       <c t="s" r="C246" s="7">
         <v>14</v>
@@ -8870,50 +8870,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>17</v>
+        <v>282</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>293</v>
+        <v>126</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c r="M246" s="7"/>
     </row>
     <row r="247" ht="14.25" customHeight="1">
-      <c t="s" r="A247" s="6">
-        <v>13</v>
-      </c>
-      <c r="B247" s="7">
-        <v>154</v>
-      </c>
-      <c t="s" r="C247" s="7">
-        <v>14</v>
-      </c>
+      <c r="A247" s="6"/>
+      <c r="B247" s="7"/>
+      <c r="C247" s="7"/>
       <c r="D247" s="7"/>
-      <c t="s" r="E247" s="7">
-        <v>298</v>
-      </c>
-      <c r="F247" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G247" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H247" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I247" s="7">
-        <v>65</v>
-      </c>
-      <c t="s" r="J247" s="7">
-        <v>252</v>
-      </c>
+      <c r="E247" s="7"/>
+      <c r="F247" s="7"/>
+      <c r="G247" s="8"/>
+      <c r="H247" s="8"/>
+      <c r="I247" s="7"/>
+      <c r="J247" s="7"/>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c r="M247" s="7"/>
@@ -8923,45 +8905,63 @@
         <v>13</v>
       </c>
       <c r="B248" s="7">
-        <v>163</v>
+        <v>825</v>
       </c>
       <c t="s" r="C248" s="7">
         <v>14</v>
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>16</v>
+        <v>300</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c r="M248" s="7"/>
     </row>
     <row r="249" ht="14.25" customHeight="1">
-      <c r="A249" s="6"/>
-      <c r="B249" s="7"/>
-      <c r="C249" s="7"/>
+      <c t="s" r="A249" s="6">
+        <v>13</v>
+      </c>
+      <c r="B249" s="7">
+        <v>826</v>
+      </c>
+      <c t="s" r="C249" s="7">
+        <v>14</v>
+      </c>
       <c r="D249" s="7"/>
-      <c r="E249" s="7"/>
-      <c r="F249" s="7"/>
-      <c r="G249" s="8"/>
-      <c r="H249" s="8"/>
-      <c r="I249" s="7"/>
-      <c r="J249" s="7"/>
+      <c t="s" r="E249" s="7">
+        <v>299</v>
+      </c>
+      <c r="F249" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G249" s="8">
+        <v>300</v>
+      </c>
+      <c t="s" r="H249" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I249" s="7">
+        <v>213</v>
+      </c>
+      <c t="s" r="J249" s="7">
+        <v>113</v>
+      </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c r="M249" s="7"/>
@@ -8971,14 +8971,14 @@
         <v>13</v>
       </c>
       <c r="B250" s="7">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c t="s" r="C250" s="7">
         <v>14</v>
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -8990,10 +8990,10 @@
         <v>302</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>303</v>
+        <v>209</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9001,17 +9001,17 @@
     </row>
     <row r="251" ht="14.25" customHeight="1">
       <c t="s" r="A251" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B251" s="7">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c t="s" r="C251" s="7">
         <v>14</v>
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9023,92 +9023,92 @@
         <v>16</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>212</v>
+        <v>303</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>113</v>
+        <v>304</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c r="M251" s="7"/>
     </row>
     <row r="252" ht="14.25" customHeight="1">
-      <c t="s" r="A252" s="6">
-        <v>13</v>
-      </c>
-      <c r="B252" s="7">
-        <v>820</v>
-      </c>
-      <c t="s" r="C252" s="7">
-        <v>14</v>
-      </c>
+      <c r="A252" s="6"/>
+      <c r="B252" s="7"/>
+      <c r="C252" s="7"/>
       <c r="D252" s="7"/>
-      <c t="s" r="E252" s="7">
-        <v>301</v>
-      </c>
-      <c r="F252" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G252" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H252" s="8">
-        <v>304</v>
-      </c>
-      <c t="s" r="I252" s="7">
-        <v>73</v>
-      </c>
-      <c t="s" r="J252" s="7">
-        <v>209</v>
-      </c>
+      <c r="E252" s="7"/>
+      <c r="F252" s="7"/>
+      <c r="G252" s="8"/>
+      <c r="H252" s="8"/>
+      <c r="I252" s="7"/>
+      <c r="J252" s="7"/>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c r="M252" s="7"/>
     </row>
     <row r="253" ht="14.25" customHeight="1">
       <c t="s" r="A253" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B253" s="7">
-        <v>821</v>
+        <v>463</v>
       </c>
       <c t="s" r="C253" s="7">
         <v>14</v>
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F253" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>304</v>
+        <v>17</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>16</v>
+        <v>269</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>306</v>
+        <v>221</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c r="M253" s="7"/>
     </row>
     <row r="254" ht="14.25" customHeight="1">
-      <c r="A254" s="6"/>
-      <c r="B254" s="7"/>
-      <c r="C254" s="7"/>
+      <c t="s" r="A254" s="6">
+        <v>13</v>
+      </c>
+      <c r="B254" s="7">
+        <v>464</v>
+      </c>
+      <c t="s" r="C254" s="7">
+        <v>14</v>
+      </c>
       <c r="D254" s="7"/>
-      <c r="E254" s="7"/>
-      <c r="F254" s="7"/>
-      <c r="G254" s="8"/>
-      <c r="H254" s="8"/>
-      <c r="I254" s="7"/>
-      <c r="J254" s="7"/>
+      <c t="s" r="E254" s="7">
+        <v>305</v>
+      </c>
+      <c r="F254" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G254" s="8">
+        <v>269</v>
+      </c>
+      <c t="s" r="H254" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I254" s="7">
+        <v>23</v>
+      </c>
+      <c t="s" r="J254" s="7">
+        <v>102</v>
+      </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c r="M254" s="7"/>
@@ -9118,14 +9118,14 @@
         <v>13</v>
       </c>
       <c r="B255" s="7">
-        <v>463</v>
+        <v>567</v>
       </c>
       <c t="s" r="C255" s="7">
         <v>14</v>
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F255" s="7">
         <v>320</v>
@@ -9134,13 +9134,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>268</v>
+        <v>98</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>308</v>
+        <v>43</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>221</v>
+        <v>64</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9151,29 +9151,29 @@
         <v>13</v>
       </c>
       <c r="B256" s="7">
-        <v>464</v>
+        <v>568</v>
       </c>
       <c t="s" r="C256" s="7">
         <v>14</v>
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F256" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>268</v>
+        <v>98</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>23</v>
+        <v>233</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9184,14 +9184,14 @@
         <v>13</v>
       </c>
       <c r="B257" s="7">
-        <v>567</v>
+        <v>7238</v>
       </c>
       <c t="s" r="C257" s="7">
         <v>14</v>
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F257" s="7">
         <v>320</v>
@@ -9200,13 +9200,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>98</v>
+        <v>284</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>64</v>
+        <v>307</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9214,114 +9214,114 @@
     </row>
     <row r="258" ht="14.25" customHeight="1">
       <c t="s" r="A258" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B258" s="7">
-        <v>568</v>
+        <v>7239</v>
       </c>
       <c t="s" r="C258" s="7">
         <v>14</v>
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F258" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>98</v>
+        <v>284</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>234</v>
+        <v>308</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>83</v>
+        <v>309</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c r="M258" s="7"/>
     </row>
     <row r="259" ht="14.25" customHeight="1">
-      <c t="s" r="A259" s="6">
-        <v>13</v>
-      </c>
-      <c r="B259" s="7">
-        <v>7238</v>
-      </c>
-      <c t="s" r="C259" s="7">
-        <v>14</v>
-      </c>
+      <c r="A259" s="6"/>
+      <c r="B259" s="7"/>
+      <c r="C259" s="7"/>
       <c r="D259" s="7"/>
-      <c t="s" r="E259" s="7">
-        <v>307</v>
-      </c>
-      <c r="F259" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G259" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H259" s="8">
-        <v>294</v>
-      </c>
-      <c t="s" r="I259" s="7">
-        <v>68</v>
-      </c>
-      <c t="s" r="J259" s="7">
-        <v>309</v>
-      </c>
+      <c r="E259" s="7"/>
+      <c r="F259" s="7"/>
+      <c r="G259" s="8"/>
+      <c r="H259" s="8"/>
+      <c r="I259" s="7"/>
+      <c r="J259" s="7"/>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c r="M259" s="7"/>
     </row>
     <row r="260" ht="15" customHeight="1">
       <c t="s" r="A260" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B260" s="7">
-        <v>7239</v>
+        <v>124</v>
       </c>
       <c t="s" r="C260" s="7">
         <v>14</v>
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F260" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>294</v>
+        <v>16</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c r="M260" s="7"/>
     </row>
     <row r="261" ht="14.25" customHeight="1">
-      <c r="A261" s="6"/>
-      <c r="B261" s="7"/>
-      <c r="C261" s="7"/>
+      <c t="s" r="A261" s="6">
+        <v>13</v>
+      </c>
+      <c r="B261" s="7">
+        <v>129</v>
+      </c>
+      <c t="s" r="C261" s="7">
+        <v>14</v>
+      </c>
       <c r="D261" s="7"/>
-      <c r="E261" s="7"/>
-      <c r="F261" s="7"/>
-      <c r="G261" s="8"/>
-      <c r="H261" s="8"/>
-      <c r="I261" s="7"/>
-      <c r="J261" s="7"/>
+      <c t="s" r="E261" s="7">
+        <v>310</v>
+      </c>
+      <c r="F261" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G261" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H261" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I261" s="7">
+        <v>240</v>
+      </c>
+      <c t="s" r="J261" s="7">
+        <v>212</v>
+      </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c r="M261" s="7"/>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9383,10 +9383,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9431,7 +9431,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>18</v>
@@ -9467,7 +9467,7 @@
         <v>221</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9530,7 +9530,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>315</v>
@@ -9575,7 +9575,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c t="s" r="I270" s="7">
         <v>57</v>
@@ -9605,16 +9605,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9680,7 +9680,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9725,7 +9725,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>142</v>
+        <v>240</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>119</v>
@@ -9794,7 +9794,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9860,7 +9860,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -9908,7 +9908,7 @@
         <v>321</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10004,7 +10004,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>34</v>
@@ -10073,7 +10073,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10148,10 +10148,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>89</v>
@@ -10178,13 +10178,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>293</v>
+        <v>247</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>325</v>
@@ -10250,10 +10250,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10301,7 +10301,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>142</v>
+        <v>240</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10364,7 +10364,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>42</v>
@@ -10433,7 +10433,7 @@
         <v>329</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10463,7 +10463,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>330</v>
@@ -10508,7 +10508,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c t="s" r="I301" s="7">
         <v>332</v>
@@ -10538,7 +10538,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>17</v>
@@ -10547,7 +10547,7 @@
         <v>221</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10688,13 +10688,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>300</v>
+        <v>143</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10718,7 +10718,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c t="s" r="H308" s="8">
         <v>16</v>
@@ -10790,10 +10790,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -10859,7 +10859,7 @@
         <v>334</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -10901,13 +10901,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>299</v>
+        <v>142</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -10931,7 +10931,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>41</v>
@@ -10967,13 +10967,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -10997,7 +10997,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>27</v>
@@ -11006,7 +11006,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11048,10 +11048,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J319" s="7">
         <v>210</v>
@@ -11078,7 +11078,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H320" s="8">
         <v>17</v>
@@ -11117,7 +11117,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>63</v>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -11232,13 +11232,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>222</v>
+        <v>140</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11262,7 +11262,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>222</v>
+        <v>140</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>16</v>
@@ -11337,7 +11337,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11367,10 +11367,10 @@
         <v>326</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11400,7 +11400,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>341</v>
@@ -11430,7 +11430,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>222</v>
+        <v>140</v>
       </c>
       <c t="s" r="I331" s="7">
         <v>114</v>
@@ -11460,13 +11460,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>222</v>
+        <v>140</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J332" s="7">
         <v>105</v>
@@ -11502,7 +11502,7 @@
         <v>342</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11580,10 +11580,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>220</v>
+        <v>144</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11613,7 +11613,7 @@
         <v>110</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c t="s" r="J337" s="7">
         <v>121</v>
@@ -11646,10 +11646,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11676,10 +11676,10 @@
         <v>49</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>93</v>
@@ -11706,7 +11706,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>49</v>
@@ -11745,7 +11745,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>346</v>
@@ -11793,10 +11793,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11943,7 +11943,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12042,7 +12042,7 @@
         <v>136</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12072,7 +12072,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>29</v>
@@ -12123,7 +12123,7 @@
         <v>352</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12219,7 +12219,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>28</v>
@@ -12330,7 +12330,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c t="s" r="I361" s="7">
         <v>111</v>
@@ -12360,13 +12360,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="J362" s="7">
         <v>89</v>
@@ -12402,7 +12402,7 @@
         <v>63</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12546,7 +12546,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>118</v>
@@ -12681,7 +12681,7 @@
         <v>314</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12756,13 +12756,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>142</v>
+        <v>240</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12786,7 +12786,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>16</v>
@@ -12858,7 +12858,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>285</v>
+        <v>249</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>346</v>
@@ -12903,10 +12903,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>299</v>
+        <v>142</v>
       </c>
       <c t="s" r="J380" s="7">
         <v>221</v>
@@ -12933,7 +12933,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>16</v>
@@ -12972,10 +12972,10 @@
         <v>363</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13041,7 +13041,7 @@
         <v>209</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13089,7 +13089,7 @@
         <v>352</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13122,7 +13122,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13155,7 +13155,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13221,7 +13221,7 @@
         <v>367</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13293,7 +13293,7 @@
         <v>330</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>16</v>
@@ -13302,7 +13302,7 @@
         <v>138</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13365,7 +13365,7 @@
         <v>371</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>372</v>
@@ -13401,7 +13401,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>204</v>
+        <v>141</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13440,7 +13440,7 @@
         <v>330</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>16</v>
@@ -13449,7 +13449,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>142</v>
+        <v>240</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13560,7 +13560,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>71</v>
@@ -13577,7 +13577,7 @@
         <v>2866</v>
       </c>
       <c t="s" r="C403" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
@@ -13610,7 +13610,7 @@
         <v>2867</v>
       </c>
       <c t="s" r="C404" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
@@ -13674,7 +13674,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J406" s="7">
         <v>341</v>
@@ -13707,7 +13707,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>136</v>
@@ -13740,7 +13740,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>379</v>
@@ -13785,13 +13785,13 @@
         <v>381</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -13887,7 +13887,7 @@
         <v>317</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -13920,7 +13920,7 @@
         <v>385</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>

--- a/Data/FlightPlan/FPL_07OCT26.xlsx
+++ b/Data/FlightPlan/FPL_07OCT26.xlsx
@@ -704,6 +704,129 @@
     <t>VN-A634</t>
   </si>
   <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
     <t>SIN</t>
   </si>
   <si>
@@ -716,129 +839,6 @@
     <t>19:40</t>
   </si>
   <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
     <t>VN-A645</t>
   </si>
   <si>
@@ -1172,7 +1172,7 @@
     <t>Total Record(s): 337</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 07, 2026 00:01</t>
+    <t xml:space="preserve">Generated on  Oct 07, 2026 00:15</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -6091,7 +6091,7 @@
         <v>13</v>
       </c>
       <c r="B154" s="7">
-        <v>887</v>
+        <v>272</v>
       </c>
       <c t="s" r="C154" s="7">
         <v>14</v>
@@ -6107,13 +6107,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H154" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I154" s="7">
+        <v>191</v>
+      </c>
+      <c t="s" r="J154" s="7">
         <v>231</v>
-      </c>
-      <c t="s" r="I154" s="7">
-        <v>144</v>
-      </c>
-      <c t="s" r="J154" s="7">
-        <v>232</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6124,7 +6124,7 @@
         <v>13</v>
       </c>
       <c r="B155" s="7">
-        <v>882</v>
+        <v>693</v>
       </c>
       <c t="s" r="C155" s="7">
         <v>14</v>
@@ -6137,16 +6137,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>231</v>
+        <v>41</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>199</v>
+        <v>52</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6157,7 +6157,7 @@
         <v>13</v>
       </c>
       <c r="B156" s="7">
-        <v>282</v>
+        <v>692</v>
       </c>
       <c t="s" r="C156" s="7">
         <v>14</v>
@@ -6170,65 +6170,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>233</v>
+        <v>45</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
       <c r="M156" s="7"/>
     </row>
     <row r="157" ht="14.25" customHeight="1">
-      <c t="s" r="A157" s="6">
-        <v>13</v>
-      </c>
-      <c r="B157" s="7">
-        <v>283</v>
-      </c>
-      <c t="s" r="C157" s="7">
-        <v>14</v>
-      </c>
+      <c r="A157" s="6"/>
+      <c r="B157" s="7"/>
+      <c r="C157" s="7"/>
       <c r="D157" s="7"/>
-      <c t="s" r="E157" s="7">
-        <v>230</v>
-      </c>
-      <c r="F157" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G157" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="H157" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I157" s="7">
-        <v>235</v>
-      </c>
-      <c t="s" r="J157" s="7">
-        <v>167</v>
-      </c>
+      <c r="E157" s="7"/>
+      <c r="F157" s="7"/>
+      <c r="G157" s="8"/>
+      <c r="H157" s="8"/>
+      <c r="I157" s="7"/>
+      <c r="J157" s="7"/>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c r="M157" s="7"/>
     </row>
     <row r="158" ht="14.25" customHeight="1">
-      <c r="A158" s="6"/>
-      <c r="B158" s="7"/>
-      <c r="C158" s="7"/>
+      <c t="s" r="A158" s="6">
+        <v>13</v>
+      </c>
+      <c r="B158" s="7">
+        <v>224</v>
+      </c>
+      <c t="s" r="C158" s="7">
+        <v>14</v>
+      </c>
       <c r="D158" s="7"/>
-      <c r="E158" s="7"/>
-      <c r="F158" s="7"/>
-      <c r="G158" s="8"/>
-      <c r="H158" s="8"/>
-      <c r="I158" s="7"/>
-      <c r="J158" s="7"/>
+      <c t="s" r="E158" s="7">
+        <v>233</v>
+      </c>
+      <c r="F158" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G158" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H158" s="8">
+        <v>234</v>
+      </c>
+      <c t="s" r="I158" s="7">
+        <v>235</v>
+      </c>
+      <c t="s" r="J158" s="7">
+        <v>190</v>
+      </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c r="M158" s="7"/>
@@ -6238,29 +6238,29 @@
         <v>13</v>
       </c>
       <c r="B159" s="7">
-        <v>224</v>
+        <v>741</v>
       </c>
       <c t="s" r="C159" s="7">
         <v>14</v>
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
+        <v>233</v>
+      </c>
+      <c r="F159" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G159" s="8">
+        <v>234</v>
+      </c>
+      <c t="s" r="H159" s="8">
+        <v>228</v>
+      </c>
+      <c t="s" r="I159" s="7">
         <v>236</v>
       </c>
-      <c r="F159" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G159" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H159" s="8">
+      <c t="s" r="J159" s="7">
         <v>237</v>
-      </c>
-      <c t="s" r="I159" s="7">
-        <v>238</v>
-      </c>
-      <c t="s" r="J159" s="7">
-        <v>190</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6271,29 +6271,29 @@
         <v>13</v>
       </c>
       <c r="B160" s="7">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c t="s" r="C160" s="7">
         <v>14</v>
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6304,29 +6304,29 @@
         <v>13</v>
       </c>
       <c r="B161" s="7">
-        <v>740</v>
+        <v>227</v>
       </c>
       <c t="s" r="C161" s="7">
         <v>14</v>
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>237</v>
+        <v>16</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>241</v>
+        <v>144</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>220</v>
+        <v>23</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6337,29 +6337,29 @@
         <v>13</v>
       </c>
       <c r="B162" s="7">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c t="s" r="C162" s="7">
         <v>14</v>
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>237</v>
+        <v>16</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>144</v>
+        <v>51</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>23</v>
+        <v>181</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6370,29 +6370,29 @@
         <v>13</v>
       </c>
       <c r="B163" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="C163" s="7">
         <v>14</v>
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>181</v>
+        <v>239</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6403,29 +6403,29 @@
         <v>13</v>
       </c>
       <c r="B164" s="7">
-        <v>253</v>
+        <v>216</v>
       </c>
       <c t="s" r="C164" s="7">
         <v>14</v>
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>16</v>
+        <v>234</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>52</v>
+        <v>240</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6436,78 +6436,78 @@
         <v>13</v>
       </c>
       <c r="B165" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="C165" s="7">
         <v>14</v>
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>16</v>
+        <v>234</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>237</v>
+        <v>16</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>244</v>
+        <v>161</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c r="M165" s="7"/>
     </row>
     <row r="166" ht="14.25" customHeight="1">
-      <c t="s" r="A166" s="6">
-        <v>13</v>
-      </c>
-      <c r="B166" s="7">
-        <v>217</v>
-      </c>
-      <c t="s" r="C166" s="7">
-        <v>14</v>
-      </c>
+      <c r="A166" s="6"/>
+      <c r="B166" s="7"/>
+      <c r="C166" s="7"/>
       <c r="D166" s="7"/>
-      <c t="s" r="E166" s="7">
-        <v>236</v>
-      </c>
-      <c r="F166" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G166" s="8">
-        <v>237</v>
-      </c>
-      <c t="s" r="H166" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I166" s="7">
-        <v>245</v>
-      </c>
-      <c t="s" r="J166" s="7">
-        <v>161</v>
-      </c>
+      <c r="E166" s="7"/>
+      <c r="F166" s="7"/>
+      <c r="G166" s="8"/>
+      <c r="H166" s="8"/>
+      <c r="I166" s="7"/>
+      <c r="J166" s="7"/>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c r="M166" s="7"/>
     </row>
     <row r="167" ht="14.25" customHeight="1">
-      <c r="A167" s="6"/>
-      <c r="B167" s="7"/>
-      <c r="C167" s="7"/>
+      <c t="s" r="A167" s="6">
+        <v>13</v>
+      </c>
+      <c r="B167" s="7">
+        <v>138</v>
+      </c>
+      <c t="s" r="C167" s="7">
+        <v>14</v>
+      </c>
       <c r="D167" s="7"/>
-      <c r="E167" s="7"/>
-      <c r="F167" s="7"/>
-      <c r="G167" s="8"/>
-      <c r="H167" s="8"/>
-      <c r="I167" s="7"/>
-      <c r="J167" s="7"/>
+      <c t="s" r="E167" s="7">
+        <v>243</v>
+      </c>
+      <c r="F167" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G167" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H167" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I167" s="7">
+        <v>60</v>
+      </c>
+      <c t="s" r="J167" s="7">
+        <v>89</v>
+      </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c r="M167" s="7"/>
@@ -6517,29 +6517,29 @@
         <v>13</v>
       </c>
       <c r="B168" s="7">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c t="s" r="C168" s="7">
         <v>14</v>
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>60</v>
+        <v>244</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6550,29 +6550,29 @@
         <v>13</v>
       </c>
       <c r="B169" s="7">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c t="s" r="C169" s="7">
         <v>14</v>
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>247</v>
+        <v>65</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>115</v>
+        <v>245</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6583,78 +6583,78 @@
         <v>13</v>
       </c>
       <c r="B170" s="7">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c t="s" r="C170" s="7">
         <v>14</v>
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
+        <v>243</v>
+      </c>
+      <c r="F170" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G170" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H170" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I170" s="7">
+        <v>39</v>
+      </c>
+      <c t="s" r="J170" s="7">
         <v>246</v>
-      </c>
-      <c r="F170" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G170" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H170" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I170" s="7">
-        <v>65</v>
-      </c>
-      <c t="s" r="J170" s="7">
-        <v>248</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c r="M170" s="7"/>
     </row>
     <row r="171" ht="14.25" customHeight="1">
-      <c t="s" r="A171" s="6">
-        <v>13</v>
-      </c>
-      <c r="B171" s="7">
-        <v>163</v>
-      </c>
-      <c t="s" r="C171" s="7">
-        <v>14</v>
-      </c>
+      <c r="A171" s="6"/>
+      <c r="B171" s="7"/>
+      <c r="C171" s="7"/>
       <c r="D171" s="7"/>
-      <c t="s" r="E171" s="7">
-        <v>246</v>
-      </c>
-      <c r="F171" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G171" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H171" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I171" s="7">
-        <v>39</v>
-      </c>
-      <c t="s" r="J171" s="7">
-        <v>249</v>
-      </c>
+      <c r="E171" s="7"/>
+      <c r="F171" s="7"/>
+      <c r="G171" s="8"/>
+      <c r="H171" s="8"/>
+      <c r="I171" s="7"/>
+      <c r="J171" s="7"/>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c r="M171" s="7"/>
     </row>
     <row r="172" ht="14.25" customHeight="1">
-      <c r="A172" s="6"/>
-      <c r="B172" s="7"/>
-      <c r="C172" s="7"/>
+      <c t="s" r="A172" s="6">
+        <v>13</v>
+      </c>
+      <c r="B172" s="7">
+        <v>771</v>
+      </c>
+      <c t="s" r="C172" s="7">
+        <v>14</v>
+      </c>
       <c r="D172" s="7"/>
-      <c r="E172" s="7"/>
-      <c r="F172" s="7"/>
-      <c r="G172" s="8"/>
-      <c r="H172" s="8"/>
-      <c r="I172" s="7"/>
-      <c r="J172" s="7"/>
+      <c t="s" r="E172" s="7">
+        <v>247</v>
+      </c>
+      <c r="F172" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G172" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H172" s="8">
+        <v>170</v>
+      </c>
+      <c t="s" r="I172" s="7">
+        <v>248</v>
+      </c>
+      <c t="s" r="J172" s="7">
+        <v>76</v>
+      </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
       <c r="M172" s="7"/>
@@ -6664,29 +6664,29 @@
         <v>13</v>
       </c>
       <c r="B173" s="7">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c t="s" r="C173" s="7">
         <v>14</v>
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>17</v>
+        <v>170</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>170</v>
+        <v>17</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6697,29 +6697,29 @@
         <v>13</v>
       </c>
       <c r="B174" s="7">
-        <v>770</v>
+        <v>787</v>
       </c>
       <c t="s" r="C174" s="7">
         <v>14</v>
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
+        <v>247</v>
+      </c>
+      <c r="F174" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G174" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H174" s="8">
+        <v>170</v>
+      </c>
+      <c t="s" r="I174" s="7">
         <v>250</v>
       </c>
-      <c r="F174" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G174" s="8">
-        <v>170</v>
-      </c>
-      <c t="s" r="H174" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I174" s="7">
-        <v>252</v>
-      </c>
       <c t="s" r="J174" s="7">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6730,29 +6730,29 @@
         <v>13</v>
       </c>
       <c r="B175" s="7">
-        <v>787</v>
+        <v>774</v>
       </c>
       <c t="s" r="C175" s="7">
         <v>14</v>
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>17</v>
+        <v>170</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>170</v>
+        <v>17</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>253</v>
+        <v>199</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>171</v>
+        <v>222</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6763,29 +6763,29 @@
         <v>13</v>
       </c>
       <c r="B176" s="7">
-        <v>774</v>
+        <v>517</v>
       </c>
       <c t="s" r="C176" s="7">
         <v>14</v>
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>170</v>
+        <v>17</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>199</v>
+        <v>28</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6796,78 +6796,78 @@
         <v>13</v>
       </c>
       <c r="B177" s="7">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c t="s" r="C177" s="7">
         <v>14</v>
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>28</v>
+        <v>252</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c r="M177" s="7"/>
     </row>
     <row r="178" ht="14.25" customHeight="1">
-      <c t="s" r="A178" s="6">
-        <v>13</v>
-      </c>
-      <c r="B178" s="7">
-        <v>520</v>
-      </c>
-      <c t="s" r="C178" s="7">
-        <v>14</v>
-      </c>
+      <c r="A178" s="6"/>
+      <c r="B178" s="7"/>
+      <c r="C178" s="7"/>
       <c r="D178" s="7"/>
-      <c t="s" r="E178" s="7">
-        <v>250</v>
-      </c>
-      <c r="F178" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G178" s="8">
-        <v>49</v>
-      </c>
-      <c t="s" r="H178" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I178" s="7">
-        <v>255</v>
-      </c>
-      <c t="s" r="J178" s="7">
-        <v>248</v>
-      </c>
+      <c r="E178" s="7"/>
+      <c r="F178" s="7"/>
+      <c r="G178" s="8"/>
+      <c r="H178" s="8"/>
+      <c r="I178" s="7"/>
+      <c r="J178" s="7"/>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c r="M178" s="7"/>
     </row>
     <row r="179" ht="14.25" customHeight="1">
-      <c r="A179" s="6"/>
-      <c r="B179" s="7"/>
-      <c r="C179" s="7"/>
+      <c t="s" r="A179" s="6">
+        <v>13</v>
+      </c>
+      <c r="B179" s="7">
+        <v>449</v>
+      </c>
+      <c t="s" r="C179" s="7">
+        <v>14</v>
+      </c>
       <c r="D179" s="7"/>
-      <c r="E179" s="7"/>
-      <c r="F179" s="7"/>
-      <c r="G179" s="8"/>
-      <c r="H179" s="8"/>
-      <c r="I179" s="7"/>
-      <c r="J179" s="7"/>
+      <c t="s" r="E179" s="7">
+        <v>253</v>
+      </c>
+      <c r="F179" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G179" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H179" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="I179" s="7">
+        <v>162</v>
+      </c>
+      <c t="s" r="J179" s="7">
+        <v>254</v>
+      </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c r="M179" s="7"/>
@@ -6877,29 +6877,29 @@
         <v>13</v>
       </c>
       <c r="B180" s="7">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c t="s" r="C180" s="7">
         <v>14</v>
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -6910,29 +6910,29 @@
         <v>13</v>
       </c>
       <c r="B181" s="7">
-        <v>450</v>
+        <v>775</v>
       </c>
       <c t="s" r="C181" s="7">
         <v>14</v>
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
+        <v>253</v>
+      </c>
+      <c r="F181" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G181" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H181" s="8">
+        <v>170</v>
+      </c>
+      <c t="s" r="I181" s="7">
         <v>256</v>
       </c>
-      <c r="F181" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G181" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="H181" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I181" s="7">
-        <v>118</v>
-      </c>
       <c t="s" r="J181" s="7">
-        <v>258</v>
+        <v>213</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -6943,29 +6943,29 @@
         <v>13</v>
       </c>
       <c r="B182" s="7">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c t="s" r="C182" s="7">
         <v>14</v>
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>17</v>
+        <v>170</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>170</v>
+        <v>17</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>259</v>
+        <v>80</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>213</v>
+        <v>43</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -6976,29 +6976,29 @@
         <v>13</v>
       </c>
       <c r="B183" s="7">
-        <v>772</v>
+        <v>495</v>
       </c>
       <c t="s" r="C183" s="7">
         <v>14</v>
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>170</v>
+        <v>17</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>43</v>
+        <v>257</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7009,78 +7009,78 @@
         <v>13</v>
       </c>
       <c r="B184" s="7">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c t="s" r="C184" s="7">
         <v>14</v>
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>228</v>
+        <v>17</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>193</v>
+        <v>116</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c r="M184" s="7"/>
     </row>
     <row r="185" ht="15" customHeight="1">
-      <c t="s" r="A185" s="6">
-        <v>13</v>
-      </c>
-      <c r="B185" s="7">
-        <v>496</v>
-      </c>
-      <c t="s" r="C185" s="7">
-        <v>14</v>
-      </c>
+      <c r="A185" s="6"/>
+      <c r="B185" s="7"/>
+      <c r="C185" s="7"/>
       <c r="D185" s="7"/>
-      <c t="s" r="E185" s="7">
-        <v>256</v>
-      </c>
-      <c r="F185" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G185" s="8">
-        <v>228</v>
-      </c>
-      <c t="s" r="H185" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I185" s="7">
-        <v>116</v>
-      </c>
-      <c t="s" r="J185" s="7">
-        <v>261</v>
-      </c>
+      <c r="E185" s="7"/>
+      <c r="F185" s="7"/>
+      <c r="G185" s="8"/>
+      <c r="H185" s="8"/>
+      <c r="I185" s="7"/>
+      <c r="J185" s="7"/>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c r="M185" s="7"/>
     </row>
     <row r="186" ht="14.25" customHeight="1">
-      <c r="A186" s="6"/>
-      <c r="B186" s="7"/>
-      <c r="C186" s="7"/>
+      <c t="s" r="A186" s="6">
+        <v>13</v>
+      </c>
+      <c r="B186" s="7">
+        <v>1491</v>
+      </c>
+      <c t="s" r="C186" s="7">
+        <v>14</v>
+      </c>
       <c r="D186" s="7"/>
-      <c r="E186" s="7"/>
-      <c r="F186" s="7"/>
-      <c r="G186" s="8"/>
-      <c r="H186" s="8"/>
-      <c r="I186" s="7"/>
-      <c r="J186" s="7"/>
+      <c t="s" r="E186" s="7">
+        <v>259</v>
+      </c>
+      <c r="F186" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G186" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H186" s="8">
+        <v>228</v>
+      </c>
+      <c t="s" r="I186" s="7">
+        <v>99</v>
+      </c>
+      <c t="s" r="J186" s="7">
+        <v>112</v>
+      </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c r="M186" s="7"/>
@@ -7090,29 +7090,29 @@
         <v>13</v>
       </c>
       <c r="B187" s="7">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c t="s" r="C187" s="7">
         <v>14</v>
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>228</v>
+        <v>17</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7123,29 +7123,29 @@
         <v>13</v>
       </c>
       <c r="B188" s="7">
-        <v>1492</v>
+        <v>405</v>
       </c>
       <c t="s" r="C188" s="7">
         <v>14</v>
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>228</v>
+        <v>17</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>17</v>
+        <v>110</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>87</v>
+        <v>181</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7156,29 +7156,29 @@
         <v>13</v>
       </c>
       <c r="B189" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c t="s" r="C189" s="7">
         <v>14</v>
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>17</v>
+        <v>110</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>110</v>
+        <v>17</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>181</v>
+        <v>37</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7186,81 +7186,81 @@
     </row>
     <row r="190" ht="15" customHeight="1">
       <c t="s" r="A190" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B190" s="7">
-        <v>406</v>
+        <v>958</v>
       </c>
       <c t="s" r="C190" s="7">
         <v>14</v>
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>110</v>
+        <v>17</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>17</v>
+        <v>260</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>136</v>
+        <v>71</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c r="M190" s="7"/>
     </row>
     <row r="191" ht="14.25" customHeight="1">
-      <c t="s" r="A191" s="6">
-        <v>46</v>
-      </c>
-      <c r="B191" s="7">
-        <v>958</v>
-      </c>
-      <c t="s" r="C191" s="7">
-        <v>14</v>
-      </c>
+      <c r="A191" s="6"/>
+      <c r="B191" s="7"/>
+      <c r="C191" s="7"/>
       <c r="D191" s="7"/>
-      <c t="s" r="E191" s="7">
-        <v>262</v>
-      </c>
-      <c r="F191" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G191" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H191" s="8">
-        <v>263</v>
-      </c>
-      <c t="s" r="I191" s="7">
-        <v>182</v>
-      </c>
-      <c t="s" r="J191" s="7">
-        <v>71</v>
-      </c>
+      <c r="E191" s="7"/>
+      <c r="F191" s="7"/>
+      <c r="G191" s="8"/>
+      <c r="H191" s="8"/>
+      <c r="I191" s="7"/>
+      <c r="J191" s="7"/>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c r="M191" s="7"/>
     </row>
     <row r="192" ht="14.25" customHeight="1">
-      <c r="A192" s="6"/>
-      <c r="B192" s="7"/>
-      <c r="C192" s="7"/>
+      <c t="s" r="A192" s="6">
+        <v>13</v>
+      </c>
+      <c r="B192" s="7">
+        <v>120</v>
+      </c>
+      <c t="s" r="C192" s="7">
+        <v>14</v>
+      </c>
       <c r="D192" s="7"/>
-      <c r="E192" s="7"/>
-      <c r="F192" s="7"/>
-      <c r="G192" s="8"/>
-      <c r="H192" s="8"/>
-      <c r="I192" s="7"/>
-      <c r="J192" s="7"/>
+      <c t="s" r="E192" s="7">
+        <v>261</v>
+      </c>
+      <c r="F192" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G192" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H192" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I192" s="7">
+        <v>235</v>
+      </c>
+      <c t="s" r="J192" s="7">
+        <v>57</v>
+      </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c r="M192" s="7"/>
@@ -7270,29 +7270,29 @@
         <v>13</v>
       </c>
       <c r="B193" s="7">
-        <v>120</v>
+        <v>505</v>
       </c>
       <c t="s" r="C193" s="7">
         <v>14</v>
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>238</v>
+        <v>197</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7303,29 +7303,29 @@
         <v>13</v>
       </c>
       <c r="B194" s="7">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c t="s" r="C194" s="7">
         <v>14</v>
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7336,29 +7336,29 @@
         <v>13</v>
       </c>
       <c r="B195" s="7">
-        <v>506</v>
+        <v>453</v>
       </c>
       <c t="s" r="C195" s="7">
         <v>14</v>
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>212</v>
+        <v>23</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7369,29 +7369,29 @@
         <v>13</v>
       </c>
       <c r="B196" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c t="s" r="C196" s="7">
         <v>14</v>
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>23</v>
+        <v>181</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7402,29 +7402,29 @@
         <v>13</v>
       </c>
       <c r="B197" s="7">
-        <v>456</v>
+        <v>521</v>
       </c>
       <c t="s" r="C197" s="7">
         <v>14</v>
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>181</v>
+        <v>65</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7435,78 +7435,78 @@
         <v>13</v>
       </c>
       <c r="B198" s="7">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c t="s" r="C198" s="7">
         <v>14</v>
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>54</v>
+        <v>262</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c r="M198" s="7"/>
     </row>
     <row r="199" ht="14.25" customHeight="1">
-      <c t="s" r="A199" s="6">
-        <v>13</v>
-      </c>
-      <c r="B199" s="7">
-        <v>518</v>
-      </c>
-      <c t="s" r="C199" s="7">
-        <v>14</v>
-      </c>
+      <c r="A199" s="6"/>
+      <c r="B199" s="7"/>
+      <c r="C199" s="7"/>
       <c r="D199" s="7"/>
-      <c t="s" r="E199" s="7">
-        <v>264</v>
-      </c>
-      <c r="F199" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G199" s="8">
-        <v>49</v>
-      </c>
-      <c t="s" r="H199" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I199" s="7">
-        <v>67</v>
-      </c>
-      <c t="s" r="J199" s="7">
-        <v>265</v>
-      </c>
+      <c r="E199" s="7"/>
+      <c r="F199" s="7"/>
+      <c r="G199" s="8"/>
+      <c r="H199" s="8"/>
+      <c r="I199" s="7"/>
+      <c r="J199" s="7"/>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c r="M199" s="7"/>
     </row>
     <row r="200" ht="15" customHeight="1">
-      <c r="A200" s="6"/>
-      <c r="B200" s="7"/>
-      <c r="C200" s="7"/>
+      <c t="s" r="A200" s="6">
+        <v>13</v>
+      </c>
+      <c r="B200" s="7">
+        <v>621</v>
+      </c>
+      <c t="s" r="C200" s="7">
+        <v>14</v>
+      </c>
       <c r="D200" s="7"/>
-      <c r="E200" s="7"/>
-      <c r="F200" s="7"/>
-      <c r="G200" s="8"/>
-      <c r="H200" s="8"/>
-      <c r="I200" s="7"/>
-      <c r="J200" s="7"/>
+      <c t="s" r="E200" s="7">
+        <v>263</v>
+      </c>
+      <c r="F200" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G200" s="8">
+        <v>49</v>
+      </c>
+      <c t="s" r="H200" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I200" s="7">
+        <v>264</v>
+      </c>
+      <c t="s" r="J200" s="7">
+        <v>265</v>
+      </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c r="M200" s="7"/>
@@ -7516,29 +7516,29 @@
         <v>13</v>
       </c>
       <c r="B201" s="7">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c t="s" r="C201" s="7">
         <v>14</v>
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H201" s="8">
         <v>49</v>
       </c>
-      <c t="s" r="H201" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I201" s="7">
-        <v>267</v>
+        <v>31</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>268</v>
+        <v>77</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7549,29 +7549,29 @@
         <v>13</v>
       </c>
       <c r="B202" s="7">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c t="s" r="C202" s="7">
         <v>14</v>
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
+        <v>263</v>
+      </c>
+      <c r="F202" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G202" s="8">
+        <v>49</v>
+      </c>
+      <c t="s" r="H202" s="8">
         <v>266</v>
       </c>
-      <c r="F202" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G202" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H202" s="8">
-        <v>49</v>
-      </c>
       <c t="s" r="I202" s="7">
-        <v>31</v>
+        <v>267</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7582,78 +7582,78 @@
         <v>13</v>
       </c>
       <c r="B203" s="7">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c t="s" r="C203" s="7">
         <v>14</v>
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
+        <v>263</v>
+      </c>
+      <c r="F203" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G203" s="8">
         <v>266</v>
       </c>
-      <c r="F203" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G203" s="8">
+      <c t="s" r="H203" s="8">
         <v>49</v>
       </c>
-      <c t="s" r="H203" s="8">
-        <v>269</v>
-      </c>
       <c t="s" r="I203" s="7">
-        <v>270</v>
+        <v>121</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c r="M203" s="7"/>
     </row>
     <row r="204" ht="14.25" customHeight="1">
-      <c t="s" r="A204" s="6">
-        <v>13</v>
-      </c>
-      <c r="B204" s="7">
-        <v>704</v>
-      </c>
-      <c t="s" r="C204" s="7">
-        <v>14</v>
-      </c>
+      <c r="A204" s="6"/>
+      <c r="B204" s="7"/>
+      <c r="C204" s="7"/>
       <c r="D204" s="7"/>
-      <c t="s" r="E204" s="7">
-        <v>266</v>
-      </c>
-      <c r="F204" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G204" s="8">
-        <v>269</v>
-      </c>
-      <c t="s" r="H204" s="8">
-        <v>49</v>
-      </c>
-      <c t="s" r="I204" s="7">
-        <v>121</v>
-      </c>
-      <c t="s" r="J204" s="7">
-        <v>159</v>
-      </c>
+      <c r="E204" s="7"/>
+      <c r="F204" s="7"/>
+      <c r="G204" s="8"/>
+      <c r="H204" s="8"/>
+      <c r="I204" s="7"/>
+      <c r="J204" s="7"/>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c r="M204" s="7"/>
     </row>
     <row r="205" ht="15" customHeight="1">
-      <c r="A205" s="6"/>
-      <c r="B205" s="7"/>
-      <c r="C205" s="7"/>
+      <c t="s" r="A205" s="6">
+        <v>13</v>
+      </c>
+      <c r="B205" s="7">
+        <v>123</v>
+      </c>
+      <c t="s" r="C205" s="7">
+        <v>14</v>
+      </c>
       <c r="D205" s="7"/>
-      <c r="E205" s="7"/>
-      <c r="F205" s="7"/>
-      <c r="G205" s="8"/>
-      <c r="H205" s="8"/>
-      <c r="I205" s="7"/>
-      <c r="J205" s="7"/>
+      <c t="s" r="E205" s="7">
+        <v>268</v>
+      </c>
+      <c r="F205" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G205" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H205" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I205" s="7">
+        <v>269</v>
+      </c>
+      <c t="s" r="J205" s="7">
+        <v>270</v>
+      </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c r="M205" s="7"/>
@@ -7663,29 +7663,29 @@
         <v>13</v>
       </c>
       <c r="B206" s="7">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c t="s" r="C206" s="7">
         <v>14</v>
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>272</v>
+        <v>165</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>273</v>
+        <v>119</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7696,29 +7696,29 @@
         <v>13</v>
       </c>
       <c r="B207" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="C207" s="7">
         <v>14</v>
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>165</v>
+        <v>79</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7729,29 +7729,29 @@
         <v>13</v>
       </c>
       <c r="B208" s="7">
-        <v>133</v>
+        <v>327</v>
       </c>
       <c t="s" r="C208" s="7">
         <v>14</v>
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>36</v>
+        <v>185</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7762,29 +7762,29 @@
         <v>13</v>
       </c>
       <c r="B209" s="7">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c t="s" r="C209" s="7">
         <v>14</v>
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7795,78 +7795,78 @@
         <v>13</v>
       </c>
       <c r="B210" s="7">
-        <v>326</v>
+        <v>642</v>
       </c>
       <c t="s" r="C210" s="7">
         <v>14</v>
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c r="M210" s="7"/>
     </row>
     <row r="211" ht="14.25" customHeight="1">
-      <c t="s" r="A211" s="6">
-        <v>13</v>
-      </c>
-      <c r="B211" s="7">
-        <v>642</v>
-      </c>
-      <c t="s" r="C211" s="7">
-        <v>14</v>
-      </c>
+      <c r="A211" s="6"/>
+      <c r="B211" s="7"/>
+      <c r="C211" s="7"/>
       <c r="D211" s="7"/>
-      <c t="s" r="E211" s="7">
-        <v>271</v>
-      </c>
-      <c r="F211" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G211" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H211" s="8">
-        <v>49</v>
-      </c>
-      <c t="s" r="I211" s="7">
-        <v>104</v>
-      </c>
-      <c t="s" r="J211" s="7">
-        <v>136</v>
-      </c>
+      <c r="E211" s="7"/>
+      <c r="F211" s="7"/>
+      <c r="G211" s="8"/>
+      <c r="H211" s="8"/>
+      <c r="I211" s="7"/>
+      <c r="J211" s="7"/>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c r="M211" s="7"/>
     </row>
     <row r="212" ht="14.25" customHeight="1">
-      <c r="A212" s="6"/>
-      <c r="B212" s="7"/>
-      <c r="C212" s="7"/>
+      <c t="s" r="A212" s="6">
+        <v>13</v>
+      </c>
+      <c r="B212" s="7">
+        <v>887</v>
+      </c>
+      <c t="s" r="C212" s="7">
+        <v>14</v>
+      </c>
       <c r="D212" s="7"/>
-      <c r="E212" s="7"/>
-      <c r="F212" s="7"/>
-      <c r="G212" s="8"/>
-      <c r="H212" s="8"/>
-      <c r="I212" s="7"/>
-      <c r="J212" s="7"/>
+      <c t="s" r="E212" s="7">
+        <v>271</v>
+      </c>
+      <c r="F212" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G212" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H212" s="8">
+        <v>272</v>
+      </c>
+      <c t="s" r="I212" s="7">
+        <v>144</v>
+      </c>
+      <c t="s" r="J212" s="7">
+        <v>273</v>
+      </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c r="M212" s="7"/>
@@ -7876,29 +7876,29 @@
         <v>13</v>
       </c>
       <c r="B213" s="7">
-        <v>272</v>
+        <v>882</v>
       </c>
       <c t="s" r="C213" s="7">
         <v>14</v>
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>275</v>
+        <v>73</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -7909,29 +7909,29 @@
         <v>13</v>
       </c>
       <c r="B214" s="7">
-        <v>693</v>
+        <v>282</v>
       </c>
       <c t="s" r="C214" s="7">
         <v>14</v>
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
+        <v>271</v>
+      </c>
+      <c r="F214" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G214" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H214" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I214" s="7">
         <v>274</v>
       </c>
-      <c r="F214" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G214" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="H214" s="8">
-        <v>110</v>
-      </c>
-      <c t="s" r="I214" s="7">
-        <v>52</v>
-      </c>
       <c t="s" r="J214" s="7">
-        <v>115</v>
+        <v>275</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -7942,29 +7942,29 @@
         <v>13</v>
       </c>
       <c r="B215" s="7">
-        <v>692</v>
+        <v>283</v>
       </c>
       <c t="s" r="C215" s="7">
         <v>14</v>
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>45</v>
+        <v>232</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>235</v>
+        <v>167</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8111,7 +8111,7 @@
         <v>279</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8189,7 +8189,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>71</v>
@@ -8336,7 +8336,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>222</v>
@@ -8483,7 +8483,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>290</v>
@@ -8513,10 +8513,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>232</v>
+        <v>273</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>200</v>
@@ -8543,7 +8543,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>16</v>
@@ -8597,7 +8597,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>31</v>
@@ -8693,10 +8693,10 @@
         <v>49</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>294</v>
@@ -8723,7 +8723,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>16</v>
@@ -9068,7 +9068,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c t="s" r="I253" s="7">
         <v>306</v>
@@ -9098,7 +9098,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>17</v>
@@ -9170,7 +9170,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c t="s" r="J256" s="7">
         <v>83</v>
@@ -9317,7 +9317,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c t="s" r="J261" s="7">
         <v>212</v>
@@ -9386,7 +9386,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>234</v>
+        <v>275</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9530,7 +9530,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>315</v>
@@ -9575,7 +9575,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c t="s" r="I270" s="7">
         <v>57</v>
@@ -9605,16 +9605,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9725,7 +9725,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>119</v>
@@ -9827,7 +9827,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9860,7 +9860,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -9908,7 +9908,7 @@
         <v>321</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10073,7 +10073,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10148,7 +10148,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c t="s" r="I289" s="7">
         <v>179</v>
@@ -10178,13 +10178,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>325</v>
@@ -10301,7 +10301,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10331,7 +10331,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>119</v>
@@ -10364,7 +10364,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>42</v>
@@ -10691,7 +10691,7 @@
         <v>282</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>143</v>
@@ -10859,7 +10859,7 @@
         <v>334</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11006,7 +11006,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11048,7 +11048,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c t="s" r="I319" s="7">
         <v>177</v>
@@ -11078,7 +11078,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c t="s" r="H320" s="8">
         <v>17</v>
@@ -11235,7 +11235,7 @@
         <v>140</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>177</v>
@@ -11370,7 +11370,7 @@
         <v>227</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>232</v>
+        <v>273</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11613,7 +11613,7 @@
         <v>110</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>232</v>
+        <v>273</v>
       </c>
       <c t="s" r="J337" s="7">
         <v>121</v>
@@ -12042,7 +12042,7 @@
         <v>136</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12465,7 +12465,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>345</v>
@@ -12546,7 +12546,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>118</v>
@@ -12681,7 +12681,7 @@
         <v>314</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12759,7 +12759,7 @@
         <v>192</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>213</v>
@@ -12858,7 +12858,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>346</v>
@@ -12972,10 +12972,10 @@
         <v>363</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13449,7 +13449,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13674,7 +13674,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c t="s" r="J406" s="7">
         <v>341</v>
@@ -13707,7 +13707,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>136</v>
@@ -13740,7 +13740,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>379</v>
@@ -13788,7 +13788,7 @@
         <v>170</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>158</v>
@@ -13887,7 +13887,7 @@
         <v>317</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -13920,7 +13920,7 @@
         <v>385</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>

--- a/Data/FlightPlan/FPL_07OCT26.xlsx
+++ b/Data/FlightPlan/FPL_07OCT26.xlsx
@@ -242,6 +242,9 @@
     <t>07:35</t>
   </si>
   <si>
+    <t>08:05</t>
+  </si>
+  <si>
     <t>08:50</t>
   </si>
   <si>
@@ -653,6 +656,12 @@
     <t>13:35</t>
   </si>
   <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
     <t>HGH</t>
   </si>
   <si>
@@ -758,9 +767,6 @@
     <t>05:45</t>
   </si>
   <si>
-    <t>08:05</t>
-  </si>
-  <si>
     <t>13:10</t>
   </si>
   <si>
@@ -830,9 +836,6 @@
     <t>SIN</t>
   </si>
   <si>
-    <t>14:15</t>
-  </si>
-  <si>
     <t>17:40</t>
   </si>
   <si>
@@ -905,9 +908,6 @@
     <t>04:10</t>
   </si>
   <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
     <t>VN-A653</t>
   </si>
   <si>
@@ -1121,6 +1121,9 @@
     <t>04:35</t>
   </si>
   <si>
+    <t>VN-A699</t>
+  </si>
+  <si>
     <t>VN-A810</t>
   </si>
   <si>
@@ -1172,7 +1175,7 @@
     <t>Total Record(s): 337</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 07, 2026 00:15</t>
+    <t xml:space="preserve">Generated on  Oct 07, 2026 02:25</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2616,7 +2619,9 @@
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
+      <c t="s" r="M37" s="7">
+        <v>77</v>
+      </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c t="s" r="A38" s="6">
@@ -2642,10 +2647,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
@@ -2675,7 +2680,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J39" s="7">
         <v>36</v>
@@ -2708,10 +2713,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -2741,10 +2746,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -2777,7 +2782,7 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
@@ -2786,13 +2791,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H43" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -2810,22 +2815,22 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H44" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -2843,7 +2848,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -2852,13 +2857,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H45" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -2876,22 +2881,22 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G46" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H46" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -2924,7 +2929,7 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -2936,10 +2941,10 @@
         <v>61</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
@@ -2957,7 +2962,7 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
@@ -2969,7 +2974,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="J49" s="7">
         <v>22</v>
@@ -2990,7 +2995,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -2999,10 +3004,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H50" s="8">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J50" s="7">
         <v>50</v>
@@ -3023,22 +3028,22 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G51" s="8">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="H51" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3056,7 +3061,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3068,7 +3073,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J52" s="7">
         <v>73</v>
@@ -3089,7 +3094,7 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3101,10 +3106,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3122,7 +3127,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3134,10 +3139,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3155,7 +3160,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3167,10 +3172,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3203,7 +3208,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3212,13 +3217,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H57" s="8">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3236,22 +3241,22 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G58" s="8">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="H58" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3269,7 +3274,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3281,10 +3286,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3302,7 +3307,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3317,7 +3322,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3350,7 +3355,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3362,7 +3367,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J62" s="7">
         <v>33</v>
@@ -3383,7 +3388,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3395,7 +3400,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J63" s="7">
         <v>50</v>
@@ -3416,7 +3421,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3431,7 +3436,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -3449,7 +3454,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3461,7 +3466,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J65" s="7">
         <v>63</v>
@@ -3482,7 +3487,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3497,7 +3502,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3530,19 +3535,19 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J68" s="7">
         <v>33</v>
@@ -3563,7 +3568,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3575,10 +3580,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3596,7 +3601,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -3608,7 +3613,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J70" s="7">
         <v>43</v>
@@ -3629,7 +3634,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3662,7 +3667,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3671,13 +3676,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H72" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="I72" s="7">
         <v>66</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3695,22 +3700,22 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G73" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="H73" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3743,7 +3748,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -3755,7 +3760,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J75" s="7">
         <v>34</v>
@@ -3776,7 +3781,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -3785,13 +3790,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H76" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I76" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3809,13 +3814,13 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H77" s="8">
         <v>17</v>
@@ -3824,7 +3829,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3842,7 +3847,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -3854,10 +3859,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -3890,7 +3895,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -3899,13 +3904,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -3923,22 +3928,22 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -3956,7 +3961,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -3989,7 +3994,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4004,7 +4009,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4037,7 +4042,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4046,13 +4051,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H85" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I85" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4070,13 +4075,13 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G86" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H86" s="8">
         <v>16</v>
@@ -4103,7 +4108,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4115,10 +4120,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4132,11 +4137,11 @@
         <v>3523</v>
       </c>
       <c t="s" r="C88" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4148,10 +4153,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4165,11 +4170,11 @@
         <v>3523</v>
       </c>
       <c t="s" r="C89" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4178,13 +4183,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H89" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4217,22 +4222,22 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="H91" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4250,7 +4255,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4262,10 +4267,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4283,7 +4288,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4292,13 +4297,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4316,22 +4321,22 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4364,7 +4369,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4373,10 +4378,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>23</v>
@@ -4397,22 +4402,22 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="H97" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4430,7 +4435,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4445,7 +4450,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4463,7 +4468,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4472,13 +4477,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4507,23 +4512,23 @@
         <v>7707</v>
       </c>
       <c t="s" r="C101" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="H101" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J101" s="7">
         <v>25</v>
@@ -4540,11 +4545,11 @@
         <v>7707</v>
       </c>
       <c t="s" r="C102" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4553,10 +4558,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>63</v>
@@ -4577,22 +4582,22 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4610,7 +4615,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4622,10 +4627,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4654,11 +4659,11 @@
         <v>5069</v>
       </c>
       <c t="s" r="C106" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4667,13 +4672,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H106" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4687,23 +4692,23 @@
         <v>7620</v>
       </c>
       <c t="s" r="C107" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="H107" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J107" s="7">
         <v>62</v>
@@ -4720,11 +4725,11 @@
         <v>7620</v>
       </c>
       <c t="s" r="C108" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4733,10 +4738,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>69</v>
@@ -4753,26 +4758,26 @@
         <v>7621</v>
       </c>
       <c t="s" r="C109" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4805,7 +4810,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4814,13 +4819,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4838,22 +4843,22 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -4871,7 +4876,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -4883,10 +4888,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -4904,7 +4909,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -4913,13 +4918,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -4952,7 +4957,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -4964,10 +4969,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -4985,7 +4990,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -4994,10 +4999,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>44</v>
@@ -5018,22 +5023,22 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="H118" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5051,7 +5056,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5063,10 +5068,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5099,7 +5104,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5111,10 +5116,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5132,7 +5137,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5144,7 +5149,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>36</v>
@@ -5165,7 +5170,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5177,10 +5182,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5198,7 +5203,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5207,13 +5212,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5231,22 +5236,22 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5264,7 +5269,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5273,13 +5278,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5312,7 +5317,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5324,10 +5329,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5345,7 +5350,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5354,7 +5359,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H129" s="8">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="I129" s="7">
         <v>44</v>
@@ -5378,22 +5383,22 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="H130" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5411,7 +5416,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5420,13 +5425,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5459,26 +5464,30 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>213</v>
-      </c>
-      <c r="K133" s="7"/>
+        <v>214</v>
+      </c>
+      <c t="s" r="K133" s="7">
+        <v>215</v>
+      </c>
       <c r="L133" s="7"/>
-      <c r="M133" s="7"/>
+      <c t="s" r="M133" s="7">
+        <v>216</v>
+      </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
       <c t="s" r="A134" s="6">
@@ -5492,22 +5501,22 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="I134" s="7">
         <v>43</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5525,22 +5534,22 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5558,22 +5567,22 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5606,7 +5615,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5621,7 +5630,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5639,7 +5648,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5651,10 +5660,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5672,7 +5681,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5684,10 +5693,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5705,7 +5714,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5717,10 +5726,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5738,7 +5747,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5747,13 +5756,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5771,13 +5780,13 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>17</v>
@@ -5804,7 +5813,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5813,10 +5822,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>29</v>
@@ -5837,22 +5846,22 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c t="s" r="H145" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5885,7 +5894,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -5894,13 +5903,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="I147" s="7">
         <v>71</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -5918,22 +5927,22 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -5951,7 +5960,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -5960,13 +5969,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -5984,13 +5993,13 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>16</v>
@@ -5999,7 +6008,7 @@
         <v>66</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6017,7 +6026,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6029,10 +6038,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6050,7 +6059,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6062,10 +6071,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6098,7 +6107,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6110,10 +6119,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6131,7 +6140,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6140,13 +6149,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="I155" s="7">
         <v>52</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6164,13 +6173,13 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>41</v>
@@ -6179,7 +6188,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6212,7 +6221,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6221,13 +6230,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6245,22 +6254,22 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6278,22 +6287,22 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6311,19 +6320,19 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>23</v>
@@ -6344,7 +6353,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6353,13 +6362,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I162" s="7">
         <v>51</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6377,13 +6386,13 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>16</v>
@@ -6392,7 +6401,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6410,7 +6419,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6419,13 +6428,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6443,22 +6452,22 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6491,7 +6500,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6506,7 +6515,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6524,7 +6533,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6536,10 +6545,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6557,7 +6566,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6572,7 +6581,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6590,7 +6599,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6605,7 +6614,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6638,7 +6647,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6647,10 +6656,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>76</v>
@@ -6671,22 +6680,22 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>249</v>
+        <v>77</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6704,7 +6713,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6713,13 +6722,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6737,22 +6746,22 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6770,7 +6779,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6785,7 +6794,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6803,7 +6812,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6815,10 +6824,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6851,7 +6860,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6863,10 +6872,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -6884,7 +6893,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -6896,10 +6905,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -6917,7 +6926,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -6926,13 +6935,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -6950,19 +6959,19 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>43</v>
@@ -6983,7 +6992,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -6992,13 +7001,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7016,22 +7025,22 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7064,7 +7073,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7073,13 +7082,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7097,22 +7106,22 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7130,7 +7139,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7139,13 +7148,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7163,13 +7172,13 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="H189" s="8">
         <v>17</v>
@@ -7178,7 +7187,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7196,7 +7205,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7205,10 +7214,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J190" s="7">
         <v>71</v>
@@ -7244,7 +7253,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7256,7 +7265,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c t="s" r="J192" s="7">
         <v>57</v>
@@ -7277,7 +7286,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7289,10 +7298,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7310,7 +7319,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7322,10 +7331,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7343,7 +7352,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7376,7 +7385,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7388,7 +7397,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J196" s="7">
         <v>28</v>
@@ -7409,7 +7418,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7442,7 +7451,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7457,7 +7466,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7490,7 +7499,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7502,10 +7511,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7523,7 +7532,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7538,7 +7547,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7556,7 +7565,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7565,13 +7574,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7589,22 +7598,22 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7637,7 +7646,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7649,10 +7658,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7670,7 +7679,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7682,10 +7691,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7703,7 +7712,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7715,7 +7724,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>36</v>
@@ -7736,7 +7745,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7748,10 +7757,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7769,7 +7778,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7784,7 +7793,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7802,7 +7811,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7814,10 +7823,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7850,7 +7859,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7859,13 +7868,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7883,19 +7892,19 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J213" s="7">
         <v>73</v>
@@ -7916,7 +7925,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -7928,10 +7937,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -7949,7 +7958,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -7961,10 +7970,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -7997,7 +8006,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8009,10 +8018,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8030,7 +8039,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8039,13 +8048,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8063,22 +8072,22 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8096,7 +8105,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8108,10 +8117,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8144,7 +8153,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8156,10 +8165,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8177,7 +8186,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8189,7 +8198,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>71</v>
@@ -8225,7 +8234,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8234,13 +8243,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8258,22 +8267,22 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8291,7 +8300,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8300,13 +8309,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8324,22 +8333,22 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8357,7 +8366,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8366,13 +8375,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8390,22 +8399,22 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8438,7 +8447,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8450,10 +8459,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8471,7 +8480,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8483,10 +8492,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8504,7 +8513,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8513,13 +8522,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8537,13 +8546,13 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>16</v>
@@ -8552,7 +8561,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8585,7 +8594,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8597,7 +8606,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>31</v>
@@ -8618,7 +8627,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8630,10 +8639,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8651,7 +8660,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8663,10 +8672,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8684,7 +8693,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8693,13 +8702,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8717,19 +8726,19 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>38</v>
@@ -8750,7 +8759,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8759,13 +8768,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8783,22 +8792,22 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8824,29 +8833,29 @@
         <v>13</v>
       </c>
       <c r="B245" s="7">
-        <v>901</v>
+        <v>825</v>
       </c>
       <c t="s" r="C245" s="7">
         <v>14</v>
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>144</v>
+        <v>22</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>23</v>
+        <v>301</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -8857,55 +8866,73 @@
         <v>13</v>
       </c>
       <c r="B246" s="7">
-        <v>902</v>
+        <v>826</v>
       </c>
       <c t="s" r="C246" s="7">
         <v>14</v>
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>126</v>
+        <v>214</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>185</v>
+        <v>114</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c r="M246" s="7"/>
     </row>
     <row r="247" ht="14.25" customHeight="1">
-      <c r="A247" s="6"/>
-      <c r="B247" s="7"/>
-      <c r="C247" s="7"/>
+      <c t="s" r="A247" s="6">
+        <v>13</v>
+      </c>
+      <c r="B247" s="7">
+        <v>820</v>
+      </c>
+      <c t="s" r="C247" s="7">
+        <v>14</v>
+      </c>
       <c r="D247" s="7"/>
-      <c r="E247" s="7"/>
-      <c r="F247" s="7"/>
-      <c r="G247" s="8"/>
-      <c r="H247" s="8"/>
-      <c r="I247" s="7"/>
-      <c r="J247" s="7"/>
+      <c t="s" r="E247" s="7">
+        <v>299</v>
+      </c>
+      <c r="F247" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G247" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H247" s="8">
+        <v>302</v>
+      </c>
+      <c t="s" r="I247" s="7">
+        <v>73</v>
+      </c>
+      <c t="s" r="J247" s="7">
+        <v>210</v>
+      </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c r="M247" s="7"/>
     </row>
     <row r="248" ht="14.25" customHeight="1">
       <c t="s" r="A248" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B248" s="7">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c t="s" r="C248" s="7">
         <v>14</v>
@@ -8918,50 +8945,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>16</v>
+        <v>302</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>300</v>
+        <v>16</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>22</v>
+        <v>303</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c r="M248" s="7"/>
     </row>
     <row r="249" ht="14.25" customHeight="1">
-      <c t="s" r="A249" s="6">
-        <v>13</v>
-      </c>
-      <c r="B249" s="7">
-        <v>826</v>
-      </c>
-      <c t="s" r="C249" s="7">
-        <v>14</v>
-      </c>
+      <c r="A249" s="6"/>
+      <c r="B249" s="7"/>
+      <c r="C249" s="7"/>
       <c r="D249" s="7"/>
-      <c t="s" r="E249" s="7">
-        <v>299</v>
-      </c>
-      <c r="F249" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G249" s="8">
-        <v>300</v>
-      </c>
-      <c t="s" r="H249" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I249" s="7">
-        <v>213</v>
-      </c>
-      <c t="s" r="J249" s="7">
-        <v>113</v>
-      </c>
+      <c r="E249" s="7"/>
+      <c r="F249" s="7"/>
+      <c r="G249" s="8"/>
+      <c r="H249" s="8"/>
+      <c r="I249" s="7"/>
+      <c r="J249" s="7"/>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c r="M249" s="7"/>
@@ -8971,29 +8980,29 @@
         <v>13</v>
       </c>
       <c r="B250" s="7">
-        <v>820</v>
+        <v>463</v>
       </c>
       <c t="s" r="C250" s="7">
         <v>14</v>
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F250" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>302</v>
+        <v>268</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>73</v>
+        <v>306</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9001,48 +9010,66 @@
     </row>
     <row r="251" ht="14.25" customHeight="1">
       <c t="s" r="A251" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B251" s="7">
-        <v>821</v>
+        <v>464</v>
       </c>
       <c t="s" r="C251" s="7">
         <v>14</v>
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F251" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>302</v>
+        <v>268</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>303</v>
+        <v>23</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>304</v>
+        <v>103</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c r="M251" s="7"/>
     </row>
     <row r="252" ht="14.25" customHeight="1">
-      <c r="A252" s="6"/>
-      <c r="B252" s="7"/>
-      <c r="C252" s="7"/>
+      <c t="s" r="A252" s="6">
+        <v>13</v>
+      </c>
+      <c r="B252" s="7">
+        <v>567</v>
+      </c>
+      <c t="s" r="C252" s="7">
+        <v>14</v>
+      </c>
       <c r="D252" s="7"/>
-      <c r="E252" s="7"/>
-      <c r="F252" s="7"/>
-      <c r="G252" s="8"/>
-      <c r="H252" s="8"/>
-      <c r="I252" s="7"/>
-      <c r="J252" s="7"/>
+      <c t="s" r="E252" s="7">
+        <v>305</v>
+      </c>
+      <c r="F252" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G252" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H252" s="8">
+        <v>99</v>
+      </c>
+      <c t="s" r="I252" s="7">
+        <v>43</v>
+      </c>
+      <c t="s" r="J252" s="7">
+        <v>64</v>
+      </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c r="M252" s="7"/>
@@ -9052,7 +9079,7 @@
         <v>13</v>
       </c>
       <c r="B253" s="7">
-        <v>463</v>
+        <v>568</v>
       </c>
       <c t="s" r="C253" s="7">
         <v>14</v>
@@ -9065,16 +9092,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>266</v>
+        <v>17</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>221</v>
+        <v>84</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9085,7 +9112,7 @@
         <v>13</v>
       </c>
       <c r="B254" s="7">
-        <v>464</v>
+        <v>7238</v>
       </c>
       <c t="s" r="C254" s="7">
         <v>14</v>
@@ -9098,16 +9125,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>266</v>
+        <v>17</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>17</v>
+        <v>285</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>102</v>
+        <v>307</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9115,10 +9142,10 @@
     </row>
     <row r="255" ht="15" customHeight="1">
       <c t="s" r="A255" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B255" s="7">
-        <v>567</v>
+        <v>7239</v>
       </c>
       <c t="s" r="C255" s="7">
         <v>14</v>
@@ -9131,50 +9158,32 @@
         <v>320</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>17</v>
+        <v>285</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>43</v>
+        <v>308</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>64</v>
+        <v>309</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c r="M255" s="7"/>
     </row>
     <row r="256" ht="14.25" customHeight="1">
-      <c t="s" r="A256" s="6">
-        <v>13</v>
-      </c>
-      <c r="B256" s="7">
-        <v>568</v>
-      </c>
-      <c t="s" r="C256" s="7">
-        <v>14</v>
-      </c>
+      <c r="A256" s="6"/>
+      <c r="B256" s="7"/>
+      <c r="C256" s="7"/>
       <c r="D256" s="7"/>
-      <c t="s" r="E256" s="7">
-        <v>305</v>
-      </c>
-      <c r="F256" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G256" s="8">
-        <v>98</v>
-      </c>
-      <c t="s" r="H256" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I256" s="7">
-        <v>274</v>
-      </c>
-      <c t="s" r="J256" s="7">
-        <v>83</v>
-      </c>
+      <c r="E256" s="7"/>
+      <c r="F256" s="7"/>
+      <c r="G256" s="8"/>
+      <c r="H256" s="8"/>
+      <c r="I256" s="7"/>
+      <c r="J256" s="7"/>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c r="M256" s="7"/>
@@ -9184,29 +9193,29 @@
         <v>13</v>
       </c>
       <c r="B257" s="7">
-        <v>7238</v>
+        <v>124</v>
       </c>
       <c t="s" r="C257" s="7">
         <v>14</v>
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F257" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>68</v>
+        <v>311</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9214,48 +9223,66 @@
     </row>
     <row r="258" ht="14.25" customHeight="1">
       <c t="s" r="A258" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B258" s="7">
-        <v>7239</v>
+        <v>129</v>
       </c>
       <c t="s" r="C258" s="7">
         <v>14</v>
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F258" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>308</v>
+        <v>240</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>309</v>
+        <v>213</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c r="M258" s="7"/>
     </row>
     <row r="259" ht="14.25" customHeight="1">
-      <c r="A259" s="6"/>
-      <c r="B259" s="7"/>
-      <c r="C259" s="7"/>
+      <c t="s" r="A259" s="6">
+        <v>13</v>
+      </c>
+      <c r="B259" s="7">
+        <v>310</v>
+      </c>
+      <c t="s" r="C259" s="7">
+        <v>14</v>
+      </c>
       <c r="D259" s="7"/>
-      <c r="E259" s="7"/>
-      <c r="F259" s="7"/>
-      <c r="G259" s="8"/>
-      <c r="H259" s="8"/>
-      <c r="I259" s="7"/>
-      <c r="J259" s="7"/>
+      <c t="s" r="E259" s="7">
+        <v>310</v>
+      </c>
+      <c r="F259" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G259" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H259" s="8">
+        <v>99</v>
+      </c>
+      <c t="s" r="I259" s="7">
+        <v>91</v>
+      </c>
+      <c t="s" r="J259" s="7">
+        <v>28</v>
+      </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c r="M259" s="7"/>
@@ -9265,7 +9292,7 @@
         <v>13</v>
       </c>
       <c r="B260" s="7">
-        <v>124</v>
+        <v>309</v>
       </c>
       <c t="s" r="C260" s="7">
         <v>14</v>
@@ -9278,50 +9305,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>311</v>
+        <v>167</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>312</v>
+        <v>276</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c r="M260" s="7"/>
     </row>
     <row r="261" ht="14.25" customHeight="1">
-      <c t="s" r="A261" s="6">
-        <v>13</v>
-      </c>
-      <c r="B261" s="7">
-        <v>129</v>
-      </c>
-      <c t="s" r="C261" s="7">
-        <v>14</v>
-      </c>
+      <c r="A261" s="6"/>
+      <c r="B261" s="7"/>
+      <c r="C261" s="7"/>
       <c r="D261" s="7"/>
-      <c t="s" r="E261" s="7">
-        <v>310</v>
-      </c>
-      <c r="F261" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G261" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H261" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I261" s="7">
-        <v>237</v>
-      </c>
-      <c t="s" r="J261" s="7">
-        <v>212</v>
-      </c>
+      <c r="E261" s="7"/>
+      <c r="F261" s="7"/>
+      <c r="G261" s="8"/>
+      <c r="H261" s="8"/>
+      <c r="I261" s="7"/>
+      <c r="J261" s="7"/>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c r="M261" s="7"/>
@@ -9331,29 +9340,29 @@
         <v>13</v>
       </c>
       <c r="B262" s="7">
-        <v>310</v>
+        <v>274</v>
       </c>
       <c t="s" r="C262" s="7">
         <v>14</v>
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F262" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G262" s="8">
         <v>16</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>90</v>
+        <v>293</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9364,45 +9373,63 @@
         <v>13</v>
       </c>
       <c r="B263" s="7">
-        <v>309</v>
+        <v>275</v>
       </c>
       <c t="s" r="C263" s="7">
         <v>14</v>
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F263" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>166</v>
+        <v>224</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>275</v>
+        <v>147</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c r="M263" s="7"/>
     </row>
     <row r="264" ht="14.25" customHeight="1">
-      <c r="A264" s="6"/>
-      <c r="B264" s="7"/>
-      <c r="C264" s="7"/>
+      <c t="s" r="A264" s="6">
+        <v>13</v>
+      </c>
+      <c r="B264" s="7">
+        <v>144</v>
+      </c>
+      <c t="s" r="C264" s="7">
+        <v>14</v>
+      </c>
       <c r="D264" s="7"/>
-      <c r="E264" s="7"/>
-      <c r="F264" s="7"/>
-      <c r="G264" s="8"/>
-      <c r="H264" s="8"/>
-      <c r="I264" s="7"/>
-      <c r="J264" s="7"/>
+      <c t="s" r="E264" s="7">
+        <v>313</v>
+      </c>
+      <c r="F264" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G264" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H264" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I264" s="7">
+        <v>43</v>
+      </c>
+      <c t="s" r="J264" s="7">
+        <v>314</v>
+      </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c r="M264" s="7"/>
@@ -9412,7 +9439,7 @@
         <v>13</v>
       </c>
       <c r="B265" s="7">
-        <v>274</v>
+        <v>159</v>
       </c>
       <c t="s" r="C265" s="7">
         <v>14</v>
@@ -9425,50 +9452,32 @@
         <v>320</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>292</v>
+        <v>235</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>18</v>
+        <v>315</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c r="M265" s="7"/>
     </row>
     <row r="266" ht="14.25" customHeight="1">
-      <c t="s" r="A266" s="6">
-        <v>13</v>
-      </c>
-      <c r="B266" s="7">
-        <v>275</v>
-      </c>
-      <c t="s" r="C266" s="7">
-        <v>14</v>
-      </c>
+      <c r="A266" s="6"/>
+      <c r="B266" s="7"/>
+      <c r="C266" s="7"/>
       <c r="D266" s="7"/>
-      <c t="s" r="E266" s="7">
-        <v>313</v>
-      </c>
-      <c r="F266" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G266" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="H266" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I266" s="7">
-        <v>221</v>
-      </c>
-      <c t="s" r="J266" s="7">
-        <v>146</v>
-      </c>
+      <c r="E266" s="7"/>
+      <c r="F266" s="7"/>
+      <c r="G266" s="8"/>
+      <c r="H266" s="8"/>
+      <c r="I266" s="7"/>
+      <c r="J266" s="7"/>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c r="M266" s="7"/>
@@ -9478,29 +9487,29 @@
         <v>13</v>
       </c>
       <c r="B267" s="7">
-        <v>144</v>
+        <v>813</v>
       </c>
       <c t="s" r="C267" s="7">
         <v>14</v>
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F267" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
         <v>16</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>17</v>
+        <v>274</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9511,45 +9520,63 @@
         <v>13</v>
       </c>
       <c r="B268" s="7">
-        <v>159</v>
+        <v>970</v>
       </c>
       <c t="s" r="C268" s="7">
         <v>14</v>
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F268" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>17</v>
+        <v>274</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>315</v>
+        <v>252</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c r="M268" s="7"/>
     </row>
     <row r="269" ht="14.25" customHeight="1">
-      <c r="A269" s="6"/>
-      <c r="B269" s="7"/>
-      <c r="C269" s="7"/>
+      <c t="s" r="A269" s="6">
+        <v>13</v>
+      </c>
+      <c r="B269" s="7">
+        <v>715</v>
+      </c>
+      <c t="s" r="C269" s="7">
+        <v>14</v>
+      </c>
       <c r="D269" s="7"/>
-      <c r="E269" s="7"/>
-      <c r="F269" s="7"/>
-      <c r="G269" s="8"/>
-      <c r="H269" s="8"/>
-      <c r="I269" s="7"/>
-      <c r="J269" s="7"/>
+      <c t="s" r="E269" s="7">
+        <v>316</v>
+      </c>
+      <c r="F269" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G269" s="8">
+        <v>49</v>
+      </c>
+      <c t="s" r="H269" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="I269" s="7">
+        <v>19</v>
+      </c>
+      <c t="s" r="J269" s="7">
+        <v>43</v>
+      </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c r="M269" s="7"/>
@@ -9559,7 +9586,7 @@
         <v>13</v>
       </c>
       <c r="B270" s="7">
-        <v>813</v>
+        <v>714</v>
       </c>
       <c t="s" r="C270" s="7">
         <v>14</v>
@@ -9572,50 +9599,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>272</v>
+        <v>49</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>317</v>
+        <v>167</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c r="M270" s="7"/>
     </row>
     <row r="271" ht="14.25" customHeight="1">
-      <c t="s" r="A271" s="6">
-        <v>13</v>
-      </c>
-      <c r="B271" s="7">
-        <v>970</v>
-      </c>
-      <c t="s" r="C271" s="7">
-        <v>14</v>
-      </c>
+      <c r="A271" s="6"/>
+      <c r="B271" s="7"/>
+      <c r="C271" s="7"/>
       <c r="D271" s="7"/>
-      <c t="s" r="E271" s="7">
-        <v>316</v>
-      </c>
-      <c r="F271" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G271" s="8">
-        <v>272</v>
-      </c>
-      <c t="s" r="H271" s="8">
-        <v>49</v>
-      </c>
-      <c t="s" r="I271" s="7">
-        <v>255</v>
-      </c>
-      <c t="s" r="J271" s="7">
-        <v>250</v>
-      </c>
+      <c r="E271" s="7"/>
+      <c r="F271" s="7"/>
+      <c r="G271" s="8"/>
+      <c r="H271" s="8"/>
+      <c r="I271" s="7"/>
+      <c r="J271" s="7"/>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c r="M271" s="7"/>
@@ -9625,29 +9634,29 @@
         <v>13</v>
       </c>
       <c r="B272" s="7">
-        <v>715</v>
+        <v>447</v>
       </c>
       <c t="s" r="C272" s="7">
         <v>14</v>
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F272" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c t="s" r="H272" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>19</v>
+        <v>240</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9658,45 +9667,63 @@
         <v>13</v>
       </c>
       <c r="B273" s="7">
-        <v>714</v>
+        <v>440</v>
       </c>
       <c t="s" r="C273" s="7">
         <v>14</v>
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F273" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G273" s="8">
         <v>24</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>73</v>
+        <v>319</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>166</v>
+        <v>36</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c r="M273" s="7"/>
     </row>
     <row r="274" ht="14.25" customHeight="1">
-      <c r="A274" s="6"/>
-      <c r="B274" s="7"/>
-      <c r="C274" s="7"/>
+      <c t="s" r="A274" s="6">
+        <v>13</v>
+      </c>
+      <c r="B274" s="7">
+        <v>407</v>
+      </c>
+      <c t="s" r="C274" s="7">
+        <v>14</v>
+      </c>
       <c r="D274" s="7"/>
-      <c r="E274" s="7"/>
-      <c r="F274" s="7"/>
-      <c r="G274" s="8"/>
-      <c r="H274" s="8"/>
-      <c r="I274" s="7"/>
-      <c r="J274" s="7"/>
+      <c t="s" r="E274" s="7">
+        <v>318</v>
+      </c>
+      <c r="F274" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G274" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H274" s="8">
+        <v>111</v>
+      </c>
+      <c t="s" r="I274" s="7">
+        <v>127</v>
+      </c>
+      <c t="s" r="J274" s="7">
+        <v>186</v>
+      </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c r="M274" s="7"/>
@@ -9706,7 +9733,7 @@
         <v>13</v>
       </c>
       <c r="B275" s="7">
-        <v>447</v>
+        <v>408</v>
       </c>
       <c t="s" r="C275" s="7">
         <v>14</v>
@@ -9719,16 +9746,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>237</v>
+        <v>91</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>119</v>
+        <v>242</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9739,7 +9766,7 @@
         <v>13</v>
       </c>
       <c r="B276" s="7">
-        <v>440</v>
+        <v>1127</v>
       </c>
       <c t="s" r="C276" s="7">
         <v>14</v>
@@ -9752,50 +9779,32 @@
         <v>320</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>319</v>
+        <v>106</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>36</v>
+        <v>260</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c r="M276" s="7"/>
     </row>
     <row r="277" ht="14.25" customHeight="1">
-      <c t="s" r="A277" s="6">
-        <v>13</v>
-      </c>
-      <c r="B277" s="7">
-        <v>407</v>
-      </c>
-      <c t="s" r="C277" s="7">
-        <v>14</v>
-      </c>
+      <c r="A277" s="6"/>
+      <c r="B277" s="7"/>
+      <c r="C277" s="7"/>
       <c r="D277" s="7"/>
-      <c t="s" r="E277" s="7">
-        <v>318</v>
-      </c>
-      <c r="F277" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G277" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H277" s="8">
-        <v>110</v>
-      </c>
-      <c t="s" r="I277" s="7">
-        <v>126</v>
-      </c>
-      <c t="s" r="J277" s="7">
-        <v>185</v>
-      </c>
+      <c r="E277" s="7"/>
+      <c r="F277" s="7"/>
+      <c r="G277" s="8"/>
+      <c r="H277" s="8"/>
+      <c r="I277" s="7"/>
+      <c r="J277" s="7"/>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c r="M277" s="7"/>
@@ -9805,29 +9814,29 @@
         <v>13</v>
       </c>
       <c r="B278" s="7">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c t="s" r="C278" s="7">
         <v>14</v>
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F278" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>110</v>
+        <v>17</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>90</v>
+        <v>321</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9838,45 +9847,63 @@
         <v>13</v>
       </c>
       <c r="B279" s="7">
-        <v>1127</v>
+        <v>514</v>
       </c>
       <c t="s" r="C279" s="7">
         <v>14</v>
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F279" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c r="M279" s="7"/>
     </row>
     <row r="280" ht="15" customHeight="1">
-      <c r="A280" s="6"/>
-      <c r="B280" s="7"/>
-      <c r="C280" s="7"/>
+      <c t="s" r="A280" s="6">
+        <v>13</v>
+      </c>
+      <c r="B280" s="7">
+        <v>563</v>
+      </c>
+      <c t="s" r="C280" s="7">
+        <v>14</v>
+      </c>
       <c r="D280" s="7"/>
-      <c r="E280" s="7"/>
-      <c r="F280" s="7"/>
-      <c r="G280" s="8"/>
-      <c r="H280" s="8"/>
-      <c r="I280" s="7"/>
-      <c r="J280" s="7"/>
+      <c t="s" r="E280" s="7">
+        <v>320</v>
+      </c>
+      <c r="F280" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G280" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H280" s="8">
+        <v>99</v>
+      </c>
+      <c t="s" r="I280" s="7">
+        <v>134</v>
+      </c>
+      <c t="s" r="J280" s="7">
+        <v>322</v>
+      </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c r="M280" s="7"/>
@@ -9886,7 +9913,7 @@
         <v>13</v>
       </c>
       <c r="B281" s="7">
-        <v>501</v>
+        <v>564</v>
       </c>
       <c t="s" r="C281" s="7">
         <v>14</v>
@@ -9899,16 +9926,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>321</v>
+        <v>278</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>265</v>
+        <v>34</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -9919,7 +9946,7 @@
         <v>13</v>
       </c>
       <c r="B282" s="7">
-        <v>514</v>
+        <v>942</v>
       </c>
       <c t="s" r="C282" s="7">
         <v>14</v>
@@ -9932,16 +9959,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -9952,7 +9979,7 @@
         <v>13</v>
       </c>
       <c r="B283" s="7">
-        <v>563</v>
+        <v>943</v>
       </c>
       <c t="s" r="C283" s="7">
         <v>14</v>
@@ -9965,16 +9992,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>322</v>
+        <v>248</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -9982,10 +10009,10 @@
     </row>
     <row r="284" ht="14.25" customHeight="1">
       <c t="s" r="A284" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B284" s="7">
-        <v>564</v>
+        <v>960</v>
       </c>
       <c t="s" r="C284" s="7">
         <v>14</v>
@@ -9998,50 +10025,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>277</v>
+        <v>323</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c r="M284" s="7"/>
     </row>
     <row r="285" ht="15" customHeight="1">
-      <c t="s" r="A285" s="6">
-        <v>13</v>
-      </c>
-      <c r="B285" s="7">
-        <v>942</v>
-      </c>
-      <c t="s" r="C285" s="7">
-        <v>14</v>
-      </c>
+      <c r="A285" s="6"/>
+      <c r="B285" s="7"/>
+      <c r="C285" s="7"/>
       <c r="D285" s="7"/>
-      <c t="s" r="E285" s="7">
-        <v>320</v>
-      </c>
-      <c r="F285" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G285" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H285" s="8">
-        <v>35</v>
-      </c>
-      <c t="s" r="I285" s="7">
-        <v>25</v>
-      </c>
-      <c t="s" r="J285" s="7">
-        <v>37</v>
-      </c>
+      <c r="E285" s="7"/>
+      <c r="F285" s="7"/>
+      <c r="G285" s="8"/>
+      <c r="H285" s="8"/>
+      <c r="I285" s="7"/>
+      <c r="J285" s="7"/>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c r="M285" s="7"/>
@@ -10051,29 +10060,29 @@
         <v>13</v>
       </c>
       <c r="B286" s="7">
-        <v>943</v>
+        <v>210</v>
       </c>
       <c t="s" r="C286" s="7">
         <v>14</v>
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
+        <v>324</v>
+      </c>
+      <c r="F286" s="7">
         <v>320</v>
       </c>
-      <c r="F286" s="7">
-        <v>321</v>
-      </c>
       <c t="s" r="G286" s="8">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>17</v>
+        <v>237</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>38</v>
+        <v>180</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>245</v>
+        <v>90</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10081,48 +10090,66 @@
     </row>
     <row r="287" ht="14.25" customHeight="1">
       <c t="s" r="A287" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B287" s="7">
-        <v>960</v>
+        <v>211</v>
       </c>
       <c t="s" r="C287" s="7">
         <v>14</v>
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
+        <v>324</v>
+      </c>
+      <c r="F287" s="7">
         <v>320</v>
       </c>
-      <c r="F287" s="7">
-        <v>321</v>
-      </c>
       <c t="s" r="G287" s="8">
-        <v>17</v>
+        <v>237</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>323</v>
+        <v>247</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>71</v>
+        <v>325</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c r="M287" s="7"/>
     </row>
     <row r="288" ht="14.25" customHeight="1">
-      <c r="A288" s="6"/>
-      <c r="B288" s="7"/>
-      <c r="C288" s="7"/>
+      <c t="s" r="A288" s="6">
+        <v>13</v>
+      </c>
+      <c r="B288" s="7">
+        <v>376</v>
+      </c>
+      <c t="s" r="C288" s="7">
+        <v>14</v>
+      </c>
       <c r="D288" s="7"/>
-      <c r="E288" s="7"/>
-      <c r="F288" s="7"/>
-      <c r="G288" s="8"/>
-      <c r="H288" s="8"/>
-      <c r="I288" s="7"/>
-      <c r="J288" s="7"/>
+      <c t="s" r="E288" s="7">
+        <v>324</v>
+      </c>
+      <c r="F288" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G288" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H288" s="8">
+        <v>326</v>
+      </c>
+      <c t="s" r="I288" s="7">
+        <v>45</v>
+      </c>
+      <c t="s" r="J288" s="7">
+        <v>117</v>
+      </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c r="M288" s="7"/>
@@ -10132,7 +10159,7 @@
         <v>13</v>
       </c>
       <c r="B289" s="7">
-        <v>210</v>
+        <v>377</v>
       </c>
       <c t="s" r="C289" s="7">
         <v>14</v>
@@ -10145,50 +10172,32 @@
         <v>320</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>16</v>
+        <v>326</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>234</v>
+        <v>16</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>89</v>
+        <v>195</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c r="M289" s="7"/>
     </row>
     <row r="290" ht="15" customHeight="1">
-      <c t="s" r="A290" s="6">
-        <v>13</v>
-      </c>
-      <c r="B290" s="7">
-        <v>211</v>
-      </c>
-      <c t="s" r="C290" s="7">
-        <v>14</v>
-      </c>
+      <c r="A290" s="6"/>
+      <c r="B290" s="7"/>
+      <c r="C290" s="7"/>
       <c r="D290" s="7"/>
-      <c t="s" r="E290" s="7">
-        <v>324</v>
-      </c>
-      <c r="F290" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G290" s="8">
-        <v>234</v>
-      </c>
-      <c t="s" r="H290" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I290" s="7">
-        <v>244</v>
-      </c>
-      <c t="s" r="J290" s="7">
-        <v>325</v>
-      </c>
+      <c r="E290" s="7"/>
+      <c r="F290" s="7"/>
+      <c r="G290" s="8"/>
+      <c r="H290" s="8"/>
+      <c r="I290" s="7"/>
+      <c r="J290" s="7"/>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c r="M290" s="7"/>
@@ -10198,29 +10207,29 @@
         <v>13</v>
       </c>
       <c r="B291" s="7">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c t="s" r="C291" s="7">
         <v>14</v>
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>326</v>
+        <v>61</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>116</v>
+        <v>240</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10231,45 +10240,63 @@
         <v>13</v>
       </c>
       <c r="B292" s="7">
-        <v>377</v>
+        <v>422</v>
       </c>
       <c t="s" r="C292" s="7">
         <v>14</v>
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>326</v>
+        <v>61</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>148</v>
+        <v>241</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>194</v>
+        <v>120</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c r="M292" s="7"/>
     </row>
     <row r="293" ht="14.25" customHeight="1">
-      <c r="A293" s="6"/>
-      <c r="B293" s="7"/>
-      <c r="C293" s="7"/>
+      <c t="s" r="A293" s="6">
+        <v>13</v>
+      </c>
+      <c r="B293" s="7">
+        <v>451</v>
+      </c>
+      <c t="s" r="C293" s="7">
+        <v>14</v>
+      </c>
       <c r="D293" s="7"/>
-      <c r="E293" s="7"/>
-      <c r="F293" s="7"/>
-      <c r="G293" s="8"/>
-      <c r="H293" s="8"/>
-      <c r="I293" s="7"/>
-      <c r="J293" s="7"/>
+      <c t="s" r="E293" s="7">
+        <v>327</v>
+      </c>
+      <c r="F293" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G293" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H293" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="I293" s="7">
+        <v>258</v>
+      </c>
+      <c t="s" r="J293" s="7">
+        <v>42</v>
+      </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c r="M293" s="7"/>
@@ -10279,7 +10306,7 @@
         <v>13</v>
       </c>
       <c r="B294" s="7">
-        <v>421</v>
+        <v>454</v>
       </c>
       <c t="s" r="C294" s="7">
         <v>14</v>
@@ -10292,16 +10319,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>57</v>
+        <v>128</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>237</v>
+        <v>83</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10312,7 +10339,7 @@
         <v>13</v>
       </c>
       <c r="B295" s="7">
-        <v>422</v>
+        <v>7712</v>
       </c>
       <c t="s" r="C295" s="7">
         <v>14</v>
@@ -10325,16 +10352,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>17</v>
+        <v>328</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>238</v>
+        <v>329</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10342,10 +10369,10 @@
     </row>
     <row r="296" ht="14.25" customHeight="1">
       <c t="s" r="A296" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B296" s="7">
-        <v>451</v>
+        <v>7713</v>
       </c>
       <c t="s" r="C296" s="7">
         <v>14</v>
@@ -10358,50 +10385,32 @@
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>17</v>
+        <v>328</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>256</v>
+        <v>196</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>42</v>
+        <v>330</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c r="M296" s="7"/>
     </row>
     <row r="297" ht="14.25" customHeight="1">
-      <c t="s" r="A297" s="6">
-        <v>13</v>
-      </c>
-      <c r="B297" s="7">
-        <v>454</v>
-      </c>
-      <c t="s" r="C297" s="7">
-        <v>14</v>
-      </c>
+      <c r="A297" s="6"/>
+      <c r="B297" s="7"/>
+      <c r="C297" s="7"/>
       <c r="D297" s="7"/>
-      <c t="s" r="E297" s="7">
-        <v>327</v>
-      </c>
-      <c r="F297" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G297" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="H297" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I297" s="7">
-        <v>127</v>
-      </c>
-      <c t="s" r="J297" s="7">
-        <v>82</v>
-      </c>
+      <c r="E297" s="7"/>
+      <c r="F297" s="7"/>
+      <c r="G297" s="8"/>
+      <c r="H297" s="8"/>
+      <c r="I297" s="7"/>
+      <c r="J297" s="7"/>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c r="M297" s="7"/>
@@ -10411,29 +10420,29 @@
         <v>13</v>
       </c>
       <c r="B298" s="7">
-        <v>7712</v>
+        <v>905</v>
       </c>
       <c t="s" r="C298" s="7">
         <v>14</v>
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F298" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G298" s="8">
         <v>17</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>204</v>
+        <v>333</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10441,48 +10450,66 @@
     </row>
     <row r="299" ht="14.25" customHeight="1">
       <c t="s" r="A299" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B299" s="7">
-        <v>7713</v>
+        <v>906</v>
       </c>
       <c t="s" r="C299" s="7">
         <v>14</v>
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F299" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>330</v>
+        <v>159</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c r="M299" s="7"/>
     </row>
     <row r="300" ht="15" customHeight="1">
-      <c r="A300" s="6"/>
-      <c r="B300" s="7"/>
-      <c r="C300" s="7"/>
+      <c t="s" r="A300" s="6">
+        <v>13</v>
+      </c>
+      <c r="B300" s="7">
+        <v>441</v>
+      </c>
+      <c t="s" r="C300" s="7">
+        <v>14</v>
+      </c>
       <c r="D300" s="7"/>
-      <c r="E300" s="7"/>
-      <c r="F300" s="7"/>
-      <c r="G300" s="8"/>
-      <c r="H300" s="8"/>
-      <c r="I300" s="7"/>
-      <c r="J300" s="7"/>
+      <c t="s" r="E300" s="7">
+        <v>331</v>
+      </c>
+      <c r="F300" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G300" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H300" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="I300" s="7">
+        <v>83</v>
+      </c>
+      <c t="s" r="J300" s="7">
+        <v>93</v>
+      </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c r="M300" s="7"/>
@@ -10492,7 +10519,7 @@
         <v>13</v>
       </c>
       <c r="B301" s="7">
-        <v>905</v>
+        <v>442</v>
       </c>
       <c t="s" r="C301" s="7">
         <v>14</v>
@@ -10505,16 +10532,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>300</v>
+        <v>17</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>332</v>
+        <v>106</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>333</v>
+        <v>39</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10522,10 +10549,10 @@
     </row>
     <row r="302" ht="14.25" customHeight="1">
       <c t="s" r="A302" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B302" s="7">
-        <v>906</v>
+        <v>982</v>
       </c>
       <c t="s" r="C302" s="7">
         <v>14</v>
@@ -10538,50 +10565,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>300</v>
+        <v>17</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>221</v>
+        <v>334</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>158</v>
+        <v>57</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c r="M302" s="7"/>
     </row>
     <row r="303" ht="14.25" customHeight="1">
-      <c t="s" r="A303" s="6">
-        <v>13</v>
-      </c>
-      <c r="B303" s="7">
-        <v>441</v>
-      </c>
-      <c t="s" r="C303" s="7">
-        <v>14</v>
-      </c>
+      <c r="A303" s="6"/>
+      <c r="B303" s="7"/>
+      <c r="C303" s="7"/>
       <c r="D303" s="7"/>
-      <c t="s" r="E303" s="7">
-        <v>331</v>
-      </c>
-      <c r="F303" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G303" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H303" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="I303" s="7">
-        <v>82</v>
-      </c>
-      <c t="s" r="J303" s="7">
-        <v>92</v>
-      </c>
+      <c r="E303" s="7"/>
+      <c r="F303" s="7"/>
+      <c r="G303" s="8"/>
+      <c r="H303" s="8"/>
+      <c r="I303" s="7"/>
+      <c r="J303" s="7"/>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c r="M303" s="7"/>
@@ -10591,29 +10600,29 @@
         <v>13</v>
       </c>
       <c r="B304" s="7">
-        <v>442</v>
+        <v>801</v>
       </c>
       <c t="s" r="C304" s="7">
         <v>14</v>
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F304" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>17</v>
+        <v>283</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>105</v>
+        <v>256</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>39</v>
+        <v>144</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10621,48 +10630,66 @@
     </row>
     <row r="305" ht="15" customHeight="1">
       <c t="s" r="A305" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B305" s="7">
-        <v>982</v>
+        <v>802</v>
       </c>
       <c t="s" r="C305" s="7">
         <v>14</v>
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F305" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>17</v>
+        <v>283</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c r="M305" s="7"/>
     </row>
     <row r="306" ht="14.25" customHeight="1">
-      <c r="A306" s="6"/>
-      <c r="B306" s="7"/>
-      <c r="C306" s="7"/>
+      <c t="s" r="A306" s="6">
+        <v>13</v>
+      </c>
+      <c r="B306" s="7">
+        <v>362</v>
+      </c>
+      <c t="s" r="C306" s="7">
+        <v>14</v>
+      </c>
       <c r="D306" s="7"/>
-      <c r="E306" s="7"/>
-      <c r="F306" s="7"/>
-      <c r="G306" s="8"/>
-      <c r="H306" s="8"/>
-      <c r="I306" s="7"/>
-      <c r="J306" s="7"/>
+      <c t="s" r="E306" s="7">
+        <v>335</v>
+      </c>
+      <c r="F306" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G306" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H306" s="8">
+        <v>111</v>
+      </c>
+      <c t="s" r="I306" s="7">
+        <v>128</v>
+      </c>
+      <c t="s" r="J306" s="7">
+        <v>72</v>
+      </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c r="M306" s="7"/>
@@ -10672,7 +10699,7 @@
         <v>13</v>
       </c>
       <c r="B307" s="7">
-        <v>801</v>
+        <v>363</v>
       </c>
       <c t="s" r="C307" s="7">
         <v>14</v>
@@ -10685,16 +10712,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>282</v>
+        <v>16</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>254</v>
+        <v>201</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>143</v>
+        <v>295</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10705,7 +10732,7 @@
         <v>13</v>
       </c>
       <c r="B308" s="7">
-        <v>802</v>
+        <v>3948</v>
       </c>
       <c t="s" r="C308" s="7">
         <v>14</v>
@@ -10718,16 +10745,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>282</v>
+        <v>16</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>16</v>
+        <v>328</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10735,10 +10762,10 @@
     </row>
     <row r="309" ht="14.25" customHeight="1">
       <c t="s" r="A309" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B309" s="7">
-        <v>362</v>
+        <v>3949</v>
       </c>
       <c t="s" r="C309" s="7">
         <v>14</v>
@@ -10751,50 +10778,32 @@
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>16</v>
+        <v>328</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>127</v>
+        <v>334</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>72</v>
+        <v>238</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c r="M309" s="7"/>
     </row>
     <row r="310" ht="15" customHeight="1">
-      <c t="s" r="A310" s="6">
-        <v>13</v>
-      </c>
-      <c r="B310" s="7">
-        <v>363</v>
-      </c>
-      <c t="s" r="C310" s="7">
-        <v>14</v>
-      </c>
+      <c r="A310" s="6"/>
+      <c r="B310" s="7"/>
+      <c r="C310" s="7"/>
       <c r="D310" s="7"/>
-      <c t="s" r="E310" s="7">
-        <v>335</v>
-      </c>
-      <c r="F310" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G310" s="8">
-        <v>110</v>
-      </c>
-      <c t="s" r="H310" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I310" s="7">
-        <v>200</v>
-      </c>
-      <c t="s" r="J310" s="7">
-        <v>294</v>
-      </c>
+      <c r="E310" s="7"/>
+      <c r="F310" s="7"/>
+      <c r="G310" s="8"/>
+      <c r="H310" s="8"/>
+      <c r="I310" s="7"/>
+      <c r="J310" s="7"/>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c r="M310" s="7"/>
@@ -10804,29 +10813,29 @@
         <v>13</v>
       </c>
       <c r="B311" s="7">
-        <v>3948</v>
+        <v>835</v>
       </c>
       <c t="s" r="C311" s="7">
         <v>14</v>
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F311" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>328</v>
+        <v>171</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>314</v>
+        <v>178</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10834,48 +10843,66 @@
     </row>
     <row r="312" ht="14.25" customHeight="1">
       <c t="s" r="A312" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B312" s="7">
-        <v>3949</v>
+        <v>730</v>
       </c>
       <c t="s" r="C312" s="7">
         <v>14</v>
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F312" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>328</v>
+        <v>171</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>235</v>
+        <v>101</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c r="M312" s="7"/>
     </row>
     <row r="313" ht="14.25" customHeight="1">
-      <c r="A313" s="6"/>
-      <c r="B313" s="7"/>
-      <c r="C313" s="7"/>
+      <c t="s" r="A313" s="6">
+        <v>13</v>
+      </c>
+      <c r="B313" s="7">
+        <v>731</v>
+      </c>
+      <c t="s" r="C313" s="7">
+        <v>14</v>
+      </c>
       <c r="D313" s="7"/>
-      <c r="E313" s="7"/>
-      <c r="F313" s="7"/>
-      <c r="G313" s="8"/>
-      <c r="H313" s="8"/>
-      <c r="I313" s="7"/>
-      <c r="J313" s="7"/>
+      <c t="s" r="E313" s="7">
+        <v>336</v>
+      </c>
+      <c r="F313" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G313" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H313" s="8">
+        <v>171</v>
+      </c>
+      <c t="s" r="I313" s="7">
+        <v>230</v>
+      </c>
+      <c t="s" r="J313" s="7">
+        <v>284</v>
+      </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c r="M313" s="7"/>
@@ -10885,7 +10912,7 @@
         <v>13</v>
       </c>
       <c r="B314" s="7">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c t="s" r="C314" s="7">
         <v>14</v>
@@ -10898,50 +10925,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G314" s="8">
+        <v>171</v>
+      </c>
+      <c t="s" r="H314" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H314" s="8">
-        <v>170</v>
-      </c>
       <c t="s" r="I314" s="7">
-        <v>177</v>
+        <v>130</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>142</v>
+        <v>266</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c r="M314" s="7"/>
     </row>
     <row r="315" ht="15" customHeight="1">
-      <c t="s" r="A315" s="6">
-        <v>13</v>
-      </c>
-      <c r="B315" s="7">
-        <v>730</v>
-      </c>
-      <c t="s" r="C315" s="7">
-        <v>14</v>
-      </c>
+      <c r="A315" s="6"/>
+      <c r="B315" s="7"/>
+      <c r="C315" s="7"/>
       <c r="D315" s="7"/>
-      <c t="s" r="E315" s="7">
-        <v>336</v>
-      </c>
-      <c r="F315" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G315" s="8">
-        <v>170</v>
-      </c>
-      <c t="s" r="H315" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I315" s="7">
-        <v>322</v>
-      </c>
-      <c t="s" r="J315" s="7">
-        <v>100</v>
-      </c>
+      <c r="E315" s="7"/>
+      <c r="F315" s="7"/>
+      <c r="G315" s="8"/>
+      <c r="H315" s="8"/>
+      <c r="I315" s="7"/>
+      <c r="J315" s="7"/>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c r="M315" s="7"/>
@@ -10951,29 +10960,29 @@
         <v>13</v>
       </c>
       <c r="B316" s="7">
-        <v>731</v>
+        <v>461</v>
       </c>
       <c t="s" r="C316" s="7">
         <v>14</v>
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F316" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>170</v>
+        <v>268</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>227</v>
+        <v>178</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>283</v>
+        <v>211</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -10984,45 +10993,63 @@
         <v>13</v>
       </c>
       <c r="B317" s="7">
-        <v>834</v>
+        <v>462</v>
       </c>
       <c t="s" r="C317" s="7">
         <v>14</v>
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F317" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>170</v>
+        <v>268</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>129</v>
+        <v>22</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>264</v>
+        <v>207</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c r="M317" s="7"/>
     </row>
     <row r="318" ht="14.25" customHeight="1">
-      <c r="A318" s="6"/>
-      <c r="B318" s="7"/>
-      <c r="C318" s="7"/>
+      <c t="s" r="A318" s="6">
+        <v>13</v>
+      </c>
+      <c r="B318" s="7">
+        <v>141</v>
+      </c>
+      <c t="s" r="C318" s="7">
+        <v>14</v>
+      </c>
       <c r="D318" s="7"/>
-      <c r="E318" s="7"/>
-      <c r="F318" s="7"/>
-      <c r="G318" s="8"/>
-      <c r="H318" s="8"/>
-      <c r="I318" s="7"/>
-      <c r="J318" s="7"/>
+      <c t="s" r="E318" s="7">
+        <v>337</v>
+      </c>
+      <c r="F318" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G318" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H318" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I318" s="7">
+        <v>147</v>
+      </c>
+      <c t="s" r="J318" s="7">
+        <v>63</v>
+      </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c r="M318" s="7"/>
@@ -11032,7 +11059,7 @@
         <v>13</v>
       </c>
       <c r="B319" s="7">
-        <v>461</v>
+        <v>148</v>
       </c>
       <c t="s" r="C319" s="7">
         <v>14</v>
@@ -11045,27 +11072,31 @@
         <v>320</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>266</v>
+        <v>17</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>177</v>
+        <v>63</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>210</v>
-      </c>
-      <c r="K319" s="7"/>
+        <v>93</v>
+      </c>
+      <c t="s" r="K319" s="7">
+        <v>64</v>
+      </c>
       <c r="L319" s="7"/>
-      <c r="M319" s="7"/>
+      <c t="s" r="M319" s="7">
+        <v>148</v>
+      </c>
     </row>
     <row r="320" ht="15" customHeight="1">
       <c t="s" r="A320" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B320" s="7">
-        <v>462</v>
+        <v>1980</v>
       </c>
       <c t="s" r="C320" s="7">
         <v>14</v>
@@ -11078,50 +11109,32 @@
         <v>320</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>266</v>
+        <v>17</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>17</v>
+        <v>338</v>
       </c>
       <c t="s" r="I320" s="7">
+        <v>339</v>
+      </c>
+      <c t="s" r="J320" s="7">
         <v>22</v>
-      </c>
-      <c t="s" r="J320" s="7">
-        <v>206</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c r="M320" s="7"/>
     </row>
     <row r="321" ht="14.25" customHeight="1">
-      <c t="s" r="A321" s="6">
-        <v>13</v>
-      </c>
-      <c r="B321" s="7">
-        <v>141</v>
-      </c>
-      <c t="s" r="C321" s="7">
-        <v>14</v>
-      </c>
+      <c r="A321" s="6"/>
+      <c r="B321" s="7"/>
+      <c r="C321" s="7"/>
       <c r="D321" s="7"/>
-      <c t="s" r="E321" s="7">
-        <v>337</v>
-      </c>
-      <c r="F321" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G321" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H321" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I321" s="7">
-        <v>146</v>
-      </c>
-      <c t="s" r="J321" s="7">
-        <v>63</v>
-      </c>
+      <c r="E321" s="7"/>
+      <c r="F321" s="7"/>
+      <c r="G321" s="8"/>
+      <c r="H321" s="8"/>
+      <c r="I321" s="7"/>
+      <c r="J321" s="7"/>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c r="M321" s="7"/>
@@ -11131,14 +11144,14 @@
         <v>13</v>
       </c>
       <c r="B322" s="7">
-        <v>148</v>
+        <v>1382</v>
       </c>
       <c t="s" r="C322" s="7">
         <v>14</v>
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11147,66 +11160,80 @@
         <v>16</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>63</v>
+        <v>266</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>92</v>
-      </c>
-      <c t="s" r="K322" s="7">
-        <v>64</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="K322" s="7"/>
       <c r="L322" s="7"/>
-      <c t="s" r="M322" s="7">
-        <v>147</v>
-      </c>
+      <c r="M322" s="7"/>
     </row>
     <row r="323" ht="14.25" customHeight="1">
       <c t="s" r="A323" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B323" s="7">
-        <v>1980</v>
+        <v>1383</v>
       </c>
       <c t="s" r="C323" s="7">
         <v>14</v>
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>338</v>
+        <v>16</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>339</v>
+        <v>290</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c r="M323" s="7"/>
     </row>
     <row r="324" ht="14.25" customHeight="1">
-      <c r="A324" s="6"/>
-      <c r="B324" s="7"/>
-      <c r="C324" s="7"/>
+      <c t="s" r="A324" s="6">
+        <v>13</v>
+      </c>
+      <c r="B324" s="7">
+        <v>304</v>
+      </c>
+      <c t="s" r="C324" s="7">
+        <v>14</v>
+      </c>
       <c r="D324" s="7"/>
-      <c r="E324" s="7"/>
-      <c r="F324" s="7"/>
-      <c r="G324" s="8"/>
-      <c r="H324" s="8"/>
-      <c r="I324" s="7"/>
-      <c r="J324" s="7"/>
+      <c t="s" r="E324" s="7">
+        <v>340</v>
+      </c>
+      <c r="F324" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G324" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H324" s="8">
+        <v>99</v>
+      </c>
+      <c t="s" r="I324" s="7">
+        <v>78</v>
+      </c>
+      <c t="s" r="J324" s="7">
+        <v>317</v>
+      </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c r="M324" s="7"/>
@@ -11216,7 +11243,7 @@
         <v>13</v>
       </c>
       <c r="B325" s="7">
-        <v>1382</v>
+        <v>303</v>
       </c>
       <c t="s" r="C325" s="7">
         <v>14</v>
@@ -11229,16 +11256,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>140</v>
+        <v>16</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>264</v>
+        <v>87</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11249,7 +11276,7 @@
         <v>13</v>
       </c>
       <c r="B326" s="7">
-        <v>1383</v>
+        <v>374</v>
       </c>
       <c t="s" r="C326" s="7">
         <v>14</v>
@@ -11262,16 +11289,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>140</v>
+        <v>16</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>16</v>
+        <v>326</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>289</v>
+        <v>230</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>97</v>
+        <v>216</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11282,7 +11309,7 @@
         <v>13</v>
       </c>
       <c r="B327" s="7">
-        <v>304</v>
+        <v>375</v>
       </c>
       <c t="s" r="C327" s="7">
         <v>14</v>
@@ -11295,16 +11322,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>16</v>
+        <v>326</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>77</v>
+        <v>284</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11315,7 +11342,7 @@
         <v>13</v>
       </c>
       <c r="B328" s="7">
-        <v>303</v>
+        <v>384</v>
       </c>
       <c t="s" r="C328" s="7">
         <v>14</v>
@@ -11328,16 +11355,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>198</v>
+        <v>28</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11348,7 +11375,7 @@
         <v>13</v>
       </c>
       <c r="B329" s="7">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c t="s" r="C329" s="7">
         <v>14</v>
@@ -11361,16 +11388,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G329" s="8">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>326</v>
+        <v>16</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>227</v>
+        <v>167</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>273</v>
+        <v>106</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11381,7 +11408,7 @@
         <v>13</v>
       </c>
       <c r="B330" s="7">
-        <v>375</v>
+        <v>1128</v>
       </c>
       <c t="s" r="C330" s="7">
         <v>14</v>
@@ -11394,50 +11421,32 @@
         <v>320</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>326</v>
+        <v>16</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>283</v>
+        <v>342</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>341</v>
+        <v>154</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c r="M330" s="7"/>
     </row>
     <row r="331" ht="14.25" customHeight="1">
-      <c t="s" r="A331" s="6">
-        <v>13</v>
-      </c>
-      <c r="B331" s="7">
-        <v>384</v>
-      </c>
-      <c t="s" r="C331" s="7">
-        <v>14</v>
-      </c>
+      <c r="A331" s="6"/>
+      <c r="B331" s="7"/>
+      <c r="C331" s="7"/>
       <c r="D331" s="7"/>
-      <c t="s" r="E331" s="7">
-        <v>340</v>
-      </c>
-      <c r="F331" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G331" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H331" s="8">
-        <v>140</v>
-      </c>
-      <c t="s" r="I331" s="7">
-        <v>114</v>
-      </c>
-      <c t="s" r="J331" s="7">
-        <v>28</v>
-      </c>
+      <c r="E331" s="7"/>
+      <c r="F331" s="7"/>
+      <c r="G331" s="8"/>
+      <c r="H331" s="8"/>
+      <c r="I331" s="7"/>
+      <c r="J331" s="7"/>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c r="M331" s="7"/>
@@ -11447,29 +11456,29 @@
         <v>13</v>
       </c>
       <c r="B332" s="7">
-        <v>385</v>
+        <v>339</v>
       </c>
       <c t="s" r="C332" s="7">
         <v>14</v>
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F332" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>140</v>
+        <v>16</v>
       </c>
       <c t="s" r="H332" s="8">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>166</v>
+        <v>97</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11480,45 +11489,63 @@
         <v>13</v>
       </c>
       <c r="B333" s="7">
-        <v>1128</v>
+        <v>718</v>
       </c>
       <c t="s" r="C333" s="7">
         <v>14</v>
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F333" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>342</v>
+        <v>157</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c r="M333" s="7"/>
     </row>
     <row r="334" ht="14.25" customHeight="1">
-      <c r="A334" s="6"/>
-      <c r="B334" s="7"/>
-      <c r="C334" s="7"/>
+      <c t="s" r="A334" s="6">
+        <v>13</v>
+      </c>
+      <c r="B334" s="7">
+        <v>1729</v>
+      </c>
+      <c t="s" r="C334" s="7">
+        <v>14</v>
+      </c>
       <c r="D334" s="7"/>
-      <c r="E334" s="7"/>
-      <c r="F334" s="7"/>
-      <c r="G334" s="8"/>
-      <c r="H334" s="8"/>
-      <c r="I334" s="7"/>
-      <c r="J334" s="7"/>
+      <c t="s" r="E334" s="7">
+        <v>343</v>
+      </c>
+      <c r="F334" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G334" s="8">
+        <v>49</v>
+      </c>
+      <c t="s" r="H334" s="8">
+        <v>111</v>
+      </c>
+      <c t="s" r="I334" s="7">
+        <v>216</v>
+      </c>
+      <c t="s" r="J334" s="7">
+        <v>122</v>
+      </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c r="M334" s="7"/>
@@ -11528,7 +11555,7 @@
         <v>13</v>
       </c>
       <c r="B335" s="7">
-        <v>339</v>
+        <v>1728</v>
       </c>
       <c t="s" r="C335" s="7">
         <v>14</v>
@@ -11541,16 +11568,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>96</v>
+        <v>186</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11561,7 +11588,7 @@
         <v>13</v>
       </c>
       <c r="B336" s="7">
-        <v>718</v>
+        <v>8892</v>
       </c>
       <c t="s" r="C336" s="7">
         <v>14</v>
@@ -11574,16 +11601,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>49</v>
+        <v>185</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>144</v>
+        <v>94</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11594,7 +11621,7 @@
         <v>13</v>
       </c>
       <c r="B337" s="7">
-        <v>1729</v>
+        <v>8893</v>
       </c>
       <c t="s" r="C337" s="7">
         <v>14</v>
@@ -11607,16 +11634,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G337" s="8">
+        <v>185</v>
+      </c>
+      <c t="s" r="H337" s="8">
         <v>49</v>
       </c>
-      <c t="s" r="H337" s="8">
-        <v>110</v>
-      </c>
       <c t="s" r="I337" s="7">
-        <v>273</v>
+        <v>344</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>121</v>
+        <v>345</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11627,7 +11654,7 @@
         <v>13</v>
       </c>
       <c r="B338" s="7">
-        <v>1728</v>
+        <v>878</v>
       </c>
       <c t="s" r="C338" s="7">
         <v>14</v>
@@ -11640,50 +11667,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>110</v>
+        <v>49</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>294</v>
+        <v>346</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c r="M338" s="7"/>
     </row>
     <row r="339" ht="14.25" customHeight="1">
-      <c t="s" r="A339" s="6">
-        <v>13</v>
-      </c>
-      <c r="B339" s="7">
-        <v>8892</v>
-      </c>
-      <c t="s" r="C339" s="7">
-        <v>14</v>
-      </c>
+      <c r="A339" s="6"/>
+      <c r="B339" s="7"/>
+      <c r="C339" s="7"/>
       <c r="D339" s="7"/>
-      <c t="s" r="E339" s="7">
-        <v>343</v>
-      </c>
-      <c r="F339" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G339" s="8">
-        <v>49</v>
-      </c>
-      <c t="s" r="H339" s="8">
-        <v>184</v>
-      </c>
-      <c t="s" r="I339" s="7">
-        <v>166</v>
-      </c>
-      <c t="s" r="J339" s="7">
-        <v>93</v>
-      </c>
+      <c r="E339" s="7"/>
+      <c r="F339" s="7"/>
+      <c r="G339" s="8"/>
+      <c r="H339" s="8"/>
+      <c r="I339" s="7"/>
+      <c r="J339" s="7"/>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c r="M339" s="7"/>
@@ -11693,29 +11702,29 @@
         <v>13</v>
       </c>
       <c r="B340" s="7">
-        <v>8893</v>
+        <v>630</v>
       </c>
       <c t="s" r="C340" s="7">
         <v>14</v>
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>184</v>
+        <v>16</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>344</v>
+        <v>192</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>345</v>
+        <v>306</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11726,14 +11735,14 @@
         <v>13</v>
       </c>
       <c r="B341" s="7">
-        <v>878</v>
+        <v>629</v>
       </c>
       <c t="s" r="C341" s="7">
         <v>14</v>
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -11742,29 +11751,47 @@
         <v>49</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>202</v>
+        <v>120</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>346</v>
+        <v>113</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c r="M341" s="7"/>
     </row>
     <row r="342" ht="14.25" customHeight="1">
-      <c r="A342" s="6"/>
-      <c r="B342" s="7"/>
-      <c r="C342" s="7"/>
+      <c t="s" r="A342" s="6">
+        <v>13</v>
+      </c>
+      <c r="B342" s="7">
+        <v>636</v>
+      </c>
+      <c t="s" r="C342" s="7">
+        <v>14</v>
+      </c>
       <c r="D342" s="7"/>
-      <c r="E342" s="7"/>
-      <c r="F342" s="7"/>
-      <c r="G342" s="8"/>
-      <c r="H342" s="8"/>
-      <c r="I342" s="7"/>
-      <c r="J342" s="7"/>
+      <c t="s" r="E342" s="7">
+        <v>347</v>
+      </c>
+      <c r="F342" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G342" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H342" s="8">
+        <v>49</v>
+      </c>
+      <c t="s" r="I342" s="7">
+        <v>23</v>
+      </c>
+      <c t="s" r="J342" s="7">
+        <v>114</v>
+      </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c r="M342" s="7"/>
@@ -11774,7 +11801,7 @@
         <v>13</v>
       </c>
       <c r="B343" s="7">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c t="s" r="C343" s="7">
         <v>14</v>
@@ -11787,50 +11814,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>191</v>
+        <v>121</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>306</v>
+        <v>52</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c r="M343" s="7"/>
     </row>
     <row r="344" ht="14.25" customHeight="1">
-      <c t="s" r="A344" s="6">
-        <v>13</v>
-      </c>
-      <c r="B344" s="7">
-        <v>629</v>
-      </c>
-      <c t="s" r="C344" s="7">
-        <v>14</v>
-      </c>
+      <c r="A344" s="6"/>
+      <c r="B344" s="7"/>
+      <c r="C344" s="7"/>
       <c r="D344" s="7"/>
-      <c t="s" r="E344" s="7">
-        <v>347</v>
-      </c>
-      <c r="F344" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G344" s="8">
-        <v>49</v>
-      </c>
-      <c t="s" r="H344" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I344" s="7">
-        <v>119</v>
-      </c>
-      <c t="s" r="J344" s="7">
-        <v>112</v>
-      </c>
+      <c r="E344" s="7"/>
+      <c r="F344" s="7"/>
+      <c r="G344" s="8"/>
+      <c r="H344" s="8"/>
+      <c r="I344" s="7"/>
+      <c r="J344" s="7"/>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c r="M344" s="7"/>
@@ -11840,14 +11849,14 @@
         <v>13</v>
       </c>
       <c r="B345" s="7">
-        <v>636</v>
+        <v>809</v>
       </c>
       <c t="s" r="C345" s="7">
         <v>14</v>
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -11856,13 +11865,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>49</v>
+        <v>349</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>113</v>
+        <v>213</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -11873,45 +11882,63 @@
         <v>13</v>
       </c>
       <c r="B346" s="7">
-        <v>633</v>
+        <v>808</v>
       </c>
       <c t="s" r="C346" s="7">
         <v>14</v>
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>49</v>
+        <v>349</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c r="M346" s="7"/>
     </row>
     <row r="347" ht="14.25" customHeight="1">
-      <c r="A347" s="6"/>
-      <c r="B347" s="7"/>
-      <c r="C347" s="7"/>
+      <c t="s" r="A347" s="6">
+        <v>13</v>
+      </c>
+      <c r="B347" s="7">
+        <v>876</v>
+      </c>
+      <c t="s" r="C347" s="7">
+        <v>14</v>
+      </c>
       <c r="D347" s="7"/>
-      <c r="E347" s="7"/>
-      <c r="F347" s="7"/>
-      <c r="G347" s="8"/>
-      <c r="H347" s="8"/>
-      <c r="I347" s="7"/>
-      <c r="J347" s="7"/>
+      <c t="s" r="E347" s="7">
+        <v>348</v>
+      </c>
+      <c r="F347" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G347" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H347" s="8">
+        <v>350</v>
+      </c>
+      <c t="s" r="I347" s="7">
+        <v>103</v>
+      </c>
+      <c t="s" r="J347" s="7">
+        <v>93</v>
+      </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c r="M347" s="7"/>
@@ -11921,7 +11948,7 @@
         <v>13</v>
       </c>
       <c r="B348" s="7">
-        <v>809</v>
+        <v>877</v>
       </c>
       <c t="s" r="C348" s="7">
         <v>14</v>
@@ -11934,16 +11961,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>16</v>
+        <v>350</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>349</v>
+        <v>16</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>212</v>
+        <v>260</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -11954,7 +11981,7 @@
         <v>13</v>
       </c>
       <c r="B349" s="7">
-        <v>808</v>
+        <v>168</v>
       </c>
       <c t="s" r="C349" s="7">
         <v>14</v>
@@ -11967,50 +11994,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>349</v>
+        <v>16</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>50</v>
+        <v>232</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>101</v>
+        <v>29</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c r="M349" s="7"/>
     </row>
     <row r="350" ht="15" customHeight="1">
-      <c t="s" r="A350" s="6">
-        <v>13</v>
-      </c>
-      <c r="B350" s="7">
-        <v>876</v>
-      </c>
-      <c t="s" r="C350" s="7">
-        <v>14</v>
-      </c>
+      <c r="A350" s="6"/>
+      <c r="B350" s="7"/>
+      <c r="C350" s="7"/>
       <c r="D350" s="7"/>
-      <c t="s" r="E350" s="7">
-        <v>348</v>
-      </c>
-      <c r="F350" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G350" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H350" s="8">
-        <v>350</v>
-      </c>
-      <c t="s" r="I350" s="7">
-        <v>102</v>
-      </c>
-      <c t="s" r="J350" s="7">
-        <v>92</v>
-      </c>
+      <c r="E350" s="7"/>
+      <c r="F350" s="7"/>
+      <c r="G350" s="8"/>
+      <c r="H350" s="8"/>
+      <c r="I350" s="7"/>
+      <c r="J350" s="7"/>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c r="M350" s="7"/>
@@ -12020,29 +12029,29 @@
         <v>13</v>
       </c>
       <c r="B351" s="7">
-        <v>877</v>
+        <v>127</v>
       </c>
       <c t="s" r="C351" s="7">
         <v>14</v>
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>350</v>
+        <v>17</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>136</v>
+        <v>352</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>258</v>
+        <v>306</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12053,14 +12062,14 @@
         <v>13</v>
       </c>
       <c r="B352" s="7">
-        <v>168</v>
+        <v>335</v>
       </c>
       <c t="s" r="C352" s="7">
         <v>14</v>
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12069,29 +12078,47 @@
         <v>16</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>229</v>
+        <v>80</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c r="M352" s="7"/>
     </row>
     <row r="353" ht="14.25" customHeight="1">
-      <c r="A353" s="6"/>
-      <c r="B353" s="7"/>
-      <c r="C353" s="7"/>
+      <c t="s" r="A353" s="6">
+        <v>13</v>
+      </c>
+      <c r="B353" s="7">
+        <v>766</v>
+      </c>
+      <c t="s" r="C353" s="7">
+        <v>14</v>
+      </c>
       <c r="D353" s="7"/>
-      <c r="E353" s="7"/>
-      <c r="F353" s="7"/>
-      <c r="G353" s="8"/>
-      <c r="H353" s="8"/>
-      <c r="I353" s="7"/>
-      <c r="J353" s="7"/>
+      <c t="s" r="E353" s="7">
+        <v>351</v>
+      </c>
+      <c r="F353" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G353" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H353" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I353" s="7">
+        <v>23</v>
+      </c>
+      <c t="s" r="J353" s="7">
+        <v>62</v>
+      </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c r="M353" s="7"/>
@@ -12101,7 +12128,7 @@
         <v>13</v>
       </c>
       <c r="B354" s="7">
-        <v>127</v>
+        <v>767</v>
       </c>
       <c t="s" r="C354" s="7">
         <v>14</v>
@@ -12114,16 +12141,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>352</v>
+        <v>182</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>306</v>
+        <v>28</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12134,7 +12161,7 @@
         <v>13</v>
       </c>
       <c r="B355" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c t="s" r="C355" s="7">
         <v>14</v>
@@ -12147,50 +12174,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c r="M355" s="7"/>
     </row>
     <row r="356" ht="14.25" customHeight="1">
-      <c t="s" r="A356" s="6">
-        <v>13</v>
-      </c>
-      <c r="B356" s="7">
-        <v>766</v>
-      </c>
-      <c t="s" r="C356" s="7">
-        <v>14</v>
-      </c>
+      <c r="A356" s="6"/>
+      <c r="B356" s="7"/>
+      <c r="C356" s="7"/>
       <c r="D356" s="7"/>
-      <c t="s" r="E356" s="7">
-        <v>351</v>
-      </c>
-      <c r="F356" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G356" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="H356" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I356" s="7">
-        <v>23</v>
-      </c>
-      <c t="s" r="J356" s="7">
-        <v>62</v>
-      </c>
+      <c r="E356" s="7"/>
+      <c r="F356" s="7"/>
+      <c r="G356" s="8"/>
+      <c r="H356" s="8"/>
+      <c r="I356" s="7"/>
+      <c r="J356" s="7"/>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c r="M356" s="7"/>
@@ -12200,29 +12209,29 @@
         <v>13</v>
       </c>
       <c r="B357" s="7">
-        <v>767</v>
+        <v>121</v>
       </c>
       <c t="s" r="C357" s="7">
         <v>14</v>
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>181</v>
+        <v>346</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>28</v>
+        <v>352</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12233,45 +12242,63 @@
         <v>13</v>
       </c>
       <c r="B358" s="7">
-        <v>338</v>
+        <v>1813</v>
       </c>
       <c t="s" r="C358" s="7">
         <v>14</v>
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>16</v>
+        <v>300</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c r="M358" s="7"/>
     </row>
     <row r="359" ht="14.25" customHeight="1">
-      <c r="A359" s="6"/>
-      <c r="B359" s="7"/>
-      <c r="C359" s="7"/>
+      <c t="s" r="A359" s="6">
+        <v>13</v>
+      </c>
+      <c r="B359" s="7">
+        <v>1814</v>
+      </c>
+      <c t="s" r="C359" s="7">
+        <v>14</v>
+      </c>
       <c r="D359" s="7"/>
-      <c r="E359" s="7"/>
-      <c r="F359" s="7"/>
-      <c r="G359" s="8"/>
-      <c r="H359" s="8"/>
-      <c r="I359" s="7"/>
-      <c r="J359" s="7"/>
+      <c t="s" r="E359" s="7">
+        <v>353</v>
+      </c>
+      <c r="F359" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G359" s="8">
+        <v>300</v>
+      </c>
+      <c t="s" r="H359" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I359" s="7">
+        <v>147</v>
+      </c>
+      <c t="s" r="J359" s="7">
+        <v>90</v>
+      </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c r="M359" s="7"/>
@@ -12281,7 +12308,7 @@
         <v>13</v>
       </c>
       <c r="B360" s="7">
-        <v>121</v>
+        <v>394</v>
       </c>
       <c t="s" r="C360" s="7">
         <v>14</v>
@@ -12294,16 +12321,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>346</v>
+        <v>63</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>352</v>
+        <v>202</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12314,7 +12341,7 @@
         <v>13</v>
       </c>
       <c r="B361" s="7">
-        <v>1813</v>
+        <v>395</v>
       </c>
       <c t="s" r="C361" s="7">
         <v>14</v>
@@ -12327,16 +12354,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>300</v>
+        <v>16</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>36</v>
+        <v>354</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12347,7 +12374,7 @@
         <v>13</v>
       </c>
       <c r="B362" s="7">
-        <v>1814</v>
+        <v>160</v>
       </c>
       <c t="s" r="C362" s="7">
         <v>14</v>
@@ -12360,16 +12387,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>300</v>
+        <v>16</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>146</v>
+        <v>244</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>89</v>
+        <v>345</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12380,7 +12407,7 @@
         <v>13</v>
       </c>
       <c r="B363" s="7">
-        <v>394</v>
+        <v>169</v>
       </c>
       <c t="s" r="C363" s="7">
         <v>14</v>
@@ -12393,50 +12420,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>63</v>
+        <v>355</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>201</v>
+        <v>356</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c r="M363" s="7"/>
     </row>
     <row r="364" ht="14.25" customHeight="1">
-      <c t="s" r="A364" s="6">
-        <v>13</v>
-      </c>
-      <c r="B364" s="7">
-        <v>395</v>
-      </c>
-      <c t="s" r="C364" s="7">
-        <v>14</v>
-      </c>
+      <c r="A364" s="6"/>
+      <c r="B364" s="7"/>
+      <c r="C364" s="7"/>
       <c r="D364" s="7"/>
-      <c t="s" r="E364" s="7">
-        <v>353</v>
-      </c>
-      <c r="F364" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G364" s="8">
-        <v>61</v>
-      </c>
-      <c t="s" r="H364" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I364" s="7">
-        <v>91</v>
-      </c>
-      <c t="s" r="J364" s="7">
-        <v>354</v>
-      </c>
+      <c r="E364" s="7"/>
+      <c r="F364" s="7"/>
+      <c r="G364" s="8"/>
+      <c r="H364" s="8"/>
+      <c r="I364" s="7"/>
+      <c r="J364" s="7"/>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c r="M364" s="7"/>
@@ -12446,29 +12455,29 @@
         <v>13</v>
       </c>
       <c r="B365" s="7">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c t="s" r="C365" s="7">
         <v>14</v>
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F365" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>241</v>
+        <v>267</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>345</v>
+        <v>119</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12479,45 +12488,63 @@
         <v>13</v>
       </c>
       <c r="B366" s="7">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c t="s" r="C366" s="7">
         <v>14</v>
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F366" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>355</v>
+        <v>32</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c r="M366" s="7"/>
     </row>
     <row r="367" ht="14.25" customHeight="1">
-      <c r="A367" s="6"/>
-      <c r="B367" s="7"/>
-      <c r="C367" s="7"/>
+      <c t="s" r="A367" s="6">
+        <v>13</v>
+      </c>
+      <c r="B367" s="7">
+        <v>525</v>
+      </c>
+      <c t="s" r="C367" s="7">
+        <v>14</v>
+      </c>
       <c r="D367" s="7"/>
-      <c r="E367" s="7"/>
-      <c r="F367" s="7"/>
-      <c r="G367" s="8"/>
-      <c r="H367" s="8"/>
-      <c r="I367" s="7"/>
-      <c r="J367" s="7"/>
+      <c t="s" r="E367" s="7">
+        <v>357</v>
+      </c>
+      <c r="F367" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G367" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H367" s="8">
+        <v>49</v>
+      </c>
+      <c t="s" r="I367" s="7">
+        <v>81</v>
+      </c>
+      <c t="s" r="J367" s="7">
+        <v>72</v>
+      </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c r="M367" s="7"/>
@@ -12527,7 +12554,7 @@
         <v>13</v>
       </c>
       <c r="B368" s="7">
-        <v>125</v>
+        <v>528</v>
       </c>
       <c t="s" r="C368" s="7">
         <v>14</v>
@@ -12540,16 +12567,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>265</v>
+        <v>341</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>118</v>
+        <v>359</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12560,7 +12587,7 @@
         <v>13</v>
       </c>
       <c r="B369" s="7">
-        <v>128</v>
+        <v>1157</v>
       </c>
       <c t="s" r="C369" s="7">
         <v>14</v>
@@ -12573,16 +12600,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>32</v>
+        <v>314</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>358</v>
+        <v>235</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12593,7 +12620,7 @@
         <v>13</v>
       </c>
       <c r="B370" s="7">
-        <v>525</v>
+        <v>1156</v>
       </c>
       <c t="s" r="C370" s="7">
         <v>14</v>
@@ -12606,50 +12633,32 @@
         <v>320</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c r="M370" s="7"/>
     </row>
     <row r="371" ht="14.25" customHeight="1">
-      <c t="s" r="A371" s="6">
-        <v>13</v>
-      </c>
-      <c r="B371" s="7">
-        <v>528</v>
-      </c>
-      <c t="s" r="C371" s="7">
-        <v>14</v>
-      </c>
+      <c r="A371" s="6"/>
+      <c r="B371" s="7"/>
+      <c r="C371" s="7"/>
       <c r="D371" s="7"/>
-      <c t="s" r="E371" s="7">
-        <v>357</v>
-      </c>
-      <c r="F371" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G371" s="8">
-        <v>49</v>
-      </c>
-      <c t="s" r="H371" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I371" s="7">
-        <v>341</v>
-      </c>
-      <c t="s" r="J371" s="7">
-        <v>359</v>
-      </c>
+      <c r="E371" s="7"/>
+      <c r="F371" s="7"/>
+      <c r="G371" s="8"/>
+      <c r="H371" s="8"/>
+      <c r="I371" s="7"/>
+      <c r="J371" s="7"/>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c r="M371" s="7"/>
@@ -12659,29 +12668,29 @@
         <v>13</v>
       </c>
       <c r="B372" s="7">
-        <v>1157</v>
+        <v>893</v>
       </c>
       <c t="s" r="C372" s="7">
         <v>14</v>
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F372" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>16</v>
+        <v>193</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>314</v>
+        <v>240</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12692,45 +12701,63 @@
         <v>13</v>
       </c>
       <c r="B373" s="7">
-        <v>1156</v>
+        <v>894</v>
       </c>
       <c t="s" r="C373" s="7">
         <v>14</v>
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F373" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>16</v>
+        <v>193</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>129</v>
+        <v>359</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c r="M373" s="7"/>
     </row>
     <row r="374" ht="14.25" customHeight="1">
-      <c r="A374" s="6"/>
-      <c r="B374" s="7"/>
-      <c r="C374" s="7"/>
+      <c t="s" r="A374" s="6">
+        <v>13</v>
+      </c>
+      <c r="B374" s="7">
+        <v>1801</v>
+      </c>
+      <c t="s" r="C374" s="7">
+        <v>14</v>
+      </c>
       <c r="D374" s="7"/>
-      <c r="E374" s="7"/>
-      <c r="F374" s="7"/>
-      <c r="G374" s="8"/>
-      <c r="H374" s="8"/>
-      <c r="I374" s="7"/>
-      <c r="J374" s="7"/>
+      <c t="s" r="E374" s="7">
+        <v>360</v>
+      </c>
+      <c r="F374" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G374" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H374" s="8">
+        <v>361</v>
+      </c>
+      <c t="s" r="I374" s="7">
+        <v>106</v>
+      </c>
+      <c t="s" r="J374" s="7">
+        <v>69</v>
+      </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c r="M374" s="7"/>
@@ -12740,7 +12767,7 @@
         <v>13</v>
       </c>
       <c r="B375" s="7">
-        <v>893</v>
+        <v>1802</v>
       </c>
       <c t="s" r="C375" s="7">
         <v>14</v>
@@ -12753,50 +12780,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>16</v>
+        <v>361</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>192</v>
+        <v>16</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>213</v>
+        <v>346</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c r="M375" s="7"/>
     </row>
     <row r="376" ht="14.25" customHeight="1">
-      <c t="s" r="A376" s="6">
-        <v>13</v>
-      </c>
-      <c r="B376" s="7">
-        <v>894</v>
-      </c>
-      <c t="s" r="C376" s="7">
-        <v>14</v>
-      </c>
+      <c r="A376" s="6"/>
+      <c r="B376" s="7"/>
+      <c r="C376" s="7"/>
       <c r="D376" s="7"/>
-      <c t="s" r="E376" s="7">
-        <v>360</v>
-      </c>
-      <c r="F376" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G376" s="8">
-        <v>192</v>
-      </c>
-      <c t="s" r="H376" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I376" s="7">
-        <v>127</v>
-      </c>
-      <c t="s" r="J376" s="7">
-        <v>359</v>
-      </c>
+      <c r="E376" s="7"/>
+      <c r="F376" s="7"/>
+      <c r="G376" s="8"/>
+      <c r="H376" s="8"/>
+      <c r="I376" s="7"/>
+      <c r="J376" s="7"/>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c r="M376" s="7"/>
@@ -12806,14 +12815,14 @@
         <v>13</v>
       </c>
       <c r="B377" s="7">
-        <v>1801</v>
+        <v>855</v>
       </c>
       <c t="s" r="C377" s="7">
         <v>14</v>
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -12822,13 +12831,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>361</v>
+        <v>165</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>69</v>
+        <v>224</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12839,45 +12848,63 @@
         <v>13</v>
       </c>
       <c r="B378" s="7">
-        <v>1802</v>
+        <v>854</v>
       </c>
       <c t="s" r="C378" s="7">
         <v>14</v>
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>361</v>
+        <v>165</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>246</v>
+        <v>36</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>346</v>
+        <v>63</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c r="M378" s="7"/>
     </row>
     <row r="379" ht="14.25" customHeight="1">
-      <c r="A379" s="6"/>
-      <c r="B379" s="7"/>
-      <c r="C379" s="7"/>
+      <c t="s" r="A379" s="6">
+        <v>13</v>
+      </c>
+      <c r="B379" s="7">
+        <v>262</v>
+      </c>
+      <c t="s" r="C379" s="7">
+        <v>14</v>
+      </c>
       <c r="D379" s="7"/>
-      <c r="E379" s="7"/>
-      <c r="F379" s="7"/>
-      <c r="G379" s="8"/>
-      <c r="H379" s="8"/>
-      <c r="I379" s="7"/>
-      <c r="J379" s="7"/>
+      <c t="s" r="E379" s="7">
+        <v>362</v>
+      </c>
+      <c r="F379" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G379" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H379" s="8">
+        <v>363</v>
+      </c>
+      <c t="s" r="I379" s="7">
+        <v>275</v>
+      </c>
+      <c t="s" r="J379" s="7">
+        <v>259</v>
+      </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c r="M379" s="7"/>
@@ -12887,7 +12914,7 @@
         <v>13</v>
       </c>
       <c r="B380" s="7">
-        <v>855</v>
+        <v>263</v>
       </c>
       <c t="s" r="C380" s="7">
         <v>14</v>
@@ -12900,16 +12927,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>164</v>
+        <v>16</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>221</v>
+        <v>364</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -12917,10 +12944,10 @@
     </row>
     <row r="381" ht="14.25" customHeight="1">
       <c t="s" r="A381" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B381" s="7">
-        <v>854</v>
+        <v>828</v>
       </c>
       <c t="s" r="C381" s="7">
         <v>14</v>
@@ -12933,50 +12960,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>164</v>
+        <v>16</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>36</v>
+        <v>210</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>63</v>
+        <v>179</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c r="M381" s="7"/>
     </row>
     <row r="382" ht="14.25" customHeight="1">
-      <c t="s" r="A382" s="6">
-        <v>13</v>
-      </c>
-      <c r="B382" s="7">
-        <v>262</v>
-      </c>
-      <c t="s" r="C382" s="7">
-        <v>14</v>
-      </c>
+      <c r="A382" s="6"/>
+      <c r="B382" s="7"/>
+      <c r="C382" s="7"/>
       <c r="D382" s="7"/>
-      <c t="s" r="E382" s="7">
-        <v>362</v>
-      </c>
-      <c r="F382" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G382" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H382" s="8">
-        <v>363</v>
-      </c>
-      <c t="s" r="I382" s="7">
-        <v>274</v>
-      </c>
-      <c t="s" r="J382" s="7">
-        <v>257</v>
-      </c>
+      <c r="E382" s="7"/>
+      <c r="F382" s="7"/>
+      <c r="G382" s="8"/>
+      <c r="H382" s="8"/>
+      <c r="I382" s="7"/>
+      <c r="J382" s="7"/>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c r="M382" s="7"/>
@@ -12986,29 +12995,29 @@
         <v>13</v>
       </c>
       <c r="B383" s="7">
-        <v>263</v>
+        <v>981</v>
       </c>
       <c t="s" r="C383" s="7">
         <v>14</v>
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>363</v>
+        <v>124</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>116</v>
+        <v>352</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>364</v>
+        <v>223</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13016,48 +13025,66 @@
     </row>
     <row r="384" ht="14.25" customHeight="1">
       <c t="s" r="A384" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B384" s="7">
-        <v>828</v>
+        <v>137</v>
       </c>
       <c t="s" r="C384" s="7">
         <v>14</v>
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>209</v>
+        <v>34</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c r="M384" s="7"/>
     </row>
     <row r="385" ht="15" customHeight="1">
-      <c r="A385" s="6"/>
-      <c r="B385" s="7"/>
-      <c r="C385" s="7"/>
+      <c t="s" r="A385" s="6">
+        <v>13</v>
+      </c>
+      <c r="B385" s="7">
+        <v>280</v>
+      </c>
+      <c t="s" r="C385" s="7">
+        <v>14</v>
+      </c>
       <c r="D385" s="7"/>
-      <c r="E385" s="7"/>
-      <c r="F385" s="7"/>
-      <c r="G385" s="8"/>
-      <c r="H385" s="8"/>
-      <c r="I385" s="7"/>
-      <c r="J385" s="7"/>
+      <c t="s" r="E385" s="7">
+        <v>365</v>
+      </c>
+      <c r="F385" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G385" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H385" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I385" s="7">
+        <v>90</v>
+      </c>
+      <c t="s" r="J385" s="7">
+        <v>225</v>
+      </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c r="M385" s="7"/>
@@ -13067,7 +13094,7 @@
         <v>13</v>
       </c>
       <c r="B386" s="7">
-        <v>981</v>
+        <v>281</v>
       </c>
       <c t="s" r="C386" s="7">
         <v>14</v>
@@ -13080,16 +13107,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>352</v>
+        <v>28</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>220</v>
+        <v>117</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13100,7 +13127,7 @@
         <v>13</v>
       </c>
       <c r="B387" s="7">
-        <v>137</v>
+        <v>858</v>
       </c>
       <c t="s" r="C387" s="7">
         <v>14</v>
@@ -13113,16 +13140,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>16</v>
+        <v>366</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>34</v>
+        <v>367</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>146</v>
+        <v>227</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13130,10 +13157,10 @@
     </row>
     <row r="388" ht="14.25" customHeight="1">
       <c t="s" r="A388" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B388" s="7">
-        <v>280</v>
+        <v>859</v>
       </c>
       <c t="s" r="C388" s="7">
         <v>14</v>
@@ -13146,50 +13173,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>16</v>
+        <v>366</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>89</v>
+        <v>368</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>222</v>
+        <v>369</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c r="M388" s="7"/>
     </row>
     <row r="389" ht="14.25" customHeight="1">
-      <c t="s" r="A389" s="6">
-        <v>13</v>
-      </c>
-      <c r="B389" s="7">
-        <v>281</v>
-      </c>
-      <c t="s" r="C389" s="7">
-        <v>14</v>
-      </c>
+      <c r="A389" s="6"/>
+      <c r="B389" s="7"/>
+      <c r="C389" s="7"/>
       <c r="D389" s="7"/>
-      <c t="s" r="E389" s="7">
-        <v>365</v>
-      </c>
-      <c r="F389" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G389" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="H389" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I389" s="7">
-        <v>28</v>
-      </c>
-      <c t="s" r="J389" s="7">
-        <v>116</v>
-      </c>
+      <c r="E389" s="7"/>
+      <c r="F389" s="7"/>
+      <c r="G389" s="8"/>
+      <c r="H389" s="8"/>
+      <c r="I389" s="7"/>
+      <c r="J389" s="7"/>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c r="M389" s="7"/>
@@ -13199,29 +13208,29 @@
         <v>13</v>
       </c>
       <c r="B390" s="7">
-        <v>858</v>
+        <v>901</v>
       </c>
       <c t="s" r="C390" s="7">
         <v>14</v>
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F390" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>366</v>
+        <v>283</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>367</v>
+        <v>145</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>224</v>
+        <v>23</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13229,32 +13238,32 @@
     </row>
     <row r="391" ht="14.25" customHeight="1">
       <c t="s" r="A391" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B391" s="7">
-        <v>859</v>
+        <v>902</v>
       </c>
       <c t="s" r="C391" s="7">
         <v>14</v>
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F391" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>366</v>
+        <v>283</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>368</v>
+        <v>127</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>369</v>
+        <v>186</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13287,22 +13296,22 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F393" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13320,7 +13329,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F394" s="7">
         <v>330</v>
@@ -13353,7 +13362,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F395" s="7">
         <v>330</v>
@@ -13362,13 +13371,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13386,13 +13395,13 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F396" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>24</v>
@@ -13401,7 +13410,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13434,22 +13443,22 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F398" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13467,7 +13476,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F399" s="7">
         <v>330</v>
@@ -13482,7 +13491,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13500,7 +13509,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F400" s="7">
         <v>330</v>
@@ -13512,7 +13521,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>66</v>
@@ -13548,7 +13557,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
@@ -13560,7 +13569,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>71</v>
@@ -13577,11 +13586,11 @@
         <v>2866</v>
       </c>
       <c t="s" r="C403" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
@@ -13590,13 +13599,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13610,17 +13619,17 @@
         <v>2867</v>
       </c>
       <c t="s" r="C404" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>24</v>
@@ -13662,19 +13671,19 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="H406" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="J406" s="7">
         <v>341</v>
@@ -13695,7 +13704,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
@@ -13707,10 +13716,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13728,7 +13737,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
@@ -13740,10 +13749,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13776,22 +13785,22 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F410" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -13824,7 +13833,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
@@ -13833,13 +13842,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="I412" s="7">
         <v>329</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -13872,7 +13881,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
@@ -13881,13 +13890,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c t="s" r="I414" s="7">
         <v>317</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -13905,22 +13914,22 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -13928,7 +13937,7 @@
     </row>
     <row r="416" ht="15.75" customHeight="1">
       <c t="s" r="A416" s="9">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B416" s="9"/>
       <c r="C416" s="9"/>
@@ -13948,7 +13957,7 @@
     <row r="417" ht="65.25" customHeight="1"/>
     <row r="418" ht="16.5" customHeight="1">
       <c t="s" r="A418" s="10">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B418" s="10"/>
       <c r="C418" s="10"/>
@@ -13961,7 +13970,7 @@
       <c r="J418" s="10"/>
       <c r="K418" s="10"/>
       <c t="s" r="L418" s="11">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M418" s="11"/>
       <c r="N418" s="11"/>

--- a/Data/FlightPlan/FPL_07OCT26.xlsx
+++ b/Data/FlightPlan/FPL_07OCT26.xlsx
@@ -656,186 +656,183 @@
     <t>13:35</t>
   </si>
   <si>
-    <t>11:35</t>
+    <t>HGH</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>SIN</t>
   </si>
   <si>
     <t>14:15</t>
   </si>
   <si>
-    <t>HGH</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
     <t>17:40</t>
   </si>
   <si>
@@ -1175,7 +1172,7 @@
     <t>Total Record(s): 337</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 07, 2026 02:25</t>
+    <t xml:space="preserve">Generated on  Oct 07, 2026 02:54</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -5482,11 +5479,11 @@
         <v>214</v>
       </c>
       <c t="s" r="K133" s="7">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -5510,13 +5507,13 @@
         <v>171</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c t="s" r="I134" s="7">
         <v>43</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5540,7 +5537,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c t="s" r="H135" s="8">
         <v>171</v>
@@ -5549,7 +5546,7 @@
         <v>195</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5579,10 +5576,10 @@
         <v>124</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5615,7 +5612,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5648,7 +5645,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5663,7 +5660,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5681,7 +5678,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5696,7 +5693,7 @@
         <v>145</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5714,7 +5711,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5747,7 +5744,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5762,7 +5759,7 @@
         <v>182</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5780,7 +5777,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5813,7 +5810,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5822,7 +5819,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c t="s" r="I144" s="7">
         <v>109</v>
@@ -5846,22 +5843,22 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
+        <v>224</v>
+      </c>
+      <c t="s" r="H145" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I145" s="7">
+        <v>225</v>
+      </c>
+      <c t="s" r="J145" s="7">
         <v>226</v>
-      </c>
-      <c t="s" r="H145" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I145" s="7">
-        <v>227</v>
-      </c>
-      <c t="s" r="J145" s="7">
-        <v>228</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5894,7 +5891,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -5909,7 +5906,7 @@
         <v>71</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -5927,7 +5924,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -5960,16 +5957,16 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
+        <v>227</v>
+      </c>
+      <c r="F149" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G149" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H149" s="8">
         <v>229</v>
-      </c>
-      <c r="F149" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G149" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H149" s="8">
-        <v>231</v>
       </c>
       <c t="s" r="I149" s="7">
         <v>116</v>
@@ -5993,13 +5990,13 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
+        <v>227</v>
+      </c>
+      <c r="F150" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G150" s="8">
         <v>229</v>
-      </c>
-      <c r="F150" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G150" s="8">
-        <v>231</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>16</v>
@@ -6026,7 +6023,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6059,7 +6056,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6071,7 +6068,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c t="s" r="J152" s="7">
         <v>205</v>
@@ -6107,7 +6104,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6122,7 +6119,7 @@
         <v>192</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6140,7 +6137,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6173,7 +6170,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6188,7 +6185,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6221,19 +6218,19 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
+        <v>234</v>
+      </c>
+      <c r="F158" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G158" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H158" s="8">
+        <v>235</v>
+      </c>
+      <c t="s" r="I158" s="7">
         <v>236</v>
-      </c>
-      <c r="F158" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G158" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H158" s="8">
-        <v>237</v>
-      </c>
-      <c t="s" r="I158" s="7">
-        <v>238</v>
       </c>
       <c t="s" r="J158" s="7">
         <v>191</v>
@@ -6254,22 +6251,22 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
+        <v>235</v>
+      </c>
+      <c t="s" r="H159" s="8">
+        <v>229</v>
+      </c>
+      <c t="s" r="I159" s="7">
         <v>237</v>
       </c>
-      <c t="s" r="H159" s="8">
-        <v>231</v>
-      </c>
-      <c t="s" r="I159" s="7">
-        <v>239</v>
-      </c>
       <c t="s" r="J159" s="7">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6287,22 +6284,22 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6320,13 +6317,13 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>16</v>
@@ -6353,7 +6350,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6386,7 +6383,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6401,7 +6398,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6419,7 +6416,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6428,13 +6425,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6452,19 +6449,19 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c t="s" r="J165" s="7">
         <v>162</v>
@@ -6500,7 +6497,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6533,7 +6530,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6545,7 +6542,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c t="s" r="J168" s="7">
         <v>116</v>
@@ -6566,7 +6563,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6581,7 +6578,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6599,7 +6596,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6614,7 +6611,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6647,7 +6644,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6659,7 +6656,7 @@
         <v>171</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>76</v>
@@ -6680,7 +6677,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6713,7 +6710,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6725,7 +6722,7 @@
         <v>171</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>172</v>
@@ -6746,7 +6743,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6761,7 +6758,7 @@
         <v>200</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6779,7 +6776,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6794,7 +6791,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6812,7 +6809,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6824,10 +6821,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6860,7 +6857,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6875,7 +6872,7 @@
         <v>163</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -6893,7 +6890,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -6908,7 +6905,7 @@
         <v>119</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -6926,7 +6923,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -6938,7 +6935,7 @@
         <v>171</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>214</v>
@@ -6959,7 +6956,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -6992,7 +6989,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7001,13 +6998,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c t="s" r="I183" s="7">
         <v>194</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7025,13 +7022,13 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>17</v>
@@ -7040,7 +7037,7 @@
         <v>117</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7073,7 +7070,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7082,7 +7079,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c t="s" r="I186" s="7">
         <v>100</v>
@@ -7106,13 +7103,13 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>17</v>
@@ -7139,7 +7136,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7172,7 +7169,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7205,7 +7202,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7214,7 +7211,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c t="s" r="I190" s="7">
         <v>183</v>
@@ -7253,7 +7250,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7265,7 +7262,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c t="s" r="J192" s="7">
         <v>57</v>
@@ -7286,7 +7283,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7319,7 +7316,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7352,7 +7349,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7385,7 +7382,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7418,7 +7415,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7451,7 +7448,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7466,7 +7463,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7499,7 +7496,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7511,10 +7508,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7532,7 +7529,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7565,7 +7562,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7574,10 +7571,10 @@
         <v>49</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>121</v>
@@ -7598,13 +7595,13 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>49</v>
@@ -7646,22 +7643,22 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
+        <v>268</v>
+      </c>
+      <c r="F205" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G205" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H205" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I205" s="7">
+        <v>269</v>
+      </c>
+      <c t="s" r="J205" s="7">
         <v>270</v>
-      </c>
-      <c r="F205" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G205" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H205" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I205" s="7">
-        <v>271</v>
-      </c>
-      <c t="s" r="J205" s="7">
-        <v>272</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7679,7 +7676,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7712,7 +7709,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7745,7 +7742,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7778,7 +7775,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7811,7 +7808,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7859,7 +7856,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7868,13 +7865,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c t="s" r="I212" s="7">
         <v>145</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>216</v>
+        <v>273</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7892,13 +7889,13 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>16</v>
@@ -7925,7 +7922,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -7937,10 +7934,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I214" s="7">
+        <v>274</v>
+      </c>
+      <c t="s" r="J214" s="7">
         <v>275</v>
-      </c>
-      <c t="s" r="J214" s="7">
-        <v>276</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -7958,7 +7955,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -7970,7 +7967,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c t="s" r="J215" s="7">
         <v>168</v>
@@ -8006,7 +8003,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8018,7 +8015,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c t="s" r="J217" s="7">
         <v>214</v>
@@ -8039,7 +8036,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8048,7 +8045,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c t="s" r="I218" s="7">
         <v>128</v>
@@ -8072,13 +8069,13 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>17</v>
@@ -8105,7 +8102,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8117,10 +8114,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8153,7 +8150,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8168,7 +8165,7 @@
         <v>211</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8186,7 +8183,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8198,7 +8195,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>71</v>
@@ -8234,7 +8231,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8267,7 +8264,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8300,22 +8297,22 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
+        <v>281</v>
+      </c>
+      <c r="F227" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G227" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H227" s="8">
         <v>282</v>
-      </c>
-      <c r="F227" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G227" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H227" s="8">
-        <v>283</v>
       </c>
       <c t="s" r="I227" s="7">
         <v>89</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8333,22 +8330,22 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
+        <v>281</v>
+      </c>
+      <c r="F228" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G228" s="8">
         <v>282</v>
       </c>
-      <c r="F228" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G228" s="8">
-        <v>283</v>
-      </c>
       <c t="s" r="H228" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8366,7 +8363,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8375,10 +8372,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H229" s="8">
+        <v>284</v>
+      </c>
+      <c t="s" r="I229" s="7">
         <v>285</v>
-      </c>
-      <c t="s" r="I229" s="7">
-        <v>286</v>
       </c>
       <c t="s" r="J229" s="7">
         <v>210</v>
@@ -8399,22 +8396,22 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I230" s="7">
+        <v>286</v>
+      </c>
+      <c t="s" r="J230" s="7">
         <v>287</v>
-      </c>
-      <c t="s" r="J230" s="7">
-        <v>288</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8447,7 +8444,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8459,7 +8456,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>79</v>
@@ -8480,7 +8477,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8492,10 +8489,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8513,7 +8510,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8522,10 +8519,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>216</v>
+        <v>273</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>201</v>
@@ -8546,13 +8543,13 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>16</v>
@@ -8594,7 +8591,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8606,7 +8603,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>31</v>
@@ -8627,7 +8624,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8642,7 +8639,7 @@
         <v>139</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8660,7 +8657,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8675,7 +8672,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8693,7 +8690,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8702,13 +8699,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8726,13 +8723,13 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>16</v>
@@ -8759,7 +8756,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8768,13 +8765,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c t="s" r="I242" s="7">
         <v>151</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8792,22 +8789,22 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I243" s="7">
+        <v>296</v>
+      </c>
+      <c t="s" r="J243" s="7">
         <v>297</v>
-      </c>
-      <c t="s" r="J243" s="7">
-        <v>298</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8840,22 +8837,22 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
+        <v>298</v>
+      </c>
+      <c r="F245" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G245" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H245" s="8">
         <v>299</v>
-      </c>
-      <c r="F245" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G245" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H245" s="8">
-        <v>300</v>
       </c>
       <c t="s" r="I245" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -8873,13 +8870,13 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
+        <v>298</v>
+      </c>
+      <c r="F246" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G246" s="8">
         <v>299</v>
-      </c>
-      <c r="F246" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G246" s="8">
-        <v>300</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>16</v>
@@ -8906,7 +8903,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -8915,7 +8912,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c t="s" r="I247" s="7">
         <v>73</v>
@@ -8939,22 +8936,22 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
+        <v>301</v>
+      </c>
+      <c t="s" r="H248" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I248" s="7">
         <v>302</v>
       </c>
-      <c t="s" r="H248" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I248" s="7">
+      <c t="s" r="J248" s="7">
         <v>303</v>
-      </c>
-      <c t="s" r="J248" s="7">
-        <v>304</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -8987,7 +8984,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F250" s="7">
         <v>320</v>
@@ -8996,13 +8993,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9020,13 +9017,13 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F251" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>17</v>
@@ -9053,7 +9050,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F252" s="7">
         <v>320</v>
@@ -9086,7 +9083,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
@@ -9098,7 +9095,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c t="s" r="J253" s="7">
         <v>84</v>
@@ -9119,7 +9116,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F254" s="7">
         <v>320</v>
@@ -9128,13 +9125,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c t="s" r="I254" s="7">
         <v>68</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9152,22 +9149,22 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F255" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I255" s="7">
+        <v>307</v>
+      </c>
+      <c t="s" r="J255" s="7">
         <v>308</v>
-      </c>
-      <c t="s" r="J255" s="7">
-        <v>309</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9200,22 +9197,22 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
+        <v>309</v>
+      </c>
+      <c r="F257" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G257" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H257" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I257" s="7">
         <v>310</v>
       </c>
-      <c r="F257" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G257" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H257" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I257" s="7">
+      <c t="s" r="J257" s="7">
         <v>311</v>
-      </c>
-      <c t="s" r="J257" s="7">
-        <v>312</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9233,7 +9230,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9245,7 +9242,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>213</v>
@@ -9266,7 +9263,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9299,7 +9296,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9314,7 +9311,7 @@
         <v>167</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9347,7 +9344,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F262" s="7">
         <v>320</v>
@@ -9359,7 +9356,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c t="s" r="J262" s="7">
         <v>18</v>
@@ -9380,7 +9377,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F263" s="7">
         <v>320</v>
@@ -9392,7 +9389,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>147</v>
@@ -9413,7 +9410,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
@@ -9428,7 +9425,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9446,7 +9443,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
@@ -9458,10 +9455,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9494,7 +9491,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9503,13 +9500,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c t="s" r="I267" s="7">
         <v>57</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9527,22 +9524,22 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9560,7 +9557,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9593,7 +9590,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9641,7 +9638,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -9653,7 +9650,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c t="s" r="J272" s="7">
         <v>120</v>
@@ -9674,7 +9671,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
@@ -9686,7 +9683,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>36</v>
@@ -9707,7 +9704,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
@@ -9740,7 +9737,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -9755,7 +9752,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9773,7 +9770,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
@@ -9788,7 +9785,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9821,7 +9818,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -9833,10 +9830,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9854,7 +9851,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -9887,7 +9884,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -9902,7 +9899,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -9920,7 +9917,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -9932,7 +9929,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>34</v>
@@ -9953,7 +9950,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -9986,7 +9983,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10001,7 +9998,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10019,7 +10016,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10031,7 +10028,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>71</v>
@@ -10067,7 +10064,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10076,7 +10073,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c t="s" r="I286" s="7">
         <v>180</v>
@@ -10100,22 +10097,22 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10133,7 +10130,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -10142,7 +10139,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c t="s" r="I288" s="7">
         <v>45</v>
@@ -10166,13 +10163,13 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>16</v>
@@ -10214,7 +10211,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
@@ -10229,7 +10226,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10247,7 +10244,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -10259,7 +10256,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>120</v>
@@ -10280,7 +10277,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10292,7 +10289,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>42</v>
@@ -10313,7 +10310,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10346,7 +10343,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10355,10 +10352,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H295" s="8">
+        <v>327</v>
+      </c>
+      <c t="s" r="I295" s="7">
         <v>328</v>
-      </c>
-      <c t="s" r="I295" s="7">
-        <v>329</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>205</v>
@@ -10379,13 +10376,13 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>17</v>
@@ -10394,7 +10391,7 @@
         <v>196</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10427,22 +10424,22 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
+        <v>330</v>
+      </c>
+      <c r="F298" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G298" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H298" s="8">
+        <v>299</v>
+      </c>
+      <c t="s" r="I298" s="7">
         <v>331</v>
       </c>
-      <c r="F298" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G298" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H298" s="8">
-        <v>300</v>
-      </c>
-      <c t="s" r="I298" s="7">
+      <c t="s" r="J298" s="7">
         <v>332</v>
-      </c>
-      <c t="s" r="J298" s="7">
-        <v>333</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10460,19 +10457,19 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>159</v>
@@ -10493,7 +10490,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -10526,7 +10523,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10559,7 +10556,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -10571,7 +10568,7 @@
         <v>124</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>57</v>
@@ -10607,7 +10604,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -10616,10 +10613,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>144</v>
@@ -10640,19 +10637,19 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c t="s" r="J305" s="7">
         <v>23</v>
@@ -10673,7 +10670,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -10706,7 +10703,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -10721,7 +10718,7 @@
         <v>201</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10739,7 +10736,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -10748,10 +10745,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>131</v>
@@ -10772,22 +10769,22 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10820,7 +10817,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -10853,7 +10850,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -10865,7 +10862,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c t="s" r="J312" s="7">
         <v>101</v>
@@ -10886,7 +10883,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -10898,10 +10895,10 @@
         <v>171</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -10919,7 +10916,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -10934,7 +10931,7 @@
         <v>130</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -10967,7 +10964,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -10976,7 +10973,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c t="s" r="I316" s="7">
         <v>178</v>
@@ -11000,13 +10997,13 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>17</v>
@@ -11033,7 +11030,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11066,7 +11063,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11103,7 +11100,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11112,10 +11109,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H320" s="8">
+        <v>337</v>
+      </c>
+      <c t="s" r="I320" s="7">
         <v>338</v>
-      </c>
-      <c t="s" r="I320" s="7">
-        <v>339</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>22</v>
@@ -11151,7 +11148,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11163,7 +11160,7 @@
         <v>141</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c t="s" r="J322" s="7">
         <v>178</v>
@@ -11184,7 +11181,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11196,7 +11193,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>98</v>
@@ -11217,7 +11214,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11232,7 +11229,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11250,7 +11247,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11283,7 +11280,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11292,13 +11289,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>216</v>
+        <v>273</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11316,22 +11313,22 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c t="s" r="H327" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11349,7 +11346,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11382,7 +11379,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11415,7 +11412,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11427,7 +11424,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>154</v>
@@ -11463,7 +11460,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -11496,7 +11493,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -11529,7 +11526,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -11541,7 +11538,7 @@
         <v>111</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>216</v>
+        <v>273</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>122</v>
@@ -11562,7 +11559,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -11577,7 +11574,7 @@
         <v>186</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11595,7 +11592,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -11628,7 +11625,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -11640,10 +11637,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I337" s="7">
+        <v>343</v>
+      </c>
+      <c t="s" r="J337" s="7">
         <v>344</v>
-      </c>
-      <c t="s" r="J337" s="7">
-        <v>345</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11661,7 +11658,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -11676,7 +11673,7 @@
         <v>203</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11709,7 +11706,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -11724,7 +11721,7 @@
         <v>192</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11742,7 +11739,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -11775,7 +11772,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -11808,7 +11805,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -11856,16 +11853,16 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
+        <v>347</v>
+      </c>
+      <c r="F345" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G345" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H345" s="8">
         <v>348</v>
-      </c>
-      <c r="F345" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G345" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H345" s="8">
-        <v>349</v>
       </c>
       <c t="s" r="I345" s="7">
         <v>78</v>
@@ -11889,13 +11886,13 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
+        <v>347</v>
+      </c>
+      <c r="F346" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G346" s="8">
         <v>348</v>
-      </c>
-      <c r="F346" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G346" s="8">
-        <v>349</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>16</v>
@@ -11922,7 +11919,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -11931,7 +11928,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c t="s" r="I347" s="7">
         <v>103</v>
@@ -11955,13 +11952,13 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>16</v>
@@ -11970,7 +11967,7 @@
         <v>137</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -11988,7 +11985,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12000,7 +11997,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c t="s" r="J349" s="7">
         <v>29</v>
@@ -12036,22 +12033,22 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
+        <v>350</v>
+      </c>
+      <c r="F351" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G351" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H351" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I351" s="7">
         <v>351</v>
       </c>
-      <c r="F351" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G351" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H351" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I351" s="7">
-        <v>352</v>
-      </c>
       <c t="s" r="J351" s="7">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12069,7 +12066,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12102,7 +12099,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12135,7 +12132,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12168,7 +12165,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12216,7 +12213,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12228,10 +12225,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12249,7 +12246,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12258,7 +12255,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c t="s" r="I358" s="7">
         <v>112</v>
@@ -12282,13 +12279,13 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>16</v>
@@ -12315,7 +12312,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12348,7 +12345,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12363,7 +12360,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12381,7 +12378,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12393,10 +12390,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12414,7 +12411,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12426,10 +12423,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I363" s="7">
+        <v>354</v>
+      </c>
+      <c t="s" r="J363" s="7">
         <v>355</v>
-      </c>
-      <c t="s" r="J363" s="7">
-        <v>356</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12462,7 +12459,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -12474,7 +12471,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>119</v>
@@ -12495,7 +12492,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -12510,7 +12507,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12528,7 +12525,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -12561,7 +12558,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -12573,10 +12570,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12594,7 +12591,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -12606,10 +12603,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12627,7 +12624,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -12675,7 +12672,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -12687,7 +12684,7 @@
         <v>193</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c t="s" r="J372" s="7">
         <v>214</v>
@@ -12708,7 +12705,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -12723,7 +12720,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12741,16 +12738,16 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
+        <v>359</v>
+      </c>
+      <c r="F374" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G374" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H374" s="8">
         <v>360</v>
-      </c>
-      <c r="F374" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G374" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H374" s="8">
-        <v>361</v>
       </c>
       <c t="s" r="I374" s="7">
         <v>106</v>
@@ -12774,22 +12771,22 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
+        <v>359</v>
+      </c>
+      <c r="F375" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G375" s="8">
         <v>360</v>
       </c>
-      <c r="F375" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G375" s="8">
-        <v>361</v>
-      </c>
       <c t="s" r="H375" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12822,7 +12819,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -12837,7 +12834,7 @@
         <v>143</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12855,7 +12852,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -12888,22 +12885,22 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
+        <v>361</v>
+      </c>
+      <c r="F379" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G379" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H379" s="8">
         <v>362</v>
       </c>
-      <c r="F379" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G379" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H379" s="8">
-        <v>363</v>
-      </c>
       <c t="s" r="I379" s="7">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -12921,13 +12918,13 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
+        <v>361</v>
+      </c>
+      <c r="F380" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G380" s="8">
         <v>362</v>
-      </c>
-      <c r="F380" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G380" s="8">
-        <v>363</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>16</v>
@@ -12936,7 +12933,7 @@
         <v>117</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -12954,7 +12951,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13002,7 +12999,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13014,10 +13011,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13035,7 +13032,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13068,7 +13065,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13083,7 +13080,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13101,7 +13098,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13134,22 +13131,22 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
+        <v>364</v>
+      </c>
+      <c r="F387" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G387" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H387" s="8">
         <v>365</v>
       </c>
-      <c r="F387" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G387" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H387" s="8">
+      <c t="s" r="I387" s="7">
         <v>366</v>
       </c>
-      <c t="s" r="I387" s="7">
-        <v>367</v>
-      </c>
       <c t="s" r="J387" s="7">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13167,22 +13164,22 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
+        <v>364</v>
+      </c>
+      <c r="F388" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G388" s="8">
         <v>365</v>
       </c>
-      <c r="F388" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G388" s="8">
-        <v>366</v>
-      </c>
       <c t="s" r="H388" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I388" s="7">
+        <v>367</v>
+      </c>
+      <c t="s" r="J388" s="7">
         <v>368</v>
-      </c>
-      <c t="s" r="J388" s="7">
-        <v>369</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13215,7 +13212,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -13224,7 +13221,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c t="s" r="I390" s="7">
         <v>145</v>
@@ -13248,13 +13245,13 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>17</v>
@@ -13296,7 +13293,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F393" s="7">
         <v>330</v>
@@ -13329,7 +13326,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F394" s="7">
         <v>330</v>
@@ -13362,7 +13359,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F395" s="7">
         <v>330</v>
@@ -13371,13 +13368,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H395" s="8">
+        <v>371</v>
+      </c>
+      <c t="s" r="I395" s="7">
+        <v>283</v>
+      </c>
+      <c t="s" r="J395" s="7">
         <v>372</v>
-      </c>
-      <c t="s" r="I395" s="7">
-        <v>284</v>
-      </c>
-      <c t="s" r="J395" s="7">
-        <v>373</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13395,13 +13392,13 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F396" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>24</v>
@@ -13443,7 +13440,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F398" s="7">
         <v>330</v>
@@ -13458,7 +13455,7 @@
         <v>125</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13476,7 +13473,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F399" s="7">
         <v>330</v>
@@ -13509,7 +13506,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F400" s="7">
         <v>330</v>
@@ -13521,7 +13518,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>66</v>
@@ -13557,7 +13554,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
@@ -13590,7 +13587,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
@@ -13599,7 +13596,7 @@
         <v>24</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c t="s" r="I403" s="7">
         <v>211</v>
@@ -13623,19 +13620,19 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>56</v>
@@ -13671,22 +13668,22 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c t="s" r="H406" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13704,7 +13701,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
@@ -13716,7 +13713,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>137</v>
@@ -13737,7 +13734,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
@@ -13749,10 +13746,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13785,19 +13782,19 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F410" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c t="s" r="H410" s="8">
         <v>171</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>159</v>
@@ -13833,7 +13830,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
@@ -13842,10 +13839,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>98</v>
@@ -13881,7 +13878,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
@@ -13890,13 +13887,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -13914,22 +13911,22 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G415" s="8">
+        <v>384</v>
+      </c>
+      <c t="s" r="H415" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I415" s="7">
         <v>385</v>
       </c>
-      <c t="s" r="H415" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I415" s="7">
-        <v>386</v>
-      </c>
       <c t="s" r="J415" s="7">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -13937,7 +13934,7 @@
     </row>
     <row r="416" ht="15.75" customHeight="1">
       <c t="s" r="A416" s="9">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B416" s="9"/>
       <c r="C416" s="9"/>
@@ -13957,7 +13954,7 @@
     <row r="417" ht="65.25" customHeight="1"/>
     <row r="418" ht="16.5" customHeight="1">
       <c t="s" r="A418" s="10">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B418" s="10"/>
       <c r="C418" s="10"/>
@@ -13970,7 +13967,7 @@
       <c r="J418" s="10"/>
       <c r="K418" s="10"/>
       <c t="s" r="L418" s="11">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="M418" s="11"/>
       <c r="N418" s="11"/>

--- a/Data/FlightPlan/FPL_07OCT26.xlsx
+++ b/Data/FlightPlan/FPL_07OCT26.xlsx
@@ -368,6 +368,12 @@
     <t>VN-A536</t>
   </si>
   <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
     <t>HKG</t>
   </si>
   <si>
@@ -473,9 +479,6 @@
     <t>00:25</t>
   </si>
   <si>
-    <t>09:10</t>
-  </si>
-  <si>
     <t>VN-A551</t>
   </si>
   <si>
@@ -746,9 +749,6 @@
     <t>VN-A636</t>
   </si>
   <si>
-    <t>10:50</t>
-  </si>
-  <si>
     <t>15:20</t>
   </si>
   <si>
@@ -1172,7 +1172,7 @@
     <t>Total Record(s): 337</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 07, 2026 04:29</t>
+    <t xml:space="preserve">Generated on  Oct 07, 2026 04:45</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3345,7 +3345,7 @@
         <v>13</v>
       </c>
       <c r="B62" s="7">
-        <v>876</v>
+        <v>337</v>
       </c>
       <c t="s" r="C62" s="7">
         <v>14</v>
@@ -3361,13 +3361,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H62" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="I62" s="7">
         <v>119</v>
       </c>
-      <c t="s" r="I62" s="7">
-        <v>103</v>
-      </c>
       <c t="s" r="J62" s="7">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3378,7 +3378,7 @@
         <v>13</v>
       </c>
       <c r="B63" s="7">
-        <v>877</v>
+        <v>324</v>
       </c>
       <c t="s" r="C63" s="7">
         <v>14</v>
@@ -3391,7 +3391,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G63" s="8">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c t="s" r="H63" s="8">
         <v>16</v>
@@ -3400,7 +3400,7 @@
         <v>120</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3411,7 +3411,7 @@
         <v>13</v>
       </c>
       <c r="B64" s="7">
-        <v>168</v>
+        <v>876</v>
       </c>
       <c t="s" r="C64" s="7">
         <v>14</v>
@@ -3427,29 +3427,47 @@
         <v>16</v>
       </c>
       <c t="s" r="H64" s="8">
-        <v>17</v>
+        <v>121</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
       <c r="M64" s="7"/>
     </row>
     <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="6"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
+      <c t="s" r="A65" s="6">
+        <v>13</v>
+      </c>
+      <c r="B65" s="7">
+        <v>877</v>
+      </c>
+      <c t="s" r="C65" s="7">
+        <v>14</v>
+      </c>
       <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="7"/>
-      <c r="J65" s="7"/>
+      <c t="s" r="E65" s="7">
+        <v>118</v>
+      </c>
+      <c r="F65" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G65" s="8">
+        <v>121</v>
+      </c>
+      <c t="s" r="H65" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I65" s="7">
+        <v>122</v>
+      </c>
+      <c t="s" r="J65" s="7">
+        <v>123</v>
+      </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
       <c r="M65" s="7"/>
@@ -3459,63 +3477,45 @@
         <v>13</v>
       </c>
       <c r="B66" s="7">
-        <v>989</v>
+        <v>168</v>
       </c>
       <c t="s" r="C66" s="7">
         <v>14</v>
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G66" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H66" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I66" s="7">
         <v>124</v>
       </c>
-      <c t="s" r="H66" s="8">
-        <v>49</v>
-      </c>
-      <c t="s" r="I66" s="7">
-        <v>125</v>
-      </c>
       <c t="s" r="J66" s="7">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
       <c r="M66" s="7"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c t="s" r="A67" s="6">
-        <v>13</v>
-      </c>
-      <c r="B67" s="7">
-        <v>1504</v>
-      </c>
-      <c t="s" r="C67" s="7">
-        <v>14</v>
-      </c>
+      <c r="A67" s="6"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="7"/>
       <c r="D67" s="7"/>
-      <c t="s" r="E67" s="7">
-        <v>123</v>
-      </c>
-      <c r="F67" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G67" s="8">
-        <v>49</v>
-      </c>
-      <c t="s" r="H67" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I67" s="7">
-        <v>126</v>
-      </c>
-      <c t="s" r="J67" s="7">
-        <v>127</v>
-      </c>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="8"/>
+      <c r="I67" s="7"/>
+      <c r="J67" s="7"/>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
       <c r="M67" s="7"/>
@@ -3525,29 +3525,29 @@
         <v>13</v>
       </c>
       <c r="B68" s="7">
-        <v>1505</v>
+        <v>989</v>
       </c>
       <c t="s" r="C68" s="7">
         <v>14</v>
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3558,14 +3558,14 @@
         <v>13</v>
       </c>
       <c r="B69" s="7">
-        <v>637</v>
+        <v>1504</v>
       </c>
       <c t="s" r="C69" s="7">
         <v>14</v>
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3574,13 +3574,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H69" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>37</v>
+        <v>129</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3591,29 +3591,29 @@
         <v>13</v>
       </c>
       <c r="B70" s="7">
-        <v>895</v>
+        <v>1505</v>
       </c>
       <c t="s" r="C70" s="7">
         <v>14</v>
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G70" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="H70" s="8">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3621,114 +3621,114 @@
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c t="s" r="A71" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B71" s="7">
-        <v>896</v>
+        <v>637</v>
       </c>
       <c t="s" r="C71" s="7">
         <v>14</v>
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G71" s="8">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c t="s" r="H71" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>131</v>
+        <v>63</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c r="M71" s="7"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="6"/>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
+      <c t="s" r="A72" s="6">
+        <v>13</v>
+      </c>
+      <c r="B72" s="7">
+        <v>895</v>
+      </c>
+      <c t="s" r="C72" s="7">
+        <v>14</v>
+      </c>
       <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="8"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="7"/>
-      <c r="J72" s="7"/>
+      <c t="s" r="E72" s="7">
+        <v>125</v>
+      </c>
+      <c r="F72" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G72" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H72" s="8">
+        <v>131</v>
+      </c>
+      <c t="s" r="I72" s="7">
+        <v>66</v>
+      </c>
+      <c t="s" r="J72" s="7">
+        <v>132</v>
+      </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
       <c r="M72" s="7"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c t="s" r="A73" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B73" s="7">
-        <v>939</v>
+        <v>896</v>
       </c>
       <c t="s" r="C73" s="7">
         <v>14</v>
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
+        <v>125</v>
+      </c>
+      <c r="F73" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G73" s="8">
+        <v>131</v>
+      </c>
+      <c t="s" r="H73" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I73" s="7">
         <v>133</v>
       </c>
-      <c r="F73" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G73" s="8">
-        <v>21</v>
-      </c>
-      <c t="s" r="H73" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I73" s="7">
+      <c t="s" r="J73" s="7">
         <v>134</v>
-      </c>
-      <c t="s" r="J73" s="7">
-        <v>34</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c r="M73" s="7"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
-      <c t="s" r="A74" s="6">
-        <v>13</v>
-      </c>
-      <c r="B74" s="7">
-        <v>948</v>
-      </c>
-      <c t="s" r="C74" s="7">
-        <v>14</v>
-      </c>
+      <c r="A74" s="6"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
       <c r="D74" s="7"/>
-      <c t="s" r="E74" s="7">
-        <v>133</v>
-      </c>
-      <c r="F74" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G74" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H74" s="8">
-        <v>135</v>
-      </c>
-      <c t="s" r="I74" s="7">
-        <v>36</v>
-      </c>
-      <c t="s" r="J74" s="7">
-        <v>136</v>
-      </c>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="7"/>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
       <c r="M74" s="7"/>
@@ -3738,29 +3738,29 @@
         <v>13</v>
       </c>
       <c r="B75" s="7">
-        <v>949</v>
+        <v>939</v>
       </c>
       <c t="s" r="C75" s="7">
         <v>14</v>
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c t="s" r="H75" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -3768,17 +3768,17 @@
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c t="s" r="A76" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B76" s="7">
-        <v>932</v>
+        <v>948</v>
       </c>
       <c t="s" r="C76" s="7">
         <v>14</v>
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -3787,10 +3787,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H76" s="8">
-        <v>59</v>
+        <v>137</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c t="s" r="J76" s="7">
         <v>138</v>
@@ -3800,82 +3800,82 @@
       <c r="M76" s="7"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
-      <c r="A77" s="6"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
+      <c t="s" r="A77" s="6">
+        <v>13</v>
+      </c>
+      <c r="B77" s="7">
+        <v>949</v>
+      </c>
+      <c t="s" r="C77" s="7">
+        <v>14</v>
+      </c>
       <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="7"/>
-      <c r="J77" s="7"/>
+      <c t="s" r="E77" s="7">
+        <v>135</v>
+      </c>
+      <c r="F77" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G77" s="8">
+        <v>137</v>
+      </c>
+      <c t="s" r="H77" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I77" s="7">
+        <v>37</v>
+      </c>
+      <c t="s" r="J77" s="7">
+        <v>122</v>
+      </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
       <c r="M77" s="7"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c t="s" r="A78" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B78" s="7">
-        <v>382</v>
+        <v>932</v>
       </c>
       <c t="s" r="C78" s="7">
         <v>14</v>
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
+        <v>135</v>
+      </c>
+      <c r="F78" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G78" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H78" s="8">
+        <v>59</v>
+      </c>
+      <c t="s" r="I78" s="7">
         <v>139</v>
       </c>
-      <c r="F78" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G78" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H78" s="8">
+      <c t="s" r="J78" s="7">
         <v>140</v>
-      </c>
-      <c t="s" r="I78" s="7">
-        <v>141</v>
-      </c>
-      <c t="s" r="J78" s="7">
-        <v>142</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
       <c r="M78" s="7"/>
     </row>
     <row r="79" ht="14.25" customHeight="1">
-      <c t="s" r="A79" s="6">
-        <v>13</v>
-      </c>
-      <c r="B79" s="7">
-        <v>383</v>
-      </c>
-      <c t="s" r="C79" s="7">
-        <v>14</v>
-      </c>
+      <c r="A79" s="6"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="7"/>
       <c r="D79" s="7"/>
-      <c t="s" r="E79" s="7">
-        <v>139</v>
-      </c>
-      <c r="F79" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G79" s="8">
-        <v>140</v>
-      </c>
-      <c t="s" r="H79" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I79" s="7">
-        <v>143</v>
-      </c>
-      <c t="s" r="J79" s="7">
-        <v>144</v>
-      </c>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="7"/>
+      <c r="J79" s="7"/>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
       <c r="M79" s="7"/>
@@ -3885,14 +3885,14 @@
         <v>13</v>
       </c>
       <c r="B80" s="7">
-        <v>860</v>
+        <v>382</v>
       </c>
       <c t="s" r="C80" s="7">
         <v>14</v>
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -3901,13 +3901,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>66</v>
+        <v>144</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -3918,45 +3918,63 @@
         <v>13</v>
       </c>
       <c r="B81" s="7">
-        <v>861</v>
+        <v>383</v>
       </c>
       <c t="s" r="C81" s="7">
         <v>14</v>
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>68</v>
+        <v>145</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
       <c r="M81" s="7"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="6"/>
-      <c r="B82" s="7"/>
-      <c r="C82" s="7"/>
+      <c t="s" r="A82" s="6">
+        <v>13</v>
+      </c>
+      <c r="B82" s="7">
+        <v>860</v>
+      </c>
+      <c t="s" r="C82" s="7">
+        <v>14</v>
+      </c>
       <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8"/>
-      <c r="I82" s="7"/>
-      <c r="J82" s="7"/>
+      <c t="s" r="E82" s="7">
+        <v>141</v>
+      </c>
+      <c r="F82" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G82" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H82" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="I82" s="7">
+        <v>34</v>
+      </c>
+      <c t="s" r="J82" s="7">
+        <v>66</v>
+      </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
       <c r="M82" s="7"/>
@@ -3966,63 +3984,45 @@
         <v>13</v>
       </c>
       <c r="B83" s="7">
-        <v>852</v>
+        <v>861</v>
       </c>
       <c t="s" r="C83" s="7">
         <v>14</v>
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c t="s" r="H83" s="8">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
       <c r="M83" s="7"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
-      <c t="s" r="A84" s="6">
-        <v>13</v>
-      </c>
-      <c r="B84" s="7">
-        <v>853</v>
-      </c>
-      <c t="s" r="C84" s="7">
-        <v>14</v>
-      </c>
+      <c r="A84" s="6"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="7"/>
       <c r="D84" s="7"/>
-      <c t="s" r="E84" s="7">
-        <v>145</v>
-      </c>
-      <c r="F84" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G84" s="8">
-        <v>135</v>
-      </c>
-      <c t="s" r="H84" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I84" s="7">
-        <v>72</v>
-      </c>
-      <c t="s" r="J84" s="7">
-        <v>37</v>
-      </c>
+      <c r="E84" s="7"/>
+      <c r="F84" s="7"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="7"/>
+      <c r="J84" s="7"/>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
       <c r="M84" s="7"/>
@@ -4032,14 +4032,14 @@
         <v>13</v>
       </c>
       <c r="B85" s="7">
-        <v>1321</v>
+        <v>852</v>
       </c>
       <c t="s" r="C85" s="7">
         <v>14</v>
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4048,10 +4048,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H85" s="8">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>147</v>
+        <v>33</v>
       </c>
       <c t="s" r="J85" s="7">
         <v>148</v>
@@ -4065,29 +4065,29 @@
         <v>13</v>
       </c>
       <c r="B86" s="7">
-        <v>3523</v>
+        <v>853</v>
       </c>
       <c t="s" r="C86" s="7">
-        <v>149</v>
+        <v>14</v>
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G86" s="8">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>151</v>
+        <v>37</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4095,114 +4095,114 @@
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c t="s" r="A87" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B87" s="7">
-        <v>3523</v>
+        <v>1321</v>
       </c>
       <c t="s" r="C87" s="7">
-        <v>149</v>
+        <v>14</v>
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="H87" s="8">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c r="M87" s="7"/>
     </row>
     <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="6"/>
-      <c r="B88" s="7"/>
-      <c r="C88" s="7"/>
+      <c t="s" r="A88" s="6">
+        <v>13</v>
+      </c>
+      <c r="B88" s="7">
+        <v>3523</v>
+      </c>
+      <c t="s" r="C88" s="7">
+        <v>151</v>
+      </c>
       <c r="D88" s="7"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7"/>
-      <c r="G88" s="8"/>
-      <c r="H88" s="8"/>
-      <c r="I88" s="7"/>
-      <c r="J88" s="7"/>
+      <c t="s" r="E88" s="7">
+        <v>147</v>
+      </c>
+      <c r="F88" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G88" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H88" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I88" s="7">
+        <v>152</v>
+      </c>
+      <c t="s" r="J88" s="7">
+        <v>153</v>
+      </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c r="M88" s="7"/>
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c t="s" r="A89" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B89" s="7">
-        <v>921</v>
+        <v>3523</v>
       </c>
       <c t="s" r="C89" s="7">
-        <v>14</v>
+        <v>151</v>
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
+        <v>147</v>
+      </c>
+      <c r="F89" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G89" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H89" s="8">
+        <v>154</v>
+      </c>
+      <c t="s" r="I89" s="7">
         <v>155</v>
       </c>
-      <c r="F89" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G89" s="8">
-        <v>156</v>
-      </c>
-      <c t="s" r="H89" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I89" s="7">
-        <v>157</v>
-      </c>
       <c t="s" r="J89" s="7">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c r="M89" s="7"/>
     </row>
     <row r="90" ht="15" customHeight="1">
-      <c t="s" r="A90" s="6">
-        <v>13</v>
-      </c>
-      <c r="B90" s="7">
-        <v>145</v>
-      </c>
-      <c t="s" r="C90" s="7">
-        <v>14</v>
-      </c>
+      <c r="A90" s="6"/>
+      <c r="B90" s="7"/>
+      <c r="C90" s="7"/>
       <c r="D90" s="7"/>
-      <c t="s" r="E90" s="7">
-        <v>155</v>
-      </c>
-      <c r="F90" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G90" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H90" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I90" s="7">
-        <v>159</v>
-      </c>
-      <c t="s" r="J90" s="7">
-        <v>160</v>
-      </c>
+      <c r="E90" s="7"/>
+      <c r="F90" s="7"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="8"/>
+      <c r="I90" s="7"/>
+      <c r="J90" s="7"/>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
       <c r="M90" s="7"/>
@@ -4212,29 +4212,29 @@
         <v>13</v>
       </c>
       <c r="B91" s="7">
-        <v>1805</v>
+        <v>921</v>
       </c>
       <c t="s" r="C91" s="7">
         <v>14</v>
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>161</v>
+        <v>17</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4245,45 +4245,63 @@
         <v>13</v>
       </c>
       <c r="B92" s="7">
-        <v>1806</v>
+        <v>145</v>
       </c>
       <c t="s" r="C92" s="7">
         <v>14</v>
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H92" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I92" s="7">
+        <v>160</v>
+      </c>
+      <c t="s" r="J92" s="7">
         <v>161</v>
-      </c>
-      <c t="s" r="H92" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I92" s="7">
-        <v>151</v>
-      </c>
-      <c t="s" r="J92" s="7">
-        <v>163</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
       <c r="M92" s="7"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
-      <c r="A93" s="6"/>
-      <c r="B93" s="7"/>
-      <c r="C93" s="7"/>
+      <c t="s" r="A93" s="6">
+        <v>13</v>
+      </c>
+      <c r="B93" s="7">
+        <v>1805</v>
+      </c>
+      <c t="s" r="C93" s="7">
+        <v>14</v>
+      </c>
       <c r="D93" s="7"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7"/>
-      <c r="G93" s="8"/>
-      <c r="H93" s="8"/>
-      <c r="I93" s="7"/>
-      <c r="J93" s="7"/>
+      <c t="s" r="E93" s="7">
+        <v>156</v>
+      </c>
+      <c r="F93" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G93" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H93" s="8">
+        <v>162</v>
+      </c>
+      <c t="s" r="I93" s="7">
+        <v>149</v>
+      </c>
+      <c t="s" r="J93" s="7">
+        <v>163</v>
+      </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
       <c r="M93" s="7"/>
@@ -4293,63 +4311,45 @@
         <v>13</v>
       </c>
       <c r="B94" s="7">
-        <v>929</v>
+        <v>1806</v>
       </c>
       <c t="s" r="C94" s="7">
         <v>14</v>
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
+        <v>156</v>
+      </c>
+      <c r="F94" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G94" s="8">
+        <v>162</v>
+      </c>
+      <c t="s" r="H94" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I94" s="7">
+        <v>153</v>
+      </c>
+      <c t="s" r="J94" s="7">
         <v>164</v>
-      </c>
-      <c r="F94" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G94" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H94" s="8">
-        <v>165</v>
-      </c>
-      <c t="s" r="I94" s="7">
-        <v>166</v>
-      </c>
-      <c t="s" r="J94" s="7">
-        <v>23</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c r="M94" s="7"/>
     </row>
     <row r="95" ht="15" customHeight="1">
-      <c t="s" r="A95" s="6">
-        <v>13</v>
-      </c>
-      <c r="B95" s="7">
-        <v>928</v>
-      </c>
-      <c t="s" r="C95" s="7">
-        <v>14</v>
-      </c>
+      <c r="A95" s="6"/>
+      <c r="B95" s="7"/>
+      <c r="C95" s="7"/>
       <c r="D95" s="7"/>
-      <c t="s" r="E95" s="7">
-        <v>164</v>
-      </c>
-      <c r="F95" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G95" s="8">
-        <v>165</v>
-      </c>
-      <c t="s" r="H95" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I95" s="7">
-        <v>127</v>
-      </c>
-      <c t="s" r="J95" s="7">
-        <v>167</v>
-      </c>
+      <c r="E95" s="7"/>
+      <c r="F95" s="7"/>
+      <c r="G95" s="8"/>
+      <c r="H95" s="8"/>
+      <c r="I95" s="7"/>
+      <c r="J95" s="7"/>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c r="M95" s="7"/>
@@ -4359,14 +4359,14 @@
         <v>13</v>
       </c>
       <c r="B96" s="7">
-        <v>455</v>
+        <v>929</v>
       </c>
       <c t="s" r="C96" s="7">
         <v>14</v>
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4375,13 +4375,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>24</v>
+        <v>166</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>54</v>
+        <v>167</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>168</v>
+        <v>23</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4392,45 +4392,63 @@
         <v>13</v>
       </c>
       <c r="B97" s="7">
-        <v>968</v>
+        <v>928</v>
       </c>
       <c t="s" r="C97" s="7">
         <v>14</v>
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>24</v>
+        <v>166</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c r="M97" s="7"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="6"/>
-      <c r="B98" s="7"/>
-      <c r="C98" s="7"/>
+      <c t="s" r="A98" s="6">
+        <v>13</v>
+      </c>
+      <c r="B98" s="7">
+        <v>455</v>
+      </c>
+      <c t="s" r="C98" s="7">
+        <v>14</v>
+      </c>
       <c r="D98" s="7"/>
-      <c r="E98" s="7"/>
-      <c r="F98" s="7"/>
-      <c r="G98" s="8"/>
-      <c r="H98" s="8"/>
-      <c r="I98" s="7"/>
-      <c r="J98" s="7"/>
+      <c t="s" r="E98" s="7">
+        <v>165</v>
+      </c>
+      <c r="F98" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G98" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H98" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="I98" s="7">
+        <v>54</v>
+      </c>
+      <c t="s" r="J98" s="7">
+        <v>169</v>
+      </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
       <c r="M98" s="7"/>
@@ -4440,63 +4458,45 @@
         <v>13</v>
       </c>
       <c r="B99" s="7">
-        <v>7707</v>
+        <v>968</v>
       </c>
       <c t="s" r="C99" s="7">
-        <v>149</v>
+        <v>14</v>
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
+        <v>165</v>
+      </c>
+      <c r="F99" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G99" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H99" s="8">
+        <v>126</v>
+      </c>
+      <c t="s" r="I99" s="7">
         <v>170</v>
       </c>
-      <c r="F99" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G99" s="8">
-        <v>152</v>
-      </c>
-      <c t="s" r="H99" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I99" s="7">
-        <v>80</v>
-      </c>
       <c t="s" r="J99" s="7">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
       <c r="M99" s="7"/>
     </row>
     <row r="100" ht="15" customHeight="1">
-      <c t="s" r="A100" s="6">
-        <v>13</v>
-      </c>
-      <c r="B100" s="7">
-        <v>7707</v>
-      </c>
-      <c t="s" r="C100" s="7">
-        <v>149</v>
-      </c>
+      <c r="A100" s="6"/>
+      <c r="B100" s="7"/>
+      <c r="C100" s="7"/>
       <c r="D100" s="7"/>
-      <c t="s" r="E100" s="7">
-        <v>170</v>
-      </c>
-      <c r="F100" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G100" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H100" s="8">
-        <v>171</v>
-      </c>
-      <c t="s" r="I100" s="7">
-        <v>172</v>
-      </c>
-      <c t="s" r="J100" s="7">
-        <v>63</v>
-      </c>
+      <c r="E100" s="7"/>
+      <c r="F100" s="7"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="7"/>
+      <c r="J100" s="7"/>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
       <c r="M100" s="7"/>
@@ -4506,29 +4506,29 @@
         <v>13</v>
       </c>
       <c r="B101" s="7">
-        <v>776</v>
+        <v>7707</v>
       </c>
       <c t="s" r="C101" s="7">
-        <v>14</v>
+        <v>151</v>
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c t="s" r="H101" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>174</v>
+        <v>25</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4539,14 +4539,14 @@
         <v>13</v>
       </c>
       <c r="B102" s="7">
-        <v>167</v>
+        <v>7707</v>
       </c>
       <c t="s" r="C102" s="7">
-        <v>14</v>
+        <v>151</v>
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4555,29 +4555,47 @@
         <v>17</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>176</v>
+        <v>63</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c r="M102" s="7"/>
     </row>
     <row r="103" ht="14.25" customHeight="1">
-      <c r="A103" s="6"/>
-      <c r="B103" s="7"/>
-      <c r="C103" s="7"/>
+      <c t="s" r="A103" s="6">
+        <v>13</v>
+      </c>
+      <c r="B103" s="7">
+        <v>776</v>
+      </c>
+      <c t="s" r="C103" s="7">
+        <v>14</v>
+      </c>
       <c r="D103" s="7"/>
-      <c r="E103" s="7"/>
-      <c r="F103" s="7"/>
-      <c r="G103" s="8"/>
-      <c r="H103" s="8"/>
-      <c r="I103" s="7"/>
-      <c r="J103" s="7"/>
+      <c t="s" r="E103" s="7">
+        <v>171</v>
+      </c>
+      <c r="F103" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G103" s="8">
+        <v>172</v>
+      </c>
+      <c t="s" r="H103" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I103" s="7">
+        <v>174</v>
+      </c>
+      <c t="s" r="J103" s="7">
+        <v>175</v>
+      </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c r="M103" s="7"/>
@@ -4587,63 +4605,45 @@
         <v>13</v>
       </c>
       <c r="B104" s="7">
-        <v>5069</v>
+        <v>167</v>
       </c>
       <c t="s" r="C104" s="7">
-        <v>149</v>
+        <v>14</v>
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
+        <v>171</v>
+      </c>
+      <c r="F104" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G104" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H104" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I104" s="7">
+        <v>176</v>
+      </c>
+      <c t="s" r="J104" s="7">
         <v>177</v>
-      </c>
-      <c r="F104" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G104" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H104" s="8">
-        <v>171</v>
-      </c>
-      <c t="s" r="I104" s="7">
-        <v>178</v>
-      </c>
-      <c t="s" r="J104" s="7">
-        <v>179</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c r="M104" s="7"/>
     </row>
     <row r="105" ht="15" customHeight="1">
-      <c t="s" r="A105" s="6">
-        <v>13</v>
-      </c>
-      <c r="B105" s="7">
-        <v>7620</v>
-      </c>
-      <c t="s" r="C105" s="7">
-        <v>149</v>
-      </c>
+      <c r="A105" s="6"/>
+      <c r="B105" s="7"/>
+      <c r="C105" s="7"/>
       <c r="D105" s="7"/>
-      <c t="s" r="E105" s="7">
-        <v>177</v>
-      </c>
-      <c r="F105" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G105" s="8">
-        <v>171</v>
-      </c>
-      <c t="s" r="H105" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I105" s="7">
-        <v>180</v>
-      </c>
-      <c t="s" r="J105" s="7">
-        <v>62</v>
-      </c>
+      <c r="E105" s="7"/>
+      <c r="F105" s="7"/>
+      <c r="G105" s="8"/>
+      <c r="H105" s="8"/>
+      <c r="I105" s="7"/>
+      <c r="J105" s="7"/>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
       <c r="M105" s="7"/>
@@ -4653,14 +4653,14 @@
         <v>13</v>
       </c>
       <c r="B106" s="7">
-        <v>7620</v>
+        <v>5069</v>
       </c>
       <c t="s" r="C106" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4669,13 +4669,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H106" s="8">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>69</v>
+        <v>180</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4683,114 +4683,114 @@
     </row>
     <row r="107" ht="14.25" customHeight="1">
       <c t="s" r="A107" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B107" s="7">
-        <v>7621</v>
+        <v>7620</v>
       </c>
       <c t="s" r="C107" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
+        <v>172</v>
+      </c>
+      <c t="s" r="H107" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I107" s="7">
         <v>181</v>
       </c>
-      <c t="s" r="H107" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I107" s="7">
-        <v>183</v>
-      </c>
       <c t="s" r="J107" s="7">
-        <v>179</v>
+        <v>62</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
       <c r="M107" s="7"/>
     </row>
     <row r="108" ht="14.25" customHeight="1">
-      <c r="A108" s="6"/>
-      <c r="B108" s="7"/>
-      <c r="C108" s="7"/>
+      <c t="s" r="A108" s="6">
+        <v>13</v>
+      </c>
+      <c r="B108" s="7">
+        <v>7620</v>
+      </c>
+      <c t="s" r="C108" s="7">
+        <v>151</v>
+      </c>
       <c r="D108" s="7"/>
-      <c r="E108" s="7"/>
-      <c r="F108" s="7"/>
-      <c r="G108" s="8"/>
-      <c r="H108" s="8"/>
-      <c r="I108" s="7"/>
-      <c r="J108" s="7"/>
+      <c t="s" r="E108" s="7">
+        <v>178</v>
+      </c>
+      <c r="F108" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G108" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H108" s="8">
+        <v>182</v>
+      </c>
+      <c t="s" r="I108" s="7">
+        <v>183</v>
+      </c>
+      <c t="s" r="J108" s="7">
+        <v>69</v>
+      </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
       <c r="M108" s="7"/>
     </row>
     <row r="109" ht="14.25" customHeight="1">
       <c t="s" r="A109" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B109" s="7">
-        <v>8890</v>
+        <v>7621</v>
       </c>
       <c t="s" r="C109" s="7">
-        <v>14</v>
+        <v>151</v>
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
+        <v>178</v>
+      </c>
+      <c r="F109" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G109" s="8">
+        <v>182</v>
+      </c>
+      <c t="s" r="H109" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I109" s="7">
         <v>184</v>
       </c>
-      <c r="F109" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G109" s="8">
-        <v>49</v>
-      </c>
-      <c t="s" r="H109" s="8">
-        <v>185</v>
-      </c>
-      <c t="s" r="I109" s="7">
-        <v>113</v>
-      </c>
       <c t="s" r="J109" s="7">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c r="M109" s="7"/>
     </row>
     <row r="110" ht="15" customHeight="1">
-      <c t="s" r="A110" s="6">
-        <v>13</v>
-      </c>
-      <c r="B110" s="7">
-        <v>8891</v>
-      </c>
-      <c t="s" r="C110" s="7">
-        <v>14</v>
-      </c>
+      <c r="A110" s="6"/>
+      <c r="B110" s="7"/>
+      <c r="C110" s="7"/>
       <c r="D110" s="7"/>
-      <c t="s" r="E110" s="7">
-        <v>184</v>
-      </c>
-      <c r="F110" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G110" s="8">
-        <v>185</v>
-      </c>
-      <c t="s" r="H110" s="8">
-        <v>49</v>
-      </c>
-      <c t="s" r="I110" s="7">
-        <v>187</v>
-      </c>
-      <c t="s" r="J110" s="7">
-        <v>115</v>
-      </c>
+      <c r="E110" s="7"/>
+      <c r="F110" s="7"/>
+      <c r="G110" s="8"/>
+      <c r="H110" s="8"/>
+      <c r="I110" s="7"/>
+      <c r="J110" s="7"/>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c r="M110" s="7"/>
@@ -4800,14 +4800,14 @@
         <v>13</v>
       </c>
       <c r="B111" s="7">
-        <v>643</v>
+        <v>8890</v>
       </c>
       <c t="s" r="C111" s="7">
         <v>14</v>
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4816,13 +4816,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>16</v>
+        <v>186</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4830,114 +4830,114 @@
     </row>
     <row r="112" ht="14.25" customHeight="1">
       <c t="s" r="A112" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B112" s="7">
-        <v>868</v>
+        <v>8891</v>
       </c>
       <c t="s" r="C112" s="7">
         <v>14</v>
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>16</v>
+        <v>186</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>124</v>
+        <v>49</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>190</v>
+        <v>115</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c r="M112" s="7"/>
     </row>
     <row r="113" ht="14.25" customHeight="1">
-      <c r="A113" s="6"/>
-      <c r="B113" s="7"/>
-      <c r="C113" s="7"/>
+      <c t="s" r="A113" s="6">
+        <v>13</v>
+      </c>
+      <c r="B113" s="7">
+        <v>643</v>
+      </c>
+      <c t="s" r="C113" s="7">
+        <v>14</v>
+      </c>
       <c r="D113" s="7"/>
-      <c r="E113" s="7"/>
-      <c r="F113" s="7"/>
-      <c r="G113" s="8"/>
-      <c r="H113" s="8"/>
-      <c r="I113" s="7"/>
-      <c r="J113" s="7"/>
+      <c t="s" r="E113" s="7">
+        <v>185</v>
+      </c>
+      <c r="F113" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G113" s="8">
+        <v>49</v>
+      </c>
+      <c t="s" r="H113" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I113" s="7">
+        <v>189</v>
+      </c>
+      <c t="s" r="J113" s="7">
+        <v>190</v>
+      </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
       <c r="M113" s="7"/>
     </row>
     <row r="114" ht="14.25" customHeight="1">
       <c t="s" r="A114" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B114" s="7">
-        <v>156</v>
+        <v>868</v>
       </c>
       <c t="s" r="C114" s="7">
         <v>14</v>
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
+        <v>185</v>
+      </c>
+      <c r="F114" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G114" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H114" s="8">
+        <v>126</v>
+      </c>
+      <c t="s" r="I114" s="7">
+        <v>133</v>
+      </c>
+      <c t="s" r="J114" s="7">
         <v>191</v>
-      </c>
-      <c r="F114" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G114" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H114" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I114" s="7">
-        <v>192</v>
-      </c>
-      <c t="s" r="J114" s="7">
-        <v>193</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
       <c r="M114" s="7"/>
     </row>
     <row r="115" ht="15" customHeight="1">
-      <c t="s" r="A115" s="6">
-        <v>13</v>
-      </c>
-      <c r="B115" s="7">
-        <v>997</v>
-      </c>
-      <c t="s" r="C115" s="7">
-        <v>14</v>
-      </c>
+      <c r="A115" s="6"/>
+      <c r="B115" s="7"/>
+      <c r="C115" s="7"/>
       <c r="D115" s="7"/>
-      <c t="s" r="E115" s="7">
-        <v>191</v>
-      </c>
-      <c r="F115" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G115" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H115" s="8">
-        <v>194</v>
-      </c>
-      <c t="s" r="I115" s="7">
-        <v>112</v>
-      </c>
-      <c t="s" r="J115" s="7">
-        <v>44</v>
-      </c>
+      <c r="E115" s="7"/>
+      <c r="F115" s="7"/>
+      <c r="G115" s="8"/>
+      <c r="H115" s="8"/>
+      <c r="I115" s="7"/>
+      <c r="J115" s="7"/>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c r="M115" s="7"/>
@@ -4947,29 +4947,29 @@
         <v>13</v>
       </c>
       <c r="B116" s="7">
-        <v>998</v>
+        <v>156</v>
       </c>
       <c t="s" r="C116" s="7">
         <v>14</v>
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H116" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I116" s="7">
+        <v>193</v>
+      </c>
+      <c t="s" r="J116" s="7">
         <v>194</v>
-      </c>
-      <c t="s" r="H116" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I116" s="7">
-        <v>195</v>
-      </c>
-      <c t="s" r="J116" s="7">
-        <v>196</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -4977,17 +4977,17 @@
     </row>
     <row r="117" ht="14.25" customHeight="1">
       <c t="s" r="A117" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B117" s="7">
-        <v>938</v>
+        <v>997</v>
       </c>
       <c t="s" r="C117" s="7">
         <v>14</v>
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -4996,95 +4996,95 @@
         <v>17</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>197</v>
+        <v>112</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c r="M117" s="7"/>
     </row>
     <row r="118" ht="14.25" customHeight="1">
-      <c r="A118" s="6"/>
-      <c r="B118" s="7"/>
-      <c r="C118" s="7"/>
+      <c t="s" r="A118" s="6">
+        <v>13</v>
+      </c>
+      <c r="B118" s="7">
+        <v>998</v>
+      </c>
+      <c t="s" r="C118" s="7">
+        <v>14</v>
+      </c>
       <c r="D118" s="7"/>
-      <c r="E118" s="7"/>
-      <c r="F118" s="7"/>
-      <c r="G118" s="8"/>
-      <c r="H118" s="8"/>
-      <c r="I118" s="7"/>
-      <c r="J118" s="7"/>
+      <c t="s" r="E118" s="7">
+        <v>192</v>
+      </c>
+      <c r="F118" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G118" s="8">
+        <v>195</v>
+      </c>
+      <c t="s" r="H118" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I118" s="7">
+        <v>196</v>
+      </c>
+      <c t="s" r="J118" s="7">
+        <v>197</v>
+      </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
       <c r="M118" s="7"/>
     </row>
     <row r="119" ht="14.25" customHeight="1">
       <c t="s" r="A119" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B119" s="7">
-        <v>122</v>
+        <v>938</v>
       </c>
       <c t="s" r="C119" s="7">
         <v>14</v>
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
+        <v>192</v>
+      </c>
+      <c r="F119" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G119" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H119" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="I119" s="7">
         <v>198</v>
       </c>
-      <c r="F119" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G119" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H119" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I119" s="7">
-        <v>190</v>
-      </c>
       <c t="s" r="J119" s="7">
-        <v>199</v>
+        <v>97</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c r="M119" s="7"/>
     </row>
     <row r="120" ht="15" customHeight="1">
-      <c t="s" r="A120" s="6">
-        <v>13</v>
-      </c>
-      <c r="B120" s="7">
-        <v>515</v>
-      </c>
-      <c t="s" r="C120" s="7">
-        <v>14</v>
-      </c>
+      <c r="A120" s="6"/>
+      <c r="B120" s="7"/>
+      <c r="C120" s="7"/>
       <c r="D120" s="7"/>
-      <c t="s" r="E120" s="7">
-        <v>198</v>
-      </c>
-      <c r="F120" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G120" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H120" s="8">
-        <v>49</v>
-      </c>
-      <c t="s" r="I120" s="7">
-        <v>200</v>
-      </c>
-      <c t="s" r="J120" s="7">
-        <v>36</v>
-      </c>
+      <c r="E120" s="7"/>
+      <c r="F120" s="7"/>
+      <c r="G120" s="8"/>
+      <c r="H120" s="8"/>
+      <c r="I120" s="7"/>
+      <c r="J120" s="7"/>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c r="M120" s="7"/>
@@ -5094,29 +5094,29 @@
         <v>13</v>
       </c>
       <c r="B121" s="7">
-        <v>508</v>
+        <v>122</v>
       </c>
       <c t="s" r="C121" s="7">
         <v>14</v>
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>81</v>
+        <v>191</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5127,14 +5127,14 @@
         <v>13</v>
       </c>
       <c r="B122" s="7">
-        <v>773</v>
+        <v>515</v>
       </c>
       <c t="s" r="C122" s="7">
         <v>14</v>
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5143,13 +5143,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>171</v>
+        <v>49</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>203</v>
+        <v>36</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5160,29 +5160,29 @@
         <v>13</v>
       </c>
       <c r="B123" s="7">
-        <v>7704</v>
+        <v>508</v>
       </c>
       <c t="s" r="C123" s="7">
         <v>14</v>
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>171</v>
+        <v>49</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5190,17 +5190,17 @@
     </row>
     <row r="124" ht="14.25" customHeight="1">
       <c t="s" r="A124" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B124" s="7">
-        <v>7704</v>
+        <v>773</v>
       </c>
       <c t="s" r="C124" s="7">
         <v>14</v>
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5209,95 +5209,95 @@
         <v>17</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>205</v>
+        <v>172</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>141</v>
+        <v>204</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c r="M124" s="7"/>
     </row>
     <row r="125" ht="15" customHeight="1">
-      <c r="A125" s="6"/>
-      <c r="B125" s="7"/>
-      <c r="C125" s="7"/>
+      <c t="s" r="A125" s="6">
+        <v>13</v>
+      </c>
+      <c r="B125" s="7">
+        <v>7704</v>
+      </c>
+      <c t="s" r="C125" s="7">
+        <v>14</v>
+      </c>
       <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
-      <c r="F125" s="7"/>
-      <c r="G125" s="8"/>
-      <c r="H125" s="8"/>
-      <c r="I125" s="7"/>
-      <c r="J125" s="7"/>
+      <c t="s" r="E125" s="7">
+        <v>199</v>
+      </c>
+      <c r="F125" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G125" s="8">
+        <v>172</v>
+      </c>
+      <c t="s" r="H125" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I125" s="7">
+        <v>190</v>
+      </c>
+      <c t="s" r="J125" s="7">
+        <v>205</v>
+      </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
       <c r="M125" s="7"/>
     </row>
     <row r="126" ht="14.25" customHeight="1">
       <c t="s" r="A126" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B126" s="7">
-        <v>863</v>
+        <v>7704</v>
       </c>
       <c t="s" r="C126" s="7">
         <v>14</v>
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
+        <v>199</v>
+      </c>
+      <c r="F126" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G126" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H126" s="8">
+        <v>206</v>
+      </c>
+      <c t="s" r="I126" s="7">
         <v>207</v>
       </c>
-      <c r="F126" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G126" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H126" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I126" s="7">
-        <v>208</v>
-      </c>
       <c t="s" r="J126" s="7">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c r="M126" s="7"/>
     </row>
     <row r="127" ht="14.25" customHeight="1">
-      <c t="s" r="A127" s="6">
-        <v>13</v>
-      </c>
-      <c r="B127" s="7">
-        <v>1831</v>
-      </c>
-      <c t="s" r="C127" s="7">
-        <v>14</v>
-      </c>
+      <c r="A127" s="6"/>
+      <c r="B127" s="7"/>
+      <c r="C127" s="7"/>
       <c r="D127" s="7"/>
-      <c t="s" r="E127" s="7">
-        <v>207</v>
-      </c>
-      <c r="F127" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G127" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H127" s="8">
-        <v>209</v>
-      </c>
-      <c t="s" r="I127" s="7">
-        <v>44</v>
-      </c>
-      <c t="s" r="J127" s="7">
-        <v>45</v>
-      </c>
+      <c r="E127" s="7"/>
+      <c r="F127" s="7"/>
+      <c r="G127" s="8"/>
+      <c r="H127" s="8"/>
+      <c r="I127" s="7"/>
+      <c r="J127" s="7"/>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
       <c r="M127" s="7"/>
@@ -5307,29 +5307,29 @@
         <v>13</v>
       </c>
       <c r="B128" s="7">
-        <v>1832</v>
+        <v>863</v>
       </c>
       <c t="s" r="C128" s="7">
         <v>14</v>
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G128" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H128" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I128" s="7">
         <v>209</v>
       </c>
-      <c t="s" r="H128" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I128" s="7">
-        <v>147</v>
-      </c>
       <c t="s" r="J128" s="7">
-        <v>108</v>
+        <v>173</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5337,17 +5337,17 @@
     </row>
     <row r="129" ht="14.25" customHeight="1">
       <c t="s" r="A129" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B129" s="7">
-        <v>91</v>
+        <v>1831</v>
       </c>
       <c t="s" r="C129" s="7">
         <v>14</v>
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5359,96 +5359,92 @@
         <v>210</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>211</v>
+        <v>44</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>212</v>
+        <v>45</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c r="M129" s="7"/>
     </row>
     <row r="130" ht="15" customHeight="1">
-      <c r="A130" s="6"/>
-      <c r="B130" s="7"/>
-      <c r="C130" s="7"/>
+      <c t="s" r="A130" s="6">
+        <v>13</v>
+      </c>
+      <c r="B130" s="7">
+        <v>1832</v>
+      </c>
+      <c t="s" r="C130" s="7">
+        <v>14</v>
+      </c>
       <c r="D130" s="7"/>
-      <c r="E130" s="7"/>
-      <c r="F130" s="7"/>
-      <c r="G130" s="8"/>
-      <c r="H130" s="8"/>
-      <c r="I130" s="7"/>
-      <c r="J130" s="7"/>
+      <c t="s" r="E130" s="7">
+        <v>208</v>
+      </c>
+      <c r="F130" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G130" s="8">
+        <v>210</v>
+      </c>
+      <c t="s" r="H130" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I130" s="7">
+        <v>149</v>
+      </c>
+      <c t="s" r="J130" s="7">
+        <v>108</v>
+      </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c r="M130" s="7"/>
     </row>
     <row r="131" ht="14.25" customHeight="1">
       <c t="s" r="A131" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B131" s="7">
-        <v>919</v>
+        <v>91</v>
       </c>
       <c t="s" r="C131" s="7">
         <v>14</v>
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
+        <v>208</v>
+      </c>
+      <c r="F131" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G131" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H131" s="8">
+        <v>211</v>
+      </c>
+      <c t="s" r="I131" s="7">
+        <v>212</v>
+      </c>
+      <c t="s" r="J131" s="7">
         <v>213</v>
       </c>
-      <c r="F131" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G131" s="8">
-        <v>124</v>
-      </c>
-      <c t="s" r="H131" s="8">
-        <v>171</v>
-      </c>
-      <c t="s" r="I131" s="7">
-        <v>214</v>
-      </c>
-      <c t="s" r="J131" s="7">
-        <v>215</v>
-      </c>
-      <c t="s" r="K131" s="7">
-        <v>214</v>
-      </c>
+      <c r="K131" s="7"/>
       <c r="L131" s="7"/>
-      <c t="s" r="M131" s="7">
-        <v>215</v>
-      </c>
+      <c r="M131" s="7"/>
     </row>
     <row r="132" ht="14.25" customHeight="1">
-      <c t="s" r="A132" s="6">
-        <v>13</v>
-      </c>
-      <c r="B132" s="7">
-        <v>5348</v>
-      </c>
-      <c t="s" r="C132" s="7">
-        <v>14</v>
-      </c>
+      <c r="A132" s="6"/>
+      <c r="B132" s="7"/>
+      <c r="C132" s="7"/>
       <c r="D132" s="7"/>
-      <c t="s" r="E132" s="7">
-        <v>213</v>
-      </c>
-      <c r="F132" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G132" s="8">
-        <v>171</v>
-      </c>
-      <c t="s" r="H132" s="8">
-        <v>216</v>
-      </c>
-      <c t="s" r="I132" s="7">
-        <v>43</v>
-      </c>
-      <c t="s" r="J132" s="7">
-        <v>217</v>
-      </c>
+      <c r="E132" s="7"/>
+      <c r="F132" s="7"/>
+      <c r="G132" s="8"/>
+      <c r="H132" s="8"/>
+      <c r="I132" s="7"/>
+      <c r="J132" s="7"/>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
       <c r="M132" s="7"/>
@@ -5458,144 +5454,148 @@
         <v>13</v>
       </c>
       <c r="B133" s="7">
-        <v>5349</v>
+        <v>919</v>
       </c>
       <c t="s" r="C133" s="7">
         <v>14</v>
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
+        <v>126</v>
+      </c>
+      <c t="s" r="H133" s="8">
+        <v>172</v>
+      </c>
+      <c t="s" r="I133" s="7">
+        <v>215</v>
+      </c>
+      <c t="s" r="J133" s="7">
         <v>216</v>
       </c>
-      <c t="s" r="H133" s="8">
-        <v>171</v>
-      </c>
-      <c t="s" r="I133" s="7">
-        <v>196</v>
-      </c>
-      <c t="s" r="J133" s="7">
-        <v>218</v>
-      </c>
-      <c r="K133" s="7"/>
+      <c t="s" r="K133" s="7">
+        <v>215</v>
+      </c>
       <c r="L133" s="7"/>
-      <c r="M133" s="7"/>
+      <c t="s" r="M133" s="7">
+        <v>216</v>
+      </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
       <c t="s" r="A134" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B134" s="7">
-        <v>918</v>
+        <v>5348</v>
       </c>
       <c t="s" r="C134" s="7">
         <v>14</v>
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>124</v>
+        <v>217</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>219</v>
+        <v>43</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c r="M134" s="7"/>
     </row>
     <row r="135" ht="15" customHeight="1">
-      <c r="A135" s="6"/>
-      <c r="B135" s="7"/>
-      <c r="C135" s="7"/>
+      <c t="s" r="A135" s="6">
+        <v>13</v>
+      </c>
+      <c r="B135" s="7">
+        <v>5349</v>
+      </c>
+      <c t="s" r="C135" s="7">
+        <v>14</v>
+      </c>
       <c r="D135" s="7"/>
-      <c r="E135" s="7"/>
-      <c r="F135" s="7"/>
-      <c r="G135" s="8"/>
-      <c r="H135" s="8"/>
-      <c r="I135" s="7"/>
-      <c r="J135" s="7"/>
+      <c t="s" r="E135" s="7">
+        <v>214</v>
+      </c>
+      <c r="F135" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G135" s="8">
+        <v>217</v>
+      </c>
+      <c t="s" r="H135" s="8">
+        <v>172</v>
+      </c>
+      <c t="s" r="I135" s="7">
+        <v>197</v>
+      </c>
+      <c t="s" r="J135" s="7">
+        <v>219</v>
+      </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
       <c r="M135" s="7"/>
     </row>
     <row r="136" ht="14.25" customHeight="1">
       <c t="s" r="A136" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B136" s="7">
-        <v>503</v>
+        <v>918</v>
       </c>
       <c t="s" r="C136" s="7">
         <v>14</v>
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
+        <v>214</v>
+      </c>
+      <c r="F136" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G136" s="8">
+        <v>172</v>
+      </c>
+      <c t="s" r="H136" s="8">
+        <v>126</v>
+      </c>
+      <c t="s" r="I136" s="7">
+        <v>220</v>
+      </c>
+      <c t="s" r="J136" s="7">
         <v>221</v>
-      </c>
-      <c r="F136" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G136" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H136" s="8">
-        <v>49</v>
-      </c>
-      <c t="s" r="I136" s="7">
-        <v>31</v>
-      </c>
-      <c t="s" r="J136" s="7">
-        <v>78</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
       <c r="M136" s="7"/>
     </row>
     <row r="137" ht="14.25" customHeight="1">
-      <c t="s" r="A137" s="6">
-        <v>13</v>
-      </c>
-      <c r="B137" s="7">
-        <v>524</v>
-      </c>
-      <c t="s" r="C137" s="7">
-        <v>14</v>
-      </c>
+      <c r="A137" s="6"/>
+      <c r="B137" s="7"/>
+      <c r="C137" s="7"/>
       <c r="D137" s="7"/>
-      <c t="s" r="E137" s="7">
-        <v>221</v>
-      </c>
-      <c r="F137" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G137" s="8">
-        <v>49</v>
-      </c>
-      <c t="s" r="H137" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I137" s="7">
-        <v>134</v>
-      </c>
-      <c t="s" r="J137" s="7">
-        <v>222</v>
-      </c>
+      <c r="E137" s="7"/>
+      <c r="F137" s="7"/>
+      <c r="G137" s="8"/>
+      <c r="H137" s="8"/>
+      <c r="I137" s="7"/>
+      <c r="J137" s="7"/>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c r="M137" s="7"/>
@@ -5605,14 +5605,14 @@
         <v>13</v>
       </c>
       <c r="B138" s="7">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c t="s" r="C138" s="7">
         <v>14</v>
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5624,10 +5624,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>144</v>
+        <v>31</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>223</v>
+        <v>78</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5638,14 +5638,14 @@
         <v>13</v>
       </c>
       <c r="B139" s="7">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c t="s" r="C139" s="7">
         <v>14</v>
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5657,10 +5657,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>128</v>
+        <v>223</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5671,14 +5671,14 @@
         <v>13</v>
       </c>
       <c r="B140" s="7">
-        <v>439</v>
+        <v>507</v>
       </c>
       <c t="s" r="C140" s="7">
         <v>14</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5687,10 +5687,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c t="s" r="J140" s="7">
         <v>224</v>
@@ -5704,29 +5704,29 @@
         <v>13</v>
       </c>
       <c r="B141" s="7">
-        <v>438</v>
+        <v>510</v>
       </c>
       <c t="s" r="C141" s="7">
         <v>14</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5737,14 +5737,14 @@
         <v>13</v>
       </c>
       <c r="B142" s="7">
-        <v>7526</v>
+        <v>439</v>
       </c>
       <c t="s" r="C142" s="7">
         <v>14</v>
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5753,13 +5753,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H142" s="8">
+        <v>142</v>
+      </c>
+      <c t="s" r="I142" s="7">
+        <v>183</v>
+      </c>
+      <c t="s" r="J142" s="7">
         <v>225</v>
-      </c>
-      <c t="s" r="I142" s="7">
-        <v>109</v>
-      </c>
-      <c t="s" r="J142" s="7">
-        <v>29</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5767,114 +5767,114 @@
     </row>
     <row r="143" ht="14.25" customHeight="1">
       <c t="s" r="A143" s="6">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B143" s="7">
-        <v>7527</v>
+        <v>438</v>
       </c>
       <c t="s" r="C143" s="7">
         <v>14</v>
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>225</v>
+        <v>142</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>226</v>
+        <v>28</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>227</v>
+        <v>66</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c r="M143" s="7"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
-      <c r="A144" s="6"/>
-      <c r="B144" s="7"/>
-      <c r="C144" s="7"/>
+      <c t="s" r="A144" s="6">
+        <v>13</v>
+      </c>
+      <c r="B144" s="7">
+        <v>7526</v>
+      </c>
+      <c t="s" r="C144" s="7">
+        <v>14</v>
+      </c>
       <c r="D144" s="7"/>
-      <c r="E144" s="7"/>
-      <c r="F144" s="7"/>
-      <c r="G144" s="8"/>
-      <c r="H144" s="8"/>
-      <c r="I144" s="7"/>
-      <c r="J144" s="7"/>
+      <c t="s" r="E144" s="7">
+        <v>222</v>
+      </c>
+      <c r="F144" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G144" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H144" s="8">
+        <v>226</v>
+      </c>
+      <c t="s" r="I144" s="7">
+        <v>109</v>
+      </c>
+      <c t="s" r="J144" s="7">
+        <v>29</v>
+      </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c r="M144" s="7"/>
     </row>
     <row r="145" ht="15" customHeight="1">
       <c t="s" r="A145" s="6">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B145" s="7">
-        <v>849</v>
+        <v>7527</v>
       </c>
       <c t="s" r="C145" s="7">
         <v>14</v>
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
+        <v>222</v>
+      </c>
+      <c r="F145" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G145" s="8">
+        <v>226</v>
+      </c>
+      <c t="s" r="H145" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I145" s="7">
+        <v>227</v>
+      </c>
+      <c t="s" r="J145" s="7">
         <v>228</v>
-      </c>
-      <c r="F145" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G145" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H145" s="8">
-        <v>194</v>
-      </c>
-      <c t="s" r="I145" s="7">
-        <v>71</v>
-      </c>
-      <c t="s" r="J145" s="7">
-        <v>229</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c r="M145" s="7"/>
     </row>
     <row r="146" ht="14.25" customHeight="1">
-      <c t="s" r="A146" s="6">
-        <v>13</v>
-      </c>
-      <c r="B146" s="7">
-        <v>848</v>
-      </c>
-      <c t="s" r="C146" s="7">
-        <v>14</v>
-      </c>
+      <c r="A146" s="6"/>
+      <c r="B146" s="7"/>
+      <c r="C146" s="7"/>
       <c r="D146" s="7"/>
-      <c t="s" r="E146" s="7">
-        <v>228</v>
-      </c>
-      <c r="F146" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G146" s="8">
-        <v>194</v>
-      </c>
-      <c t="s" r="H146" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I146" s="7">
-        <v>127</v>
-      </c>
-      <c t="s" r="J146" s="7">
-        <v>160</v>
-      </c>
+      <c r="E146" s="7"/>
+      <c r="F146" s="7"/>
+      <c r="G146" s="8"/>
+      <c r="H146" s="8"/>
+      <c r="I146" s="7"/>
+      <c r="J146" s="7"/>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c r="M146" s="7"/>
@@ -5884,14 +5884,14 @@
         <v>13</v>
       </c>
       <c r="B147" s="7">
-        <v>352</v>
+        <v>849</v>
       </c>
       <c t="s" r="C147" s="7">
         <v>14</v>
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -5900,13 +5900,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H147" s="8">
+        <v>195</v>
+      </c>
+      <c t="s" r="I147" s="7">
+        <v>71</v>
+      </c>
+      <c t="s" r="J147" s="7">
         <v>230</v>
-      </c>
-      <c t="s" r="I147" s="7">
-        <v>116</v>
-      </c>
-      <c t="s" r="J147" s="7">
-        <v>84</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -5917,29 +5917,29 @@
         <v>13</v>
       </c>
       <c r="B148" s="7">
-        <v>353</v>
+        <v>848</v>
       </c>
       <c t="s" r="C148" s="7">
         <v>14</v>
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>66</v>
+        <v>129</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -5950,14 +5950,14 @@
         <v>13</v>
       </c>
       <c r="B149" s="7">
-        <v>652</v>
+        <v>352</v>
       </c>
       <c t="s" r="C149" s="7">
         <v>14</v>
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -5966,13 +5966,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>49</v>
+        <v>231</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -5983,45 +5983,63 @@
         <v>13</v>
       </c>
       <c r="B150" s="7">
-        <v>631</v>
+        <v>353</v>
       </c>
       <c t="s" r="C150" s="7">
         <v>14</v>
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>49</v>
+        <v>231</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c r="M150" s="7"/>
     </row>
     <row r="151" ht="14.25" customHeight="1">
-      <c r="A151" s="6"/>
-      <c r="B151" s="7"/>
-      <c r="C151" s="7"/>
+      <c t="s" r="A151" s="6">
+        <v>13</v>
+      </c>
+      <c r="B151" s="7">
+        <v>652</v>
+      </c>
+      <c t="s" r="C151" s="7">
+        <v>14</v>
+      </c>
       <c r="D151" s="7"/>
-      <c r="E151" s="7"/>
-      <c r="F151" s="7"/>
-      <c r="G151" s="8"/>
-      <c r="H151" s="8"/>
-      <c r="I151" s="7"/>
-      <c r="J151" s="7"/>
+      <c t="s" r="E151" s="7">
+        <v>229</v>
+      </c>
+      <c r="F151" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G151" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H151" s="8">
+        <v>49</v>
+      </c>
+      <c t="s" r="I151" s="7">
+        <v>108</v>
+      </c>
+      <c t="s" r="J151" s="7">
+        <v>109</v>
+      </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c r="M151" s="7"/>
@@ -6031,63 +6049,45 @@
         <v>13</v>
       </c>
       <c r="B152" s="7">
-        <v>272</v>
+        <v>631</v>
       </c>
       <c t="s" r="C152" s="7">
         <v>14</v>
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G152" s="8">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>193</v>
+        <v>124</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c r="M152" s="7"/>
     </row>
     <row r="153" ht="14.25" customHeight="1">
-      <c t="s" r="A153" s="6">
-        <v>13</v>
-      </c>
-      <c r="B153" s="7">
-        <v>693</v>
-      </c>
-      <c t="s" r="C153" s="7">
-        <v>14</v>
-      </c>
+      <c r="A153" s="6"/>
+      <c r="B153" s="7"/>
+      <c r="C153" s="7"/>
       <c r="D153" s="7"/>
-      <c t="s" r="E153" s="7">
-        <v>231</v>
-      </c>
-      <c r="F153" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G153" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="H153" s="8">
-        <v>111</v>
-      </c>
-      <c t="s" r="I153" s="7">
-        <v>52</v>
-      </c>
-      <c t="s" r="J153" s="7">
-        <v>116</v>
-      </c>
+      <c r="E153" s="7"/>
+      <c r="F153" s="7"/>
+      <c r="G153" s="8"/>
+      <c r="H153" s="8"/>
+      <c r="I153" s="7"/>
+      <c r="J153" s="7"/>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c r="M153" s="7"/>
@@ -6097,26 +6097,26 @@
         <v>13</v>
       </c>
       <c r="B154" s="7">
-        <v>692</v>
+        <v>272</v>
       </c>
       <c t="s" r="C154" s="7">
         <v>14</v>
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G154" s="8">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c t="s" r="H154" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>45</v>
+        <v>194</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>233</v>
@@ -6126,16 +6126,34 @@
       <c r="M154" s="7"/>
     </row>
     <row r="155" ht="15" customHeight="1">
-      <c r="A155" s="6"/>
-      <c r="B155" s="7"/>
-      <c r="C155" s="7"/>
+      <c t="s" r="A155" s="6">
+        <v>13</v>
+      </c>
+      <c r="B155" s="7">
+        <v>693</v>
+      </c>
+      <c t="s" r="C155" s="7">
+        <v>14</v>
+      </c>
       <c r="D155" s="7"/>
-      <c r="E155" s="7"/>
-      <c r="F155" s="7"/>
-      <c r="G155" s="8"/>
-      <c r="H155" s="8"/>
-      <c r="I155" s="7"/>
-      <c r="J155" s="7"/>
+      <c t="s" r="E155" s="7">
+        <v>232</v>
+      </c>
+      <c r="F155" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G155" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H155" s="8">
+        <v>111</v>
+      </c>
+      <c t="s" r="I155" s="7">
+        <v>52</v>
+      </c>
+      <c t="s" r="J155" s="7">
+        <v>116</v>
+      </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c r="M155" s="7"/>
@@ -6145,63 +6163,45 @@
         <v>13</v>
       </c>
       <c r="B156" s="7">
-        <v>224</v>
+        <v>692</v>
       </c>
       <c t="s" r="C156" s="7">
         <v>14</v>
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
+        <v>232</v>
+      </c>
+      <c r="F156" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G156" s="8">
+        <v>111</v>
+      </c>
+      <c t="s" r="H156" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I156" s="7">
+        <v>45</v>
+      </c>
+      <c t="s" r="J156" s="7">
         <v>234</v>
-      </c>
-      <c r="F156" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G156" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H156" s="8">
-        <v>235</v>
-      </c>
-      <c t="s" r="I156" s="7">
-        <v>236</v>
-      </c>
-      <c t="s" r="J156" s="7">
-        <v>192</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
       <c r="M156" s="7"/>
     </row>
     <row r="157" ht="14.25" customHeight="1">
-      <c t="s" r="A157" s="6">
-        <v>13</v>
-      </c>
-      <c r="B157" s="7">
-        <v>741</v>
-      </c>
-      <c t="s" r="C157" s="7">
-        <v>14</v>
-      </c>
+      <c r="A157" s="6"/>
+      <c r="B157" s="7"/>
+      <c r="C157" s="7"/>
       <c r="D157" s="7"/>
-      <c t="s" r="E157" s="7">
-        <v>234</v>
-      </c>
-      <c r="F157" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G157" s="8">
-        <v>235</v>
-      </c>
-      <c t="s" r="H157" s="8">
-        <v>230</v>
-      </c>
-      <c t="s" r="I157" s="7">
-        <v>237</v>
-      </c>
-      <c t="s" r="J157" s="7">
-        <v>238</v>
-      </c>
+      <c r="E157" s="7"/>
+      <c r="F157" s="7"/>
+      <c r="G157" s="8"/>
+      <c r="H157" s="8"/>
+      <c r="I157" s="7"/>
+      <c r="J157" s="7"/>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c r="M157" s="7"/>
@@ -6211,29 +6211,29 @@
         <v>13</v>
       </c>
       <c r="B158" s="7">
-        <v>740</v>
+        <v>224</v>
       </c>
       <c t="s" r="C158" s="7">
         <v>14</v>
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G158" s="8">
-        <v>230</v>
+        <v>16</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6244,29 +6244,29 @@
         <v>13</v>
       </c>
       <c r="B159" s="7">
-        <v>227</v>
+        <v>741</v>
       </c>
       <c t="s" r="C159" s="7">
         <v>14</v>
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>16</v>
+        <v>231</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>144</v>
+        <v>238</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>23</v>
+        <v>239</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6277,29 +6277,29 @@
         <v>13</v>
       </c>
       <c r="B160" s="7">
-        <v>252</v>
+        <v>740</v>
       </c>
       <c t="s" r="C160" s="7">
         <v>14</v>
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>16</v>
+        <v>231</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>86</v>
+        <v>236</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>51</v>
+        <v>240</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6310,29 +6310,29 @@
         <v>13</v>
       </c>
       <c r="B161" s="7">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c t="s" r="C161" s="7">
         <v>14</v>
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>86</v>
+        <v>236</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>240</v>
+        <v>23</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6343,14 +6343,14 @@
         <v>13</v>
       </c>
       <c r="B162" s="7">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c t="s" r="C162" s="7">
         <v>14</v>
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6359,13 +6359,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>235</v>
+        <v>86</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>241</v>
+        <v>51</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>242</v>
+        <v>183</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6376,45 +6376,63 @@
         <v>13</v>
       </c>
       <c r="B163" s="7">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c t="s" r="C163" s="7">
         <v>14</v>
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>235</v>
+        <v>86</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>243</v>
+        <v>52</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>162</v>
+        <v>241</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c r="M163" s="7"/>
     </row>
     <row r="164" ht="14.25" customHeight="1">
-      <c r="A164" s="6"/>
-      <c r="B164" s="7"/>
-      <c r="C164" s="7"/>
+      <c t="s" r="A164" s="6">
+        <v>13</v>
+      </c>
+      <c r="B164" s="7">
+        <v>216</v>
+      </c>
+      <c t="s" r="C164" s="7">
+        <v>14</v>
+      </c>
       <c r="D164" s="7"/>
-      <c r="E164" s="7"/>
-      <c r="F164" s="7"/>
-      <c r="G164" s="8"/>
-      <c r="H164" s="8"/>
-      <c r="I164" s="7"/>
-      <c r="J164" s="7"/>
+      <c t="s" r="E164" s="7">
+        <v>235</v>
+      </c>
+      <c r="F164" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G164" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H164" s="8">
+        <v>236</v>
+      </c>
+      <c t="s" r="I164" s="7">
+        <v>242</v>
+      </c>
+      <c t="s" r="J164" s="7">
+        <v>243</v>
+      </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c r="M164" s="7"/>
@@ -6424,63 +6442,45 @@
         <v>13</v>
       </c>
       <c r="B165" s="7">
-        <v>337</v>
+        <v>217</v>
       </c>
       <c t="s" r="C165" s="7">
         <v>14</v>
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
+        <v>235</v>
+      </c>
+      <c r="F165" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G165" s="8">
+        <v>236</v>
+      </c>
+      <c t="s" r="H165" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I165" s="7">
         <v>244</v>
       </c>
-      <c r="F165" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G165" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H165" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="I165" s="7">
-        <v>154</v>
-      </c>
       <c t="s" r="J165" s="7">
-        <v>33</v>
+        <v>163</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c r="M165" s="7"/>
     </row>
     <row r="166" ht="14.25" customHeight="1">
-      <c t="s" r="A166" s="6">
-        <v>13</v>
-      </c>
-      <c r="B166" s="7">
-        <v>324</v>
-      </c>
-      <c t="s" r="C166" s="7">
-        <v>14</v>
-      </c>
+      <c r="A166" s="6"/>
+      <c r="B166" s="7"/>
+      <c r="C166" s="7"/>
       <c r="D166" s="7"/>
-      <c t="s" r="E166" s="7">
-        <v>244</v>
-      </c>
-      <c r="F166" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G166" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="H166" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I166" s="7">
-        <v>245</v>
-      </c>
-      <c t="s" r="J166" s="7">
-        <v>50</v>
-      </c>
+      <c r="E166" s="7"/>
+      <c r="F166" s="7"/>
+      <c r="G166" s="8"/>
+      <c r="H166" s="8"/>
+      <c r="I166" s="7"/>
+      <c r="J166" s="7"/>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c r="M166" s="7"/>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6512,7 +6512,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6620,7 +6620,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I171" s="7">
         <v>248</v>
@@ -6650,7 +6650,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>17</v>
@@ -6686,13 +6686,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I173" s="7">
         <v>249</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6716,16 +6716,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6836,7 +6836,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c t="s" r="J178" s="7">
         <v>254</v>
@@ -6869,7 +6869,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>255</v>
@@ -6899,13 +6899,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I180" s="7">
         <v>256</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -6929,7 +6929,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>17</v>
@@ -6965,10 +6965,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>257</v>
@@ -6995,7 +6995,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="H183" s="8">
         <v>17</v>
@@ -7004,7 +7004,7 @@
         <v>117</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7046,7 +7046,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="I185" s="7">
         <v>100</v>
@@ -7076,7 +7076,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>17</v>
@@ -7085,7 +7085,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7115,10 +7115,10 @@
         <v>111</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7151,7 +7151,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7181,7 +7181,7 @@
         <v>259</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>71</v>
@@ -7229,7 +7229,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J191" s="7">
         <v>57</v>
@@ -7262,7 +7262,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J192" s="7">
         <v>112</v>
@@ -7295,7 +7295,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>113</v>
@@ -7361,7 +7361,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J195" s="7">
         <v>28</v>
@@ -7544,7 +7544,7 @@
         <v>266</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7577,7 +7577,7 @@
         <v>246</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7655,10 +7655,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>245</v>
+        <v>120</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7721,10 +7721,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7757,7 +7757,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7790,7 +7790,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7835,7 +7835,7 @@
         <v>271</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J211" s="7">
         <v>272</v>
@@ -7868,7 +7868,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J212" s="7">
         <v>73</v>
@@ -7934,10 +7934,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -7985,7 +7985,7 @@
         <v>276</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8015,10 +8015,10 @@
         <v>277</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8051,7 +8051,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8129,10 +8129,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8210,7 +8210,7 @@
         <v>86</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J224" s="7">
         <v>78</v>
@@ -8243,7 +8243,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>80</v>
@@ -8312,7 +8312,7 @@
         <v>284</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8345,7 +8345,7 @@
         <v>286</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8486,13 +8486,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="I233" s="7">
         <v>272</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8516,7 +8516,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>16</v>
@@ -8525,7 +8525,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8603,7 +8603,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>293</v>
@@ -8732,10 +8732,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>296</v>
@@ -8762,7 +8762,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>16</v>
@@ -8849,7 +8849,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J245" s="7">
         <v>114</v>
@@ -8885,7 +8885,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -8966,7 +8966,7 @@
         <v>306</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9179,7 +9179,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9275,7 +9275,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>274</v>
@@ -9356,10 +9356,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9422,7 +9422,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>314</v>
@@ -9572,7 +9572,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9617,10 +9617,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>245</v>
+        <v>120</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9683,10 +9683,10 @@
         <v>111</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9719,7 +9719,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9752,7 +9752,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9863,7 +9863,7 @@
         <v>99</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>321</v>
@@ -10040,10 +10040,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>90</v>
@@ -10070,7 +10070,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>16</v>
@@ -10142,10 +10142,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10193,7 +10193,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10223,10 +10223,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>245</v>
+        <v>120</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10289,7 +10289,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>83</v>
@@ -10325,7 +10325,7 @@
         <v>328</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10355,7 +10355,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>329</v>
@@ -10436,10 +10436,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10532,7 +10532,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c t="s" r="I301" s="7">
         <v>333</v>
@@ -10586,7 +10586,7 @@
         <v>254</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10649,7 +10649,7 @@
         <v>111</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c t="s" r="J305" s="7">
         <v>72</v>
@@ -10682,7 +10682,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>295</v>
@@ -10718,7 +10718,7 @@
         <v>313</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10751,7 +10751,7 @@
         <v>333</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10793,13 +10793,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -10823,7 +10823,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H311" s="8">
         <v>41</v>
@@ -10859,10 +10859,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J312" s="7">
         <v>283</v>
@@ -10889,13 +10889,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>263</v>
@@ -10943,10 +10943,10 @@
         <v>265</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -10979,7 +10979,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11009,7 +11009,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>63</v>
@@ -11052,7 +11052,7 @@
       </c>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -11124,13 +11124,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c t="s" r="I321" s="7">
         <v>263</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11154,7 +11154,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>16</v>
@@ -11229,7 +11229,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11259,7 +11259,7 @@
         <v>325</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>272</v>
@@ -11322,7 +11322,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c t="s" r="I327" s="7">
         <v>115</v>
@@ -11352,13 +11352,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>106</v>
@@ -11394,7 +11394,7 @@
         <v>341</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11472,10 +11472,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11538,7 +11538,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>295</v>
@@ -11568,10 +11568,10 @@
         <v>49</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>94</v>
@@ -11598,7 +11598,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>49</v>
@@ -11637,7 +11637,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J337" s="7">
         <v>345</v>
@@ -11685,7 +11685,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>306</v>
@@ -11718,7 +11718,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>245</v>
+        <v>120</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>113</v>
@@ -11784,7 +11784,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J342" s="7">
         <v>52</v>
@@ -11865,10 +11865,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12144,7 +12144,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>28</v>
@@ -12291,7 +12291,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>90</v>
@@ -12327,7 +12327,7 @@
         <v>63</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12390,7 +12390,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J362" s="7">
         <v>344</v>
@@ -12474,7 +12474,7 @@
         <v>264</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12606,7 +12606,7 @@
         <v>313</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12639,7 +12639,7 @@
         <v>107</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12681,13 +12681,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12711,13 +12711,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c t="s" r="J373" s="7">
         <v>358</v>
@@ -12828,13 +12828,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12858,7 +12858,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>16</v>
@@ -12963,10 +12963,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13005,7 +13005,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>17</v>
@@ -13014,7 +13014,7 @@
         <v>351</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13047,7 +13047,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13080,7 +13080,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13146,7 +13146,7 @@
         <v>366</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13224,7 +13224,7 @@
         <v>282</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>23</v>
@@ -13257,10 +13257,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13299,16 +13299,16 @@
         <v>330</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13407,7 +13407,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13446,16 +13446,16 @@
         <v>330</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13566,7 +13566,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>71</v>
@@ -13583,7 +13583,7 @@
         <v>2866</v>
       </c>
       <c t="s" r="C403" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
@@ -13599,7 +13599,7 @@
         <v>376</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>91</v>
@@ -13616,7 +13616,7 @@
         <v>2867</v>
       </c>
       <c t="s" r="C404" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
@@ -13716,7 +13716,7 @@
         <v>273</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13791,13 +13791,13 @@
         <v>381</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I410" s="7">
         <v>264</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -13893,7 +13893,7 @@
         <v>316</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -13926,7 +13926,7 @@
         <v>385</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>

--- a/Data/FlightPlan/FPL_07OCT26.xlsx
+++ b/Data/FlightPlan/FPL_07OCT26.xlsx
@@ -113,6 +113,9 @@
     <t>12:20</t>
   </si>
   <si>
+    <t>12:59</t>
+  </si>
+  <si>
     <t>HKG</t>
   </si>
   <si>
@@ -131,6 +134,9 @@
     <t>VN-A203</t>
   </si>
   <si>
+    <t>12:17</t>
+  </si>
+  <si>
     <t>HPH</t>
   </si>
   <si>
@@ -254,6 +260,9 @@
     <t>12:45</t>
   </si>
   <si>
+    <t>12:52</t>
+  </si>
+  <si>
     <t>13:15</t>
   </si>
   <si>
@@ -296,6 +305,9 @@
     <t>10:30</t>
   </si>
   <si>
+    <t>11:43</t>
+  </si>
+  <si>
     <t>12:25</t>
   </si>
   <si>
@@ -332,6 +344,9 @@
     <t>12:15</t>
   </si>
   <si>
+    <t>12:35</t>
+  </si>
+  <si>
     <t>14:20</t>
   </si>
   <si>
@@ -350,6 +365,9 @@
     <t>10:50</t>
   </si>
   <si>
+    <t>12:21</t>
+  </si>
+  <si>
     <t>TPE</t>
   </si>
   <si>
@@ -434,6 +452,9 @@
     <t>11:10</t>
   </si>
   <si>
+    <t>11:37</t>
+  </si>
+  <si>
     <t>21:15</t>
   </si>
   <si>
@@ -446,6 +467,9 @@
     <t>14:30</t>
   </si>
   <si>
+    <t>14:59</t>
+  </si>
+  <si>
     <t>19:10</t>
   </si>
   <si>
@@ -605,6 +629,9 @@
     <t>DPS</t>
   </si>
   <si>
+    <t>16:59</t>
+  </si>
+  <si>
     <t>17:30</t>
   </si>
   <si>
@@ -650,6 +677,9 @@
     <t>11:40</t>
   </si>
   <si>
+    <t>16:04</t>
+  </si>
+  <si>
     <t>VTE</t>
   </si>
   <si>
@@ -764,6 +794,9 @@
     <t>10:29</t>
   </si>
   <si>
+    <t>12:30</t>
+  </si>
+  <si>
     <t>18:10</t>
   </si>
   <si>
@@ -824,9 +857,6 @@
     <t>11:50</t>
   </si>
   <si>
-    <t>12:30</t>
-  </si>
-  <si>
     <t>VN-A640</t>
   </si>
   <si>
@@ -842,6 +872,9 @@
     <t>10:36</t>
   </si>
   <si>
+    <t>12:33</t>
+  </si>
+  <si>
     <t>18:45</t>
   </si>
   <si>
@@ -965,6 +998,9 @@
     <t>12:05</t>
   </si>
   <si>
+    <t>12:04</t>
+  </si>
+  <si>
     <t>16:55</t>
   </si>
   <si>
@@ -983,9 +1019,6 @@
     <t>KUL</t>
   </si>
   <si>
-    <t>12:35</t>
-  </si>
-  <si>
     <t>12:46</t>
   </si>
   <si>
@@ -1004,6 +1037,9 @@
     <t>10:20</t>
   </si>
   <si>
+    <t>12:49</t>
+  </si>
+  <si>
     <t>01:15</t>
   </si>
   <si>
@@ -1040,153 +1076,162 @@
     <t>10:15</t>
   </si>
   <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>10:57</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:07</t>
+  </si>
+  <si>
+    <t>08:58</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>10:39</t>
+  </si>
+  <si>
+    <t>12:19</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>10:48</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>11:38</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>12:32</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>09:06</t>
+  </si>
+  <si>
+    <t>11:52</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>10:07</t>
+  </si>
+  <si>
+    <t>12:06</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>09:04</t>
+  </si>
+  <si>
+    <t>11:07</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>10:27</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>08:06</t>
+  </si>
+  <si>
     <t>13:05</t>
   </si>
   <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>10:57</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:07</t>
-  </si>
-  <si>
-    <t>08:58</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>10:39</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>10:48</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>11:38</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>09:06</t>
-  </si>
-  <si>
-    <t>11:52</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>10:07</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>09:04</t>
-  </si>
-  <si>
-    <t>11:07</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>10:27</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>08:06</t>
-  </si>
-  <si>
     <t>VN-A685</t>
   </si>
   <si>
@@ -1196,6 +1241,9 @@
     <t>VN-A687</t>
   </si>
   <si>
+    <t>13:41</t>
+  </si>
+  <si>
     <t>19:30</t>
   </si>
   <si>
@@ -1283,7 +1331,7 @@
     <t>KJA</t>
   </si>
   <si>
-    <t>17:21</t>
+    <t>17:34</t>
   </si>
   <si>
     <t>01:55</t>
@@ -1310,19 +1358,22 @@
     <t>VN-A817</t>
   </si>
   <si>
+    <t>BNE</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
     <t>VN-A820</t>
   </si>
   <si>
-    <t>BNE</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
     <t>Total Record(s): 335</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 07, 2026 10:20</t>
+    <t xml:space="preserve">Generated on  Oct 07, 2026 11:15</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2053,7 +2104,9 @@
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
+      <c t="s" r="M12" s="7">
+        <v>34</v>
+      </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c t="s" r="A13" s="6">
@@ -2076,13 +2129,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H13" s="8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c t="s" r="I13" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c t="s" r="J13" s="7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
@@ -2106,16 +2159,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G14" s="8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c t="s" r="H14" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I14" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c t="s" r="J14" s="7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
@@ -2148,7 +2201,7 @@
       </c>
       <c r="D16" s="7"/>
       <c t="s" r="E16" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F16" s="7">
         <v>321</v>
@@ -2167,7 +2220,9 @@
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
+      <c t="s" r="M16" s="7">
+        <v>41</v>
+      </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c t="s" r="A17" s="6">
@@ -2181,7 +2236,7 @@
       </c>
       <c r="D17" s="7"/>
       <c t="s" r="E17" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F17" s="7">
         <v>321</v>
@@ -2190,13 +2245,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H17" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="I17" s="7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c t="s" r="J17" s="7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
@@ -2214,22 +2269,22 @@
       </c>
       <c r="D18" s="7"/>
       <c t="s" r="E18" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F18" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G18" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="H18" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I18" s="7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c t="s" r="J18" s="7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
@@ -2237,7 +2292,7 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c t="s" r="A19" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B19" s="7">
         <v>862</v>
@@ -2247,7 +2302,7 @@
       </c>
       <c r="D19" s="7"/>
       <c t="s" r="E19" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F19" s="7">
         <v>321</v>
@@ -2259,7 +2314,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I19" s="7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c t="s" r="J19" s="7">
         <v>30</v>
@@ -2295,22 +2350,22 @@
       </c>
       <c r="D21" s="7"/>
       <c t="s" r="E21" s="7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F21" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G21" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H21" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I21" s="7">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c t="s" r="J21" s="7">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
@@ -2328,7 +2383,7 @@
       </c>
       <c r="D22" s="7"/>
       <c t="s" r="E22" s="7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F22" s="7">
         <v>321</v>
@@ -2340,10 +2395,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I22" s="7">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c t="s" r="J22" s="7">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
@@ -2361,7 +2416,7 @@
       </c>
       <c r="D23" s="7"/>
       <c t="s" r="E23" s="7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F23" s="7">
         <v>321</v>
@@ -2370,13 +2425,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H23" s="8">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c t="s" r="I23" s="7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c t="s" r="J23" s="7">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
@@ -2384,7 +2439,7 @@
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c t="s" r="A24" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B24" s="7">
         <v>910</v>
@@ -2394,22 +2449,22 @@
       </c>
       <c r="D24" s="7"/>
       <c t="s" r="E24" s="7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F24" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G24" s="8">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c t="s" r="H24" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I24" s="7">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c t="s" r="J24" s="7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
@@ -2442,7 +2497,7 @@
       </c>
       <c r="D26" s="7"/>
       <c t="s" r="E26" s="7">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F26" s="7">
         <v>321</v>
@@ -2451,18 +2506,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H26" s="8">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c t="s" r="I26" s="7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c t="s" r="J26" s="7">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
       <c t="s" r="M26" s="7">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
@@ -2477,22 +2532,22 @@
       </c>
       <c r="D27" s="7"/>
       <c t="s" r="E27" s="7">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F27" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G27" s="8">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c t="s" r="H27" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I27" s="7">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c t="s" r="J27" s="7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
@@ -2525,7 +2580,7 @@
       </c>
       <c r="D29" s="7"/>
       <c t="s" r="E29" s="7">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F29" s="7">
         <v>321</v>
@@ -2537,15 +2592,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I29" s="7">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c t="s" r="J29" s="7">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
       <c t="s" r="M29" s="7">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
@@ -2560,7 +2615,7 @@
       </c>
       <c r="D30" s="7"/>
       <c t="s" r="E30" s="7">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F30" s="7">
         <v>321</v>
@@ -2572,15 +2627,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I30" s="7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c t="s" r="J30" s="7">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
       <c t="s" r="M30" s="7">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
@@ -2595,7 +2650,7 @@
       </c>
       <c r="D31" s="7"/>
       <c t="s" r="E31" s="7">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F31" s="7">
         <v>321</v>
@@ -2607,10 +2662,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I31" s="7">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c t="s" r="J31" s="7">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -2628,7 +2683,7 @@
       </c>
       <c r="D32" s="7"/>
       <c t="s" r="E32" s="7">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F32" s="7">
         <v>321</v>
@@ -2640,10 +2695,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I32" s="7">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c t="s" r="J32" s="7">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
@@ -2661,7 +2716,7 @@
       </c>
       <c r="D33" s="7"/>
       <c t="s" r="E33" s="7">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F33" s="7">
         <v>321</v>
@@ -2673,10 +2728,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I33" s="7">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c t="s" r="J33" s="7">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -2709,7 +2764,7 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
@@ -2718,17 +2773,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H35" s="8">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c t="s" r="I35" s="7">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
+      <c t="s" r="M35" s="7">
+        <v>83</v>
+      </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c t="s" r="A36" s="6">
@@ -2742,22 +2799,22 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G36" s="8">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c t="s" r="H36" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I36" s="7">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -2775,7 +2832,7 @@
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
@@ -2784,13 +2841,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H37" s="8">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c t="s" r="I37" s="7">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -2808,22 +2865,22 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G38" s="8">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c t="s" r="H38" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
@@ -2856,7 +2913,7 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
@@ -2865,18 +2922,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H40" s="8">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
       <c t="s" r="M40" s="7">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
@@ -2891,19 +2948,19 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G41" s="8">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c t="s" r="H41" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c t="s" r="J41" s="7">
         <v>18</v>
@@ -2911,7 +2968,7 @@
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
       <c t="s" r="M41" s="7">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
@@ -2926,7 +2983,7 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
@@ -2935,17 +2992,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H42" s="8">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
+      <c t="s" r="M42" s="7">
+        <v>98</v>
+      </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c t="s" r="A43" s="6">
@@ -2959,22 +3018,22 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G43" s="8">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c t="s" r="H43" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -2992,7 +3051,7 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
@@ -3001,13 +3060,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H44" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -3025,22 +3084,22 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G45" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H45" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -3058,7 +3117,7 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -3067,13 +3126,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H46" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -3091,22 +3150,22 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G47" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H47" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -3139,7 +3198,7 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
@@ -3148,17 +3207,19 @@
         <v>28</v>
       </c>
       <c t="s" r="H49" s="8">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
+      <c t="s" r="M49" s="7">
+        <v>111</v>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c t="s" r="A50" s="6">
@@ -3172,22 +3233,22 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G50" s="8">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c t="s" r="H50" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3205,7 +3266,7 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
@@ -3217,10 +3278,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3238,7 +3299,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3250,10 +3311,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3286,7 +3347,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3298,7 +3359,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c t="s" r="J54" s="7">
         <v>32</v>
@@ -3306,7 +3367,7 @@
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c t="s" r="M54" s="7">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
@@ -3321,7 +3382,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3333,14 +3394,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
-      <c r="M55" s="7"/>
+      <c t="s" r="M55" s="7">
+        <v>118</v>
+      </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c t="s" r="A56" s="6">
@@ -3354,7 +3417,7 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
@@ -3363,13 +3426,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H56" s="8">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3387,22 +3450,22 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G57" s="8">
+        <v>119</v>
+      </c>
+      <c t="s" r="H57" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I57" s="7">
+        <v>121</v>
+      </c>
+      <c t="s" r="J57" s="7">
         <v>113</v>
-      </c>
-      <c t="s" r="H57" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I57" s="7">
-        <v>115</v>
-      </c>
-      <c t="s" r="J57" s="7">
-        <v>108</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3420,7 +3483,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3432,7 +3495,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c t="s" r="J58" s="7">
         <v>26</v>
@@ -3468,19 +3531,19 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G60" s="8">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c t="s" r="H60" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c t="s" r="J60" s="7">
         <v>32</v>
@@ -3488,7 +3551,7 @@
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
       <c t="s" r="M60" s="7">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -3503,22 +3566,22 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G61" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H61" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -3536,7 +3599,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3545,13 +3608,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H62" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3569,22 +3632,22 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G63" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H63" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3602,7 +3665,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3611,13 +3674,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H64" s="8">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -3625,7 +3688,7 @@
     </row>
     <row r="65" ht="15" customHeight="1">
       <c t="s" r="A65" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B65" s="7">
         <v>896</v>
@@ -3635,22 +3698,22 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G65" s="8">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c t="s" r="H65" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -3683,7 +3746,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -3695,7 +3758,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c t="s" r="J67" s="7">
         <v>33</v>
@@ -3703,7 +3766,7 @@
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
       <c t="s" r="M67" s="7">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
@@ -3718,7 +3781,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -3727,13 +3790,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H68" s="8">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3751,22 +3814,22 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G69" s="8">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c t="s" r="H69" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3799,7 +3862,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3808,18 +3871,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H71" s="8">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c t="s" r="M71" s="7">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -3834,26 +3897,28 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G72" s="8">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c t="s" r="H72" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
-      <c r="M72" s="7"/>
+      <c t="s" r="M72" s="7">
+        <v>147</v>
+      </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c t="s" r="A73" s="6">
@@ -3867,7 +3932,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3882,7 +3947,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3900,7 +3965,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -3912,10 +3977,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -3948,7 +4013,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -3957,17 +4022,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H76" s="8">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c t="s" r="I76" s="7">
         <v>32</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
-      <c r="M76" s="7"/>
+      <c t="s" r="M76" s="7">
+        <v>152</v>
+      </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c t="s" r="A77" s="6">
@@ -3981,22 +4048,22 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c t="s" r="H77" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -4014,7 +4081,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4026,10 +4093,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -4043,11 +4110,11 @@
         <v>3523</v>
       </c>
       <c t="s" r="C79" s="7">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4059,10 +4126,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -4070,17 +4137,17 @@
     </row>
     <row r="80" ht="15" customHeight="1">
       <c t="s" r="A80" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B80" s="7">
         <v>3523</v>
       </c>
       <c t="s" r="C80" s="7">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4089,13 +4156,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4128,27 +4195,27 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G82" s="8">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c t="s" r="H82" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
       <c t="s" r="M82" s="7">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -4163,7 +4230,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4175,10 +4242,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4196,7 +4263,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4205,13 +4272,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4229,22 +4296,22 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4277,7 +4344,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4286,10 +4353,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H87" s="8">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c t="s" r="J87" s="7">
         <v>19</v>
@@ -4297,7 +4364,7 @@
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c t="s" r="M87" s="7">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
@@ -4312,22 +4379,22 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G88" s="8">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c t="s" r="H88" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4345,7 +4412,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4357,10 +4424,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4378,7 +4445,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4387,13 +4454,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H90" s="8">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4422,23 +4489,23 @@
         <v>7707</v>
       </c>
       <c t="s" r="C92" s="7">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c t="s" r="J92" s="7">
         <v>22</v>
@@ -4446,7 +4513,7 @@
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
       <c t="s" r="M92" s="7">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
@@ -4457,11 +4524,11 @@
         <v>7707</v>
       </c>
       <c t="s" r="C93" s="7">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4470,13 +4537,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4494,22 +4561,22 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4527,7 +4594,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4539,10 +4606,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4571,11 +4638,11 @@
         <v>5069</v>
       </c>
       <c t="s" r="C97" s="7">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4584,18 +4651,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -4606,26 +4673,26 @@
         <v>7620</v>
       </c>
       <c t="s" r="C98" s="7">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="H98" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4639,11 +4706,11 @@
         <v>7620</v>
       </c>
       <c t="s" r="C99" s="7">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4652,13 +4719,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4666,32 +4733,32 @@
     </row>
     <row r="100" ht="15" customHeight="1">
       <c t="s" r="A100" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B100" s="7">
         <v>7621</v>
       </c>
       <c t="s" r="C100" s="7">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c t="s" r="H100" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4724,22 +4791,22 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4757,22 +4824,22 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c t="s" r="H103" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4790,22 +4857,22 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G104" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H104" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4813,7 +4880,7 @@
     </row>
     <row r="105" ht="15" customHeight="1">
       <c t="s" r="A105" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B105" s="7">
         <v>868</v>
@@ -4823,7 +4890,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4832,13 +4899,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H105" s="8">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4871,7 +4938,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4883,15 +4950,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
       <c t="s" r="M107" s="7">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -4906,7 +4973,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4915,17 +4982,19 @@
         <v>28</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
-      <c r="M108" s="7"/>
+      <c t="s" r="M108" s="7">
+        <v>206</v>
+      </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
       <c t="s" r="A109" s="6">
@@ -4939,22 +5008,22 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4962,7 +5031,7 @@
     </row>
     <row r="110" ht="15" customHeight="1">
       <c t="s" r="A110" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B110" s="7">
         <v>938</v>
@@ -4972,7 +5041,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -4984,10 +5053,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -5020,7 +5089,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5032,15 +5101,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>203</v>
+        <v>212</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5055,7 +5124,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5064,13 +5133,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5088,22 +5157,22 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H114" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5121,7 +5190,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5130,13 +5199,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5154,22 +5223,22 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="H116" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5177,7 +5246,7 @@
     </row>
     <row r="117" ht="14.25" customHeight="1">
       <c t="s" r="A117" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B117" s="7">
         <v>7704</v>
@@ -5187,7 +5256,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5196,13 +5265,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5235,7 +5304,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5247,14 +5316,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
-      <c r="M119" s="7"/>
+      <c t="s" r="M119" s="7">
+        <v>222</v>
+      </c>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c t="s" r="A120" s="6">
@@ -5268,7 +5339,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5277,13 +5348,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5301,22 +5372,22 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5324,7 +5395,7 @@
     </row>
     <row r="122" ht="14.25" customHeight="1">
       <c t="s" r="A122" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B122" s="7">
         <v>91</v>
@@ -5334,7 +5405,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5343,13 +5414,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5382,29 +5453,29 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c t="s" r="K124" s="7">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -5419,22 +5490,22 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="H125" s="8">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5452,22 +5523,22 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5475,7 +5546,7 @@
     </row>
     <row r="127" ht="14.25" customHeight="1">
       <c t="s" r="A127" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B127" s="7">
         <v>918</v>
@@ -5485,19 +5556,19 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G127" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>31</v>
@@ -5533,7 +5604,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5542,18 +5613,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H129" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I129" s="7">
         <v>29</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>226</v>
+        <v>236</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -5568,27 +5639,27 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H130" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c t="s" r="M130" s="7">
-        <v>228</v>
+        <v>238</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -5603,7 +5674,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5612,20 +5683,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="I131" s="7">
+        <v>239</v>
+      </c>
+      <c t="s" r="J131" s="7">
         <v>229</v>
       </c>
-      <c t="s" r="J131" s="7">
-        <v>219</v>
-      </c>
       <c t="s" r="K131" s="7">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -5640,22 +5711,22 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5673,7 +5744,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5682,13 +5753,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5706,22 +5777,22 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c t="s" r="H134" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5739,7 +5810,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5748,10 +5819,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c t="s" r="J135" s="7">
         <v>26</v>
@@ -5762,7 +5833,7 @@
     </row>
     <row r="136" ht="14.25" customHeight="1">
       <c t="s" r="A136" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B136" s="7">
         <v>7527</v>
@@ -5772,22 +5843,22 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5820,7 +5891,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5829,13 +5900,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5855,22 +5926,22 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5888,7 +5959,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5897,13 +5968,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5921,22 +5992,22 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5954,7 +6025,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5963,13 +6034,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5987,22 +6058,22 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6035,7 +6106,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6044,18 +6115,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>240</v>
+        <v>250</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6070,22 +6141,22 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6103,22 +6174,22 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6151,7 +6222,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6160,18 +6231,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c t="s" r="M149" s="7">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
@@ -6186,27 +6257,27 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c t="s" r="M150" s="7">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
@@ -6221,27 +6292,27 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c t="s" r="H151" s="8">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6256,26 +6327,28 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G152" s="8">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c t="s" r="H152" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c t="s" r="J152" s="7">
         <v>19</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
-      <c r="M152" s="7"/>
+      <c t="s" r="M152" s="7">
+        <v>261</v>
+      </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
       <c t="s" r="A153" s="6">
@@ -6289,7 +6362,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6298,13 +6371,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H153" s="8">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6322,22 +6395,22 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G154" s="8">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c t="s" r="H154" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6355,7 +6428,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6364,13 +6437,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6388,22 +6461,22 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6436,7 +6509,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6445,13 +6518,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6469,22 +6542,22 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6502,7 +6575,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6514,10 +6587,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6535,7 +6608,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6547,10 +6620,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6583,7 +6656,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6592,18 +6665,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>262</v>
+        <v>273</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -6618,27 +6691,27 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>263</v>
+        <v>274</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -6653,7 +6726,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6662,13 +6735,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6686,22 +6759,22 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6719,7 +6792,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6728,13 +6801,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I167" s="7">
         <v>25</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6752,22 +6825,22 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6800,7 +6873,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6812,15 +6885,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -6835,7 +6908,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6847,15 +6920,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>270</v>
+        <v>281</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -6870,7 +6943,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6879,16 +6952,16 @@
         <v>28</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c t="s" r="K172" s="7">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
@@ -6907,29 +6980,29 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c t="s" r="K173" s="7">
         <v>22</v>
       </c>
       <c r="L173" s="7"/>
       <c t="s" r="M173" s="7">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -6944,7 +7017,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6953,13 +7026,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6977,22 +7050,22 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -7025,7 +7098,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7034,17 +7107,19 @@
         <v>28</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
-      <c r="M177" s="7"/>
+      <c t="s" r="M177" s="7">
+        <v>111</v>
+      </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
       <c t="s" r="A178" s="6">
@@ -7058,22 +7133,22 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7091,7 +7166,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7100,13 +7175,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H179" s="8">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7124,22 +7199,22 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c t="s" r="H180" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7147,7 +7222,7 @@
     </row>
     <row r="181" ht="14.25" customHeight="1">
       <c t="s" r="A181" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B181" s="7">
         <v>958</v>
@@ -7157,7 +7232,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7166,13 +7241,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7205,7 +7280,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7217,15 +7292,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>275</v>
+        <v>285</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7240,7 +7315,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7249,18 +7324,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>276</v>
+        <v>286</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -7275,26 +7350,28 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G185" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H185" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
-      <c r="M185" s="7"/>
+      <c t="s" r="M185" s="7">
+        <v>287</v>
+      </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
       <c t="s" r="A186" s="6">
@@ -7308,7 +7385,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7323,7 +7400,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7341,7 +7418,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7353,7 +7430,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c t="s" r="J187" s="7">
         <v>25</v>
@@ -7374,7 +7451,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7383,13 +7460,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7407,22 +7484,22 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H189" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7455,27 +7532,27 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>283</v>
+        <v>294</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -7490,7 +7567,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7499,18 +7576,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I192" s="7">
         <v>29</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -7525,22 +7602,22 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7558,22 +7635,22 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7606,7 +7683,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7618,15 +7695,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>288</v>
+        <v>299</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -7641,7 +7718,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7653,15 +7730,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -7676,7 +7753,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7688,10 +7765,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7709,7 +7786,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7721,10 +7798,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7742,7 +7819,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7754,10 +7831,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7775,7 +7852,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7784,13 +7861,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7823,7 +7900,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7832,13 +7909,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7856,22 +7933,22 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7889,7 +7966,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7898,13 +7975,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7922,22 +7999,22 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7970,7 +8047,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7982,15 +8059,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8005,7 +8082,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8014,13 +8091,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -8038,22 +8115,22 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -8071,7 +8148,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8083,10 +8160,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8119,27 +8196,27 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8154,7 +8231,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8163,13 +8240,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8202,7 +8279,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8211,18 +8288,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>301</v>
+        <v>312</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8237,27 +8314,27 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>302</v>
+        <v>313</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8272,7 +8349,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8281,13 +8358,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8305,22 +8382,22 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8338,7 +8415,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8347,13 +8424,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8361,7 +8438,7 @@
     </row>
     <row r="221" ht="14.25" customHeight="1">
       <c t="s" r="A221" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B221" s="7">
         <v>3901</v>
@@ -8371,22 +8448,22 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8419,7 +8496,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8428,18 +8505,18 @@
         <v>24</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>276</v>
+        <v>286</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -8454,19 +8531,19 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c t="s" r="J224" s="7">
         <v>20</v>
@@ -8487,7 +8564,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8496,13 +8573,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8520,22 +8597,22 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8568,7 +8645,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8577,10 +8654,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>29</v>
@@ -8588,7 +8665,7 @@
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>313</v>
+        <v>324</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -8603,27 +8680,27 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>316</v>
+        <v>327</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -8638,7 +8715,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8647,17 +8724,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
-      <c r="M230" s="7"/>
+      <c t="s" r="M230" s="7">
+        <v>329</v>
+      </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
       <c t="s" r="A231" s="6">
@@ -8671,22 +8750,22 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8704,22 +8783,22 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8737,7 +8816,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8746,13 +8825,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8760,7 +8839,7 @@
     </row>
     <row r="234" ht="14.25" customHeight="1">
       <c t="s" r="A234" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B234" s="7">
         <v>3909</v>
@@ -8770,22 +8849,22 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8818,7 +8897,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8827,18 +8906,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c t="s" r="I236" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>324</v>
+        <v>111</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -8853,22 +8932,22 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8886,7 +8965,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8895,13 +8974,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8909,7 +8988,7 @@
     </row>
     <row r="239" ht="14.25" customHeight="1">
       <c t="s" r="A239" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B239" s="7">
         <v>821</v>
@@ -8919,22 +8998,22 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8967,7 +9046,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="F241" s="7">
         <v>320</v>
@@ -8976,17 +9055,19 @@
         <v>28</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
-      <c r="M241" s="7"/>
+      <c t="s" r="M241" s="7">
+        <v>342</v>
+      </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
       <c t="s" r="A242" s="6">
@@ -9000,13 +9081,13 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="F242" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>28</v>
@@ -9015,7 +9096,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -9033,7 +9114,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="F243" s="7">
         <v>320</v>
@@ -9042,13 +9123,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9066,22 +9147,22 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="F244" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c t="s" r="H244" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9099,7 +9180,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="F245" s="7">
         <v>320</v>
@@ -9108,13 +9189,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9122,7 +9203,7 @@
     </row>
     <row r="246" ht="14.25" customHeight="1">
       <c t="s" r="A246" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B246" s="7">
         <v>7239</v>
@@ -9132,22 +9213,22 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="F246" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9180,7 +9261,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9189,18 +9270,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9215,29 +9296,29 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="K249" s="7">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -9252,7 +9333,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9261,13 +9342,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9285,13 +9366,13 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>17</v>
@@ -9300,7 +9381,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9333,7 +9414,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
@@ -9342,18 +9423,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>338</v>
+        <v>350</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -9368,22 +9449,22 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="F254" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9401,7 +9482,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="F255" s="7">
         <v>320</v>
@@ -9413,10 +9494,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9434,7 +9515,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="F256" s="7">
         <v>320</v>
@@ -9446,10 +9527,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9482,7 +9563,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9491,18 +9572,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -9517,27 +9598,27 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>343</v>
+        <v>275</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -9552,22 +9633,22 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9585,7 +9666,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9594,13 +9675,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9633,7 +9714,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="F263" s="7">
         <v>320</v>
@@ -9645,15 +9726,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>345</v>
+        <v>356</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -9668,7 +9749,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
@@ -9680,10 +9761,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9701,7 +9782,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
@@ -9710,13 +9791,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9734,22 +9815,22 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9767,7 +9848,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
@@ -9779,10 +9860,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9815,7 +9896,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9824,18 +9905,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>349</v>
+        <v>360</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -9850,13 +9931,13 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>28</v>
@@ -9865,12 +9946,12 @@
         <v>29</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>350</v>
+        <v>361</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -9885,7 +9966,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9894,18 +9975,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H271" s="8">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>352</v>
+        <v>363</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -9920,26 +10001,28 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c t="s" r="H272" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c t="s" r="J272" s="7">
         <v>33</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
-      <c r="M272" s="7"/>
+      <c t="s" r="M272" s="7">
+        <v>364</v>
+      </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
       <c t="s" r="A273" s="6">
@@ -9953,7 +10036,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9962,13 +10045,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c t="s" r="I273" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9986,22 +10069,22 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -10009,7 +10092,7 @@
     </row>
     <row r="275" ht="15" customHeight="1">
       <c t="s" r="A275" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B275" s="7">
         <v>960</v>
@@ -10019,7 +10102,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10031,10 +10114,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -10067,7 +10150,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -10076,13 +10159,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10100,22 +10183,22 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10133,7 +10216,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10142,13 +10225,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10166,22 +10249,22 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10214,7 +10297,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10223,18 +10306,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -10249,27 +10332,27 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>358</v>
+        <v>370</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10284,7 +10367,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10296,10 +10379,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10317,7 +10400,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10329,10 +10412,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10350,7 +10433,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10359,13 +10442,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10373,7 +10456,7 @@
     </row>
     <row r="287" ht="14.25" customHeight="1">
       <c t="s" r="A287" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B287" s="7">
         <v>7713</v>
@@ -10383,22 +10466,22 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10431,7 +10514,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10440,18 +10523,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>365</v>
+        <v>377</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -10466,22 +10549,22 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10499,7 +10582,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10508,13 +10591,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10532,13 +10615,13 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>28</v>
@@ -10547,7 +10630,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10555,7 +10638,7 @@
     </row>
     <row r="293" ht="14.25" customHeight="1">
       <c t="s" r="A293" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B293" s="7">
         <v>982</v>
@@ -10565,7 +10648,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -10574,13 +10657,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10613,7 +10696,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10622,13 +10705,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10646,22 +10729,22 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10679,7 +10762,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10688,13 +10771,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10712,22 +10795,22 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10760,7 +10843,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -10769,18 +10852,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>342</v>
+        <v>354</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -10795,19 +10878,19 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>19</v>
@@ -10828,7 +10911,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -10837,13 +10920,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10861,22 +10944,22 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10894,7 +10977,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -10903,13 +10986,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10917,7 +11000,7 @@
     </row>
     <row r="305" ht="15" customHeight="1">
       <c t="s" r="A305" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B305" s="7">
         <v>3949</v>
@@ -10927,22 +11010,22 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10975,7 +11058,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -10984,18 +11067,18 @@
         <v>24</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>370</v>
+        <v>382</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11010,26 +11093,28 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
-      <c r="M308" s="7"/>
+      <c t="s" r="M308" s="7">
+        <v>383</v>
+      </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
       <c t="s" r="A309" s="6">
@@ -11043,22 +11128,22 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -11076,22 +11161,22 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -11124,7 +11209,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11133,18 +11218,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>372</v>
+        <v>385</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -11159,13 +11244,13 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>28</v>
@@ -11174,12 +11259,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>373</v>
+        <v>386</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11194,7 +11279,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11206,10 +11291,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11227,7 +11312,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11239,22 +11324,22 @@
         <v>28</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c t="s" r="K315" s="7">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
       <c t="s" r="A316" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B316" s="7">
         <v>1980</v>
@@ -11264,7 +11349,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11273,10 +11358,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>18</v>
@@ -11312,7 +11397,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11321,18 +11406,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>275</v>
+        <v>285</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -11347,27 +11432,27 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -11382,7 +11467,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11391,18 +11476,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>377</v>
+        <v>390</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -11417,26 +11502,28 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
-      <c r="M321" s="7"/>
+      <c t="s" r="M321" s="7">
+        <v>391</v>
+      </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
       <c t="s" r="A322" s="6">
@@ -11450,7 +11537,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11459,13 +11546,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11483,22 +11570,22 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11516,7 +11603,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11525,10 +11612,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>25</v>
@@ -11549,22 +11636,22 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11582,7 +11669,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11594,10 +11681,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11630,7 +11717,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -11642,15 +11729,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>381</v>
+        <v>395</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -11665,7 +11752,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -11674,18 +11761,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>382</v>
+        <v>396</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -11700,22 +11787,22 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11733,22 +11820,22 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11766,22 +11853,22 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H332" s="8">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11799,22 +11886,22 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11832,22 +11919,22 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11880,7 +11967,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -11889,18 +11976,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>387</v>
+        <v>401</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -11915,26 +12002,30 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>106</v>
-      </c>
-      <c r="K337" s="7"/>
+        <v>110</v>
+      </c>
+      <c t="s" r="K337" s="7">
+        <v>376</v>
+      </c>
       <c r="L337" s="7"/>
-      <c r="M337" s="7"/>
+      <c t="s" r="M337" s="7">
+        <v>82</v>
+      </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
       <c t="s" r="A338" s="6">
@@ -11948,7 +12039,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -11957,17 +12048,21 @@
         <v>17</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I338" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>107</v>
-      </c>
-      <c r="K338" s="7"/>
+        <v>112</v>
+      </c>
+      <c t="s" r="K338" s="7">
+        <v>187</v>
+      </c>
       <c r="L338" s="7"/>
-      <c r="M338" s="7"/>
+      <c t="s" r="M338" s="7">
+        <v>128</v>
+      </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
       <c t="s" r="A339" s="6">
@@ -11981,26 +12076,30 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>52</v>
-      </c>
-      <c r="K339" s="7"/>
+        <v>54</v>
+      </c>
+      <c t="s" r="K339" s="7">
+        <v>85</v>
+      </c>
       <c r="L339" s="7"/>
-      <c r="M339" s="7"/>
+      <c t="s" r="M339" s="7">
+        <v>65</v>
+      </c>
     </row>
     <row r="340" ht="15" customHeight="1">
       <c r="A340" s="6"/>
@@ -12029,7 +12128,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -12041,15 +12140,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>391</v>
+        <v>405</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12064,7 +12163,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -12076,15 +12175,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>228</v>
+        <v>238</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -12099,7 +12198,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -12111,10 +12210,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>343</v>
+        <v>406</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -12132,7 +12231,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -12144,10 +12243,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -12165,7 +12264,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12177,10 +12276,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12198,7 +12297,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12210,10 +12309,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12246,7 +12345,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12258,15 +12357,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>263</v>
+        <v>274</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -12281,7 +12380,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12293,7 +12392,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c t="s" r="J349" s="7">
         <v>33</v>
@@ -12314,7 +12413,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12323,13 +12422,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="I350" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12347,19 +12446,19 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>25</v>
@@ -12380,7 +12479,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12392,10 +12491,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12428,7 +12527,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12440,15 +12539,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -12463,7 +12562,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12472,17 +12571,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
-      <c r="M355" s="7"/>
+      <c t="s" r="M355" s="7">
+        <v>410</v>
+      </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
       <c t="s" r="A356" s="6">
@@ -12496,22 +12597,22 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12529,7 +12630,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12538,13 +12639,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12562,22 +12663,22 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
+        <v>90</v>
+      </c>
+      <c t="s" r="H358" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I358" s="7">
         <v>87</v>
       </c>
-      <c t="s" r="H358" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I358" s="7">
-        <v>84</v>
-      </c>
       <c t="s" r="J358" s="7">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12595,7 +12696,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12607,10 +12708,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12628,7 +12729,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12640,10 +12741,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12676,7 +12777,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -12688,15 +12789,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>399</v>
+        <v>415</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -12711,7 +12812,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -12726,12 +12827,12 @@
         <v>30</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>400</v>
+        <v>416</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -12746,7 +12847,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -12755,13 +12856,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12779,22 +12880,22 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="H365" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12812,7 +12913,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -12824,10 +12925,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12845,7 +12946,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -12857,10 +12958,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12893,7 +12994,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12902,18 +13003,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>403</v>
+        <v>419</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -12928,22 +13029,22 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12961,7 +13062,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12970,13 +13071,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12994,22 +13095,22 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13042,7 +13143,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13051,18 +13152,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -13077,22 +13178,22 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13110,7 +13211,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13119,13 +13220,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13143,22 +13244,22 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13166,7 +13267,7 @@
     </row>
     <row r="378" ht="14.25" customHeight="1">
       <c t="s" r="A378" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B378" s="7">
         <v>828</v>
@@ -13176,7 +13277,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13188,10 +13289,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13224,27 +13325,27 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>409</v>
+        <v>425</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -13259,7 +13360,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13274,7 +13375,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13292,7 +13393,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13301,10 +13402,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c t="s" r="J382" s="7">
         <v>25</v>
@@ -13325,22 +13426,22 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13358,7 +13459,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13367,13 +13468,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13381,7 +13482,7 @@
     </row>
     <row r="385" ht="15" customHeight="1">
       <c t="s" r="A385" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B385" s="7">
         <v>859</v>
@@ -13391,22 +13492,22 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13439,7 +13540,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13448,10 +13549,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>19</v>
@@ -13472,22 +13573,22 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13520,27 +13621,27 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="F390" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -13555,7 +13656,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="F391" s="7">
         <v>330</v>
@@ -13567,7 +13668,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>19</v>
@@ -13588,7 +13689,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="F392" s="7">
         <v>330</v>
@@ -13597,13 +13698,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13621,22 +13722,22 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="F393" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13669,27 +13770,27 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="F395" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G395" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="H395" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>226</v>
+        <v>236</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -13704,7 +13805,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="F396" s="7">
         <v>330</v>
@@ -13716,10 +13817,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13737,7 +13838,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="F397" s="7">
         <v>330</v>
@@ -13749,10 +13850,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13785,7 +13886,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="F399" s="7">
         <v>330</v>
@@ -13797,15 +13898,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>422</v>
+        <v>438</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -13816,11 +13917,11 @@
         <v>2866</v>
       </c>
       <c t="s" r="C400" s="7">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="F400" s="7">
         <v>330</v>
@@ -13829,18 +13930,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>424</v>
+        <v>440</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -13851,33 +13952,33 @@
         <v>2867</v>
       </c>
       <c t="s" r="C401" s="7">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c t="s" r="K401" s="7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>425</v>
+        <v>441</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -13907,27 +14008,27 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c t="s" r="H403" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>428</v>
+        <v>444</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -13942,7 +14043,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
@@ -13954,10 +14055,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13965,7 +14066,7 @@
     </row>
     <row r="405" ht="15" customHeight="1">
       <c t="s" r="A405" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B405" s="7">
         <v>932</v>
@@ -13975,7 +14076,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
@@ -13984,13 +14085,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -14023,27 +14124,27 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>431</v>
+        <v>447</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -14066,14 +14167,14 @@
         <v>13</v>
       </c>
       <c r="B409" s="7">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c t="s" r="C409" s="7">
         <v>14</v>
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
@@ -14082,62 +14183,70 @@
         <v>17</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>91</v>
-      </c>
-      <c r="K409" s="7"/>
+        <v>39</v>
+      </c>
+      <c t="s" r="K409" s="7">
+        <v>82</v>
+      </c>
       <c r="L409" s="7"/>
-      <c r="M409" s="7"/>
+      <c t="s" r="M409" s="7">
+        <v>450</v>
+      </c>
     </row>
     <row r="410" ht="15" customHeight="1">
-      <c r="A410" s="6"/>
-      <c r="B410" s="7"/>
-      <c r="C410" s="7"/>
+      <c t="s" r="A410" s="6">
+        <v>13</v>
+      </c>
+      <c r="B410" s="7">
+        <v>84</v>
+      </c>
+      <c t="s" r="C410" s="7">
+        <v>14</v>
+      </c>
       <c r="D410" s="7"/>
-      <c r="E410" s="7"/>
-      <c r="F410" s="7"/>
-      <c r="G410" s="8"/>
-      <c r="H410" s="8"/>
-      <c r="I410" s="7"/>
-      <c r="J410" s="7"/>
-      <c r="K410" s="7"/>
+      <c t="s" r="E410" s="7">
+        <v>448</v>
+      </c>
+      <c r="F410" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G410" s="8">
+        <v>449</v>
+      </c>
+      <c t="s" r="H410" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I410" s="7">
+        <v>451</v>
+      </c>
+      <c t="s" r="J410" s="7">
+        <v>254</v>
+      </c>
+      <c t="s" r="K410" s="7">
+        <v>331</v>
+      </c>
       <c r="L410" s="7"/>
-      <c r="M410" s="7"/>
+      <c t="s" r="M410" s="7">
+        <v>293</v>
+      </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
-      <c t="s" r="A411" s="6">
-        <v>13</v>
-      </c>
-      <c r="B411" s="7">
-        <v>83</v>
-      </c>
-      <c t="s" r="C411" s="7">
-        <v>14</v>
-      </c>
+      <c r="A411" s="6"/>
+      <c r="B411" s="7"/>
+      <c r="C411" s="7"/>
       <c r="D411" s="7"/>
-      <c t="s" r="E411" s="7">
-        <v>433</v>
-      </c>
-      <c r="F411" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G411" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H411" s="8">
-        <v>434</v>
-      </c>
-      <c t="s" r="I411" s="7">
-        <v>342</v>
-      </c>
-      <c t="s" r="J411" s="7">
-        <v>38</v>
-      </c>
+      <c r="E411" s="7"/>
+      <c r="F411" s="7"/>
+      <c r="G411" s="8"/>
+      <c r="H411" s="8"/>
+      <c r="I411" s="7"/>
+      <c r="J411" s="7"/>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c r="M411" s="7"/>
@@ -14147,29 +14256,29 @@
         <v>13</v>
       </c>
       <c r="B412" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="C412" s="7">
         <v>14</v>
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>433</v>
+        <v>452</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>434</v>
+        <v>17</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>17</v>
+        <v>443</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>435</v>
+        <v>372</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>244</v>
+        <v>94</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14177,7 +14286,7 @@
     </row>
     <row r="413" ht="15.75" customHeight="1">
       <c t="s" r="A413" s="9">
-        <v>436</v>
+        <v>453</v>
       </c>
       <c r="B413" s="9"/>
       <c r="C413" s="9"/>
@@ -14197,7 +14306,7 @@
     <row r="414" ht="65.25" customHeight="1"/>
     <row r="415" ht="17.25" customHeight="1">
       <c t="s" r="A415" s="10">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="B415" s="10"/>
       <c r="C415" s="10"/>
@@ -14210,7 +14319,7 @@
       <c r="J415" s="10"/>
       <c r="K415" s="10"/>
       <c t="s" r="L415" s="11">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="M415" s="11"/>
       <c r="N415" s="11"/>
